--- a/Översikt KRAMFORS.xlsx
+++ b/Översikt KRAMFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45544</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>46183</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>45447</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>45974</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>46003</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>46094</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>46197</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>45763</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>44810</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>46196</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45831</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>45763</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>46197</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>46044</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>46241</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>46136</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>45056</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>46002</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>46181</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>46203</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>45511</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>45763</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>46196</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>46136</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>45723</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>46265</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>44713</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>45399</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>45973</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>45985</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>45974</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>45785</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>45484</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>45818</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>44524</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         <v>45356</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>45660</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>45733</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>45996</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>44629</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>45516</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>45957</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>45959</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>45985</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>45282</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>46046</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
         <v>46195</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>44813</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>46258</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>45806</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>45818</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>44967</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>45898</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>45898</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>45511</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>46036</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>46178</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>45114</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>46244</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>46254</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>45182</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7753,7 +7753,7 @@
         <v>46273</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>45665</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>45551</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>45786</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>46241</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>45468</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>45729</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>45840</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>45750</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>45156</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>45645</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>45344</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         <v>45764</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>44965</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>44852</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>45670</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>45924</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>45943</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         <v>45199</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>44803</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>45979</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>45998</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>46020</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>46021</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>46024</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         <v>46030</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         <v>46030</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>46048</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>46071</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>46098</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>45764</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>45243</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>45636</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>45114</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>45400</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>46281</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>45071</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>44817</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>44804</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>44634</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>44469</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>44859</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>44508</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>44508</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>44594</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>44608</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>44509</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>44496</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>44587</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>44511</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>44592</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44592</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>44722</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>44459</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>44688</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>44556</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>44852</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>44508</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>44817</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>44817</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>44762</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>44509</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>44859</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>44581</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>44516</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>44509</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13853,7 +13853,7 @@
         <v>44539</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>44566</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>44687</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>44594</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>44719</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>44715</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>44484</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>44803</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>44629</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>44594</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>44802</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>44509</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>44540</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>44482</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>44465</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>44550</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44607</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>44876</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>44628</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>44616</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>44749</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         <v>44697</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>44581</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>44503</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>44859</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>44484</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
         <v>44601</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15829,7 +15829,7 @@
         <v>44782</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>44474</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>44581</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>44804</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>44482</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
         <v>45365</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>44958</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16340,7 +16340,7 @@
         <v>44610</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>45588</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16486,7 +16486,7 @@
         <v>45588</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16559,7 +16559,7 @@
         <v>45588</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>45440</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>45124</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>45205</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>44608</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>44634</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>44629</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>45664</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>44991</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>45721</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>44573</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
         <v>44958</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>45307</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17518,7 +17518,7 @@
         <v>44460</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>45148</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
         <v>45190</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>45534</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17810,7 +17810,7 @@
         <v>45000</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>44978</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
         <v>45329</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>45279</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18107,7 +18107,7 @@
         <v>45712</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>45327</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>45526</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>45518</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18399,7 +18399,7 @@
         <v>45099</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18472,7 +18472,7 @@
         <v>45225</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>44830</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
         <v>45724</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>45265</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>45483</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>45232</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>44958</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>45351</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>44909</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>45482</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>44792</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>45512</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45491</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>45202</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>44469</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>45225</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>45754</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>45323</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>45461</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19879,7 +19879,7 @@
         <v>45469</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         <v>45623</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>45623</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>44879</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>44606</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>45345</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>45294</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>44956</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>45433</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20546,7 +20546,7 @@
         <v>44946</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>44546</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>45273</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20765,7 +20765,7 @@
         <v>44998</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>45085</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>45757</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>45034</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>44574</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>44826</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>45000</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>45273</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>45153</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>45153</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>44908</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>45008</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>44949</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>44503</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>45714</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>45685</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>45685</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44894</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>45036</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>45733</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>44942</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>44965</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>44965</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>45707</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>45324</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>45943</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>44951</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>45425</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>45684</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>45616</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>46029</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>46136</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23131,7 +23131,7 @@
         <v>45754</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>45524</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>45797</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23350,7 +23350,7 @@
         <v>46069</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>45959</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>45247</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>45589</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45888</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>45890</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>45890</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>45890</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>45763</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>45008</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         <v>45674</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>45726</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>45454</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>45636</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>45973</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24450,7 +24450,7 @@
         <v>45672</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>45960</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24596,7 +24596,7 @@
         <v>45821</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>45909</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44574</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24815,7 +24815,7 @@
         <v>45043</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>45898</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24966,7 +24966,7 @@
         <v>45901</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>45898</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25112,7 +25112,7 @@
         <v>45898</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25185,7 +25185,7 @@
         <v>45898</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>45901</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>45898</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>45901</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         <v>45898</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>45898</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>45898</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>45898</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>45898</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25842,7 +25842,7 @@
         <v>45841</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>45881</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>45909</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>45554</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         <v>45894</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>45729</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26280,7 +26280,7 @@
         <v>45909</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>45909</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26426,7 +26426,7 @@
         <v>46107</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26499,7 +26499,7 @@
         <v>45771</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26572,7 +26572,7 @@
         <v>45685</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26645,7 +26645,7 @@
         <v>44727</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26718,7 +26718,7 @@
         <v>45989</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26791,7 +26791,7 @@
         <v>45475</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>45912</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26942,7 +26942,7 @@
         <v>45959</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27015,7 +27015,7 @@
         <v>45062</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27088,7 +27088,7 @@
         <v>45544</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27161,7 +27161,7 @@
         <v>46084</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27234,7 +27234,7 @@
         <v>45513</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27307,7 +27307,7 @@
         <v>45876</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27380,7 +27380,7 @@
         <v>45842</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         <v>46064</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27526,7 +27526,7 @@
         <v>44855</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27599,7 +27599,7 @@
         <v>44840</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27672,7 +27672,7 @@
         <v>45875</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27745,7 +27745,7 @@
         <v>45931</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27818,7 +27818,7 @@
         <v>45918</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27891,7 +27891,7 @@
         <v>44852</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27964,7 +27964,7 @@
         <v>44519</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>45282</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28110,7 +28110,7 @@
         <v>45173</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>45280</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>45698</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28329,7 +28329,7 @@
         <v>45818</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28402,7 +28402,7 @@
         <v>45644</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>45896</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>45813</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>44782</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>44943</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28772,7 +28772,7 @@
         <v>45553</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>45278</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>45926</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>45926</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>46140</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29137,7 +29137,7 @@
         <v>46142</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29210,7 +29210,7 @@
         <v>44466</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>45744</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29361,7 +29361,7 @@
         <v>45932</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29439,7 +29439,7 @@
         <v>45418</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29512,7 +29512,7 @@
         <v>45935</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>45936</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>45190</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>45937</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29809,7 +29809,7 @@
         <v>44883</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29882,7 +29882,7 @@
         <v>46147</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>46146</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>46146</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>45936</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>46146</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30252,7 +30252,7 @@
         <v>45937</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30325,7 +30325,7 @@
         <v>45750</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>45943</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>44774</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30544,7 +30544,7 @@
         <v>45541</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>46149</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30690,7 +30690,7 @@
         <v>46149</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30763,7 +30763,7 @@
         <v>45355</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>46148</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30914,7 +30914,7 @@
         <v>44747</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>45946</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>45947</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31133,7 +31133,7 @@
         <v>45951</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>45638</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31279,7 +31279,7 @@
         <v>45952</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>45952</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31425,7 +31425,7 @@
         <v>45120</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>45672</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>45740</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>45957</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31722,7 +31722,7 @@
         <v>45680</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31795,7 +31795,7 @@
         <v>46153</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31868,7 +31868,7 @@
         <v>45674</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31941,7 +31941,7 @@
         <v>44956</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32014,7 +32014,7 @@
         <v>44956</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32087,7 +32087,7 @@
         <v>44897</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>45960</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>45964</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>45964</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>45964</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>45964</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>45964</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>45743</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>45950</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>45261</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>45964</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32900,7 +32900,7 @@
         <v>45294</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32973,7 +32973,7 @@
         <v>45964</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
         <v>45561</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33124,7 +33124,7 @@
         <v>45964</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33197,7 +33197,7 @@
         <v>44834</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>45950</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>45950</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33416,7 +33416,7 @@
         <v>45884</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33489,7 +33489,7 @@
         <v>46155</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>45750</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>45750</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33708,7 +33708,7 @@
         <v>45320</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33781,7 +33781,7 @@
         <v>44803</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33854,7 +33854,7 @@
         <v>45392</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>45968</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34000,7 +34000,7 @@
         <v>45968</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34073,7 +34073,7 @@
         <v>45971</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>45974</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34219,7 +34219,7 @@
         <v>45974</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34292,7 +34292,7 @@
         <v>45974</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>45044</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34438,7 +34438,7 @@
         <v>45959</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34511,7 +34511,7 @@
         <v>45974</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34584,7 +34584,7 @@
         <v>45974</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34657,7 +34657,7 @@
         <v>45974</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>45974</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34803,7 +34803,7 @@
         <v>45496</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34881,7 +34881,7 @@
         <v>45979</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>45979</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>45979</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>45979</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>45758</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>45979</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>45979</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>45979</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35465,7 +35465,7 @@
         <v>45981</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35538,7 +35538,7 @@
         <v>46155</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35611,7 +35611,7 @@
         <v>46155</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>45981</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>45981</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>44813</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>45763</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>45982</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36054,7 +36054,7 @@
         <v>45982</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36127,7 +36127,7 @@
         <v>45328</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36205,7 +36205,7 @@
         <v>45764</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36278,7 +36278,7 @@
         <v>45986</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36351,7 +36351,7 @@
         <v>45987</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36424,7 +36424,7 @@
         <v>46157</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36497,7 +36497,7 @@
         <v>45433</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36570,7 +36570,7 @@
         <v>45987</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36643,7 +36643,7 @@
         <v>45476</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36716,7 +36716,7 @@
         <v>45988</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36789,7 +36789,7 @@
         <v>44901</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36862,7 +36862,7 @@
         <v>45988</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36935,7 +36935,7 @@
         <v>46098</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37008,7 +37008,7 @@
         <v>44804</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37081,7 +37081,7 @@
         <v>45545</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37154,7 +37154,7 @@
         <v>46160</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37227,7 +37227,7 @@
         <v>45763</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37305,7 +37305,7 @@
         <v>45763</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>46064</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>45502</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37529,7 +37529,7 @@
         <v>44529</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37602,7 +37602,7 @@
         <v>45947</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>45947</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37748,7 +37748,7 @@
         <v>45679</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37821,7 +37821,7 @@
         <v>45707</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37894,7 +37894,7 @@
         <v>45959</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37967,7 +37967,7 @@
         <v>46160</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38045,7 +38045,7 @@
         <v>46160</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>45916</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38191,7 +38191,7 @@
         <v>46161</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38264,7 +38264,7 @@
         <v>45336</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>45734</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38410,7 +38410,7 @@
         <v>45957</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38483,7 +38483,7 @@
         <v>45728</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>45947</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38629,7 +38629,7 @@
         <v>46163</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>46047</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>45994</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38848,7 +38848,7 @@
         <v>44956</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38921,7 +38921,7 @@
         <v>46163</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38994,7 +38994,7 @@
         <v>44959</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>45999</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>45999</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39218,7 +39218,7 @@
         <v>45959</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39291,7 +39291,7 @@
         <v>45996</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39364,7 +39364,7 @@
         <v>44915</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39437,7 +39437,7 @@
         <v>46164</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39510,7 +39510,7 @@
         <v>46000</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39583,7 +39583,7 @@
         <v>46000</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39656,7 +39656,7 @@
         <v>46000</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39729,7 +39729,7 @@
         <v>46167</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>46001</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>45278</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39948,7 +39948,7 @@
         <v>46164</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40021,7 +40021,7 @@
         <v>46002</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>46164</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40167,7 +40167,7 @@
         <v>46007</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>46007</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40313,7 +40313,7 @@
         <v>45952</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40386,7 +40386,7 @@
         <v>45552</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40459,7 +40459,7 @@
         <v>45771</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40532,7 +40532,7 @@
         <v>45771</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40605,7 +40605,7 @@
         <v>46009</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>46008</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40751,7 +40751,7 @@
         <v>46146</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40824,7 +40824,7 @@
         <v>46009</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>44739</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40970,7 +40970,7 @@
         <v>46008</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41043,7 +41043,7 @@
         <v>46009</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41116,7 +41116,7 @@
         <v>46008</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41189,7 +41189,7 @@
         <v>46008</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41262,7 +41262,7 @@
         <v>46008</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>46008</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41408,7 +41408,7 @@
         <v>46008</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         <v>46009</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41554,7 +41554,7 @@
         <v>46009</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41627,7 +41627,7 @@
         <v>45034</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>46168</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41773,7 +41773,7 @@
         <v>44872</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41846,7 +41846,7 @@
         <v>46169</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41919,7 +41919,7 @@
         <v>46014</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41992,7 +41992,7 @@
         <v>45173</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42065,7 +42065,7 @@
         <v>45474</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>45546</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42211,7 +42211,7 @@
         <v>44775</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42284,7 +42284,7 @@
         <v>46168</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42357,7 +42357,7 @@
         <v>45981</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42430,7 +42430,7 @@
         <v>45300</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42503,7 +42503,7 @@
         <v>45608</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42576,7 +42576,7 @@
         <v>44529</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42649,7 +42649,7 @@
         <v>46022</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42722,7 +42722,7 @@
         <v>46024</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42795,7 +42795,7 @@
         <v>46024</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42868,7 +42868,7 @@
         <v>45712</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>46024</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>46024</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>45034</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>45040</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43233,7 +43233,7 @@
         <v>46029</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43306,7 +43306,7 @@
         <v>44741</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43379,7 +43379,7 @@
         <v>46031</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43452,7 +43452,7 @@
         <v>46031</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43525,7 +43525,7 @@
         <v>46170</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43598,7 +43598,7 @@
         <v>44894</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43671,7 +43671,7 @@
         <v>46034</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>45265</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>46174</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>46041</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43963,7 +43963,7 @@
         <v>46041</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44036,7 +44036,7 @@
         <v>46041</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>46174</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
         <v>46043</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44255,7 +44255,7 @@
         <v>46043</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44328,7 +44328,7 @@
         <v>46043</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44401,7 +44401,7 @@
         <v>44571</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44474,7 +44474,7 @@
         <v>46043</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44547,7 +44547,7 @@
         <v>46042</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44620,7 +44620,7 @@
         <v>46043</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45034</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44766,7 +44766,7 @@
         <v>46174</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44839,7 +44839,7 @@
         <v>46174</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44912,7 +44912,7 @@
         <v>45664</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44985,7 +44985,7 @@
         <v>46044</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45063,7 +45063,7 @@
         <v>45572</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45136,7 +45136,7 @@
         <v>44556</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>46044</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45282,7 +45282,7 @@
         <v>46174</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45355,7 +45355,7 @@
         <v>46049</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45428,7 +45428,7 @@
         <v>46048</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>45182</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>46049</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45647,7 +45647,7 @@
         <v>46046</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45720,7 +45720,7 @@
         <v>46049</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45793,7 +45793,7 @@
         <v>46043</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45866,7 +45866,7 @@
         <v>46046</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45939,7 +45939,7 @@
         <v>46046</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46012,7 +46012,7 @@
         <v>46047</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>46176</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46158,7 +46158,7 @@
         <v>46176</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>46054</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46304,7 +46304,7 @@
         <v>45161</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46377,7 +46377,7 @@
         <v>46046</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46450,7 +46450,7 @@
         <v>46054</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46523,7 +46523,7 @@
         <v>46054</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46596,7 +46596,7 @@
         <v>45302</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46669,7 +46669,7 @@
         <v>46046</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46742,7 +46742,7 @@
         <v>44916</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46815,7 +46815,7 @@
         <v>45425</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46893,7 +46893,7 @@
         <v>45763</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46971,7 +46971,7 @@
         <v>45044</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47044,7 +47044,7 @@
         <v>45674</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47117,7 +47117,7 @@
         <v>46177</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47190,7 +47190,7 @@
         <v>46063</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47263,7 +47263,7 @@
         <v>46063</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47336,7 +47336,7 @@
         <v>46062</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47409,7 +47409,7 @@
         <v>45356</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47482,7 +47482,7 @@
         <v>44971</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47555,7 +47555,7 @@
         <v>45450</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45660</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47701,7 +47701,7 @@
         <v>46069</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47774,7 +47774,7 @@
         <v>46069</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45173</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47920,7 +47920,7 @@
         <v>46181</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47993,7 +47993,7 @@
         <v>46181</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48066,7 +48066,7 @@
         <v>46181</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         <v>46181</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48212,7 +48212,7 @@
         <v>45419</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48285,7 +48285,7 @@
         <v>45729</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48358,7 +48358,7 @@
         <v>46181</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48436,7 +48436,7 @@
         <v>46043</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48509,7 +48509,7 @@
         <v>46071</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48582,7 +48582,7 @@
         <v>45513</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48655,7 +48655,7 @@
         <v>46072</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48728,7 +48728,7 @@
         <v>46072</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48801,7 +48801,7 @@
         <v>46181</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48874,7 +48874,7 @@
         <v>45764</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48952,7 +48952,7 @@
         <v>45420</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49025,7 +49025,7 @@
         <v>45632</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49098,7 +49098,7 @@
         <v>45189</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49171,7 +49171,7 @@
         <v>46077</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49244,7 +49244,7 @@
         <v>44880</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49317,7 +49317,7 @@
         <v>45163</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49395,7 +49395,7 @@
         <v>46188</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49468,7 +49468,7 @@
         <v>46188</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>46188</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>45239</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49692,7 +49692,7 @@
         <v>45645</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>45579</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49843,7 +49843,7 @@
         <v>45538</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>45450</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49989,7 +49989,7 @@
         <v>46190</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50062,7 +50062,7 @@
         <v>46190</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50135,7 +50135,7 @@
         <v>44769</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>46094</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50281,7 +50281,7 @@
         <v>44965</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50354,7 +50354,7 @@
         <v>46093</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45724</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50500,7 +50500,7 @@
         <v>46190</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50573,7 +50573,7 @@
         <v>46190</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50646,7 +50646,7 @@
         <v>46052</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50719,7 +50719,7 @@
         <v>46098</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50792,7 +50792,7 @@
         <v>45365</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50865,7 +50865,7 @@
         <v>46098</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50938,7 +50938,7 @@
         <v>46099</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51016,7 +51016,7 @@
         <v>46099</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51089,7 +51089,7 @@
         <v>46195</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51162,7 +51162,7 @@
         <v>46195</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51235,7 +51235,7 @@
         <v>44888</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51308,7 +51308,7 @@
         <v>44908</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51381,7 +51381,7 @@
         <v>46100</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51454,7 +51454,7 @@
         <v>46104</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51527,7 +51527,7 @@
         <v>46195</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51600,7 +51600,7 @@
         <v>45365</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51673,7 +51673,7 @@
         <v>46104</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51746,7 +51746,7 @@
         <v>45034</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51819,7 +51819,7 @@
         <v>46105</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51892,7 +51892,7 @@
         <v>46198</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51965,7 +51965,7 @@
         <v>46198</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>46198</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52111,7 +52111,7 @@
         <v>46198</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52184,7 +52184,7 @@
         <v>46198</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52257,7 +52257,7 @@
         <v>46199</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52330,7 +52330,7 @@
         <v>46199</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52403,7 +52403,7 @@
         <v>44536</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52481,7 +52481,7 @@
         <v>46119</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52554,7 +52554,7 @@
         <v>46034</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52627,7 +52627,7 @@
         <v>44613</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52705,7 +52705,7 @@
         <v>46244</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>46071</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>44608</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52924,7 +52924,7 @@
         <v>46127</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52997,7 +52997,7 @@
         <v>46128</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53070,7 +53070,7 @@
         <v>46112</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53143,7 +53143,7 @@
         <v>46127</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53216,7 +53216,7 @@
         <v>46199</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53289,7 +53289,7 @@
         <v>45764</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53367,7 +53367,7 @@
         <v>45726</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53440,7 +53440,7 @@
         <v>46244</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53513,7 +53513,7 @@
         <v>46204</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53586,7 +53586,7 @@
         <v>44880</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53659,7 +53659,7 @@
         <v>45589</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53732,7 +53732,7 @@
         <v>45034</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53805,7 +53805,7 @@
         <v>44477</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53878,7 +53878,7 @@
         <v>45365</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53951,7 +53951,7 @@
         <v>46134</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54024,7 +54024,7 @@
         <v>46134</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54097,7 +54097,7 @@
         <v>45089</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54170,7 +54170,7 @@
         <v>44853</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54243,7 +54243,7 @@
         <v>45366</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54316,7 +54316,7 @@
         <v>45684</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54389,7 +54389,7 @@
         <v>45680</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54462,7 +54462,7 @@
         <v>44865</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54535,7 +54535,7 @@
         <v>45390</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54608,7 +54608,7 @@
         <v>46247</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54686,7 +54686,7 @@
         <v>45324</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54759,7 +54759,7 @@
         <v>45447</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54832,7 +54832,7 @@
         <v>45236</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54905,7 +54905,7 @@
         <v>44537</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54978,7 +54978,7 @@
         <v>45723</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55051,7 +55051,7 @@
         <v>45713</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55124,7 +55124,7 @@
         <v>46251</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55197,7 +55197,7 @@
         <v>46205</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55270,7 +55270,7 @@
         <v>45236</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55343,7 +55343,7 @@
         <v>45162</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55416,7 +55416,7 @@
         <v>45062</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55489,7 +55489,7 @@
         <v>44750</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55562,7 +55562,7 @@
         <v>46248</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55640,7 +55640,7 @@
         <v>45240</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55713,7 +55713,7 @@
         <v>44958</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55786,7 +55786,7 @@
         <v>45678</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55859,7 +55859,7 @@
         <v>45189</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55932,7 +55932,7 @@
         <v>46251</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56010,7 +56010,7 @@
         <v>46251</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56083,7 +56083,7 @@
         <v>45392</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56156,7 +56156,7 @@
         <v>45237</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56229,7 +56229,7 @@
         <v>46248</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56302,7 +56302,7 @@
         <v>44907</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56375,7 +56375,7 @@
         <v>45198</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56453,7 +56453,7 @@
         <v>46253</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56526,7 +56526,7 @@
         <v>46209</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56599,7 +56599,7 @@
         <v>45324</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56672,7 +56672,7 @@
         <v>46209</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56745,7 +56745,7 @@
         <v>45209</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56818,7 +56818,7 @@
         <v>45162</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56891,7 +56891,7 @@
         <v>45162</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56964,7 +56964,7 @@
         <v>46209</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57037,7 +57037,7 @@
         <v>46210</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57110,7 +57110,7 @@
         <v>46253</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57183,7 +57183,7 @@
         <v>46210</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57256,7 +57256,7 @@
         <v>45520</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57329,7 +57329,7 @@
         <v>46253</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57402,7 +57402,7 @@
         <v>45271</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57475,7 +57475,7 @@
         <v>44824</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57548,7 +57548,7 @@
         <v>46254</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57626,7 +57626,7 @@
         <v>46254</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57704,7 +57704,7 @@
         <v>45320</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57782,7 +57782,7 @@
         <v>44573</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57855,7 +57855,7 @@
         <v>46256</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57928,7 +57928,7 @@
         <v>46256</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>44574</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58074,7 +58074,7 @@
         <v>45273</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58147,7 +58147,7 @@
         <v>45519</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58220,7 +58220,7 @@
         <v>44819</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58293,7 +58293,7 @@
         <v>44638</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58366,7 +58366,7 @@
         <v>46258</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58444,7 +58444,7 @@
         <v>45763</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58522,7 +58522,7 @@
         <v>45099</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58595,7 +58595,7 @@
         <v>46265</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58673,7 +58673,7 @@
         <v>46265</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58751,7 +58751,7 @@
         <v>45365</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58824,7 +58824,7 @@
         <v>46265</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58902,7 +58902,7 @@
         <v>45180</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58975,7 +58975,7 @@
         <v>46265</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59048,7 +59048,7 @@
         <v>45400</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59121,7 +59121,7 @@
         <v>46262</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59194,7 +59194,7 @@
         <v>44860</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59267,7 +59267,7 @@
         <v>45099</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59340,7 +59340,7 @@
         <v>45232</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59418,7 +59418,7 @@
         <v>46164</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59491,7 +59491,7 @@
         <v>46140</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59564,7 +59564,7 @@
         <v>46265</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59642,7 +59642,7 @@
         <v>46265</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59720,7 +59720,7 @@
         <v>46262</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59793,7 +59793,7 @@
         <v>45271</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59866,7 +59866,7 @@
         <v>46253</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59944,7 +59944,7 @@
         <v>46266</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60017,7 +60017,7 @@
         <v>45328</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60090,7 +60090,7 @@
         <v>45770</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60168,7 +60168,7 @@
         <v>46265</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60241,7 +60241,7 @@
         <v>46267</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60314,7 +60314,7 @@
         <v>44788</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60387,7 +60387,7 @@
         <v>46253</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60465,7 +60465,7 @@
         <v>46266</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60538,7 +60538,7 @@
         <v>46224</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60616,7 +60616,7 @@
         <v>46268</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60689,7 +60689,7 @@
         <v>44564</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60762,7 +60762,7 @@
         <v>46266</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60835,7 +60835,7 @@
         <v>45034</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60908,7 +60908,7 @@
         <v>46254</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60981,7 +60981,7 @@
         <v>46254</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61054,7 +61054,7 @@
         <v>44998</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61127,7 +61127,7 @@
         <v>45645</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61200,7 +61200,7 @@
         <v>45645</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61273,7 +61273,7 @@
         <v>46225</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61346,7 +61346,7 @@
         <v>46268</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61419,7 +61419,7 @@
         <v>45776</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61497,7 +61497,7 @@
         <v>46266</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61570,7 +61570,7 @@
         <v>45782</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61643,7 +61643,7 @@
         <v>46273</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61716,7 +61716,7 @@
         <v>46273</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61789,7 +61789,7 @@
         <v>45496</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61867,7 +61867,7 @@
         <v>46120</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61940,7 +61940,7 @@
         <v>46274</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62018,7 +62018,7 @@
         <v>46232</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62091,7 +62091,7 @@
         <v>46262</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62164,7 +62164,7 @@
         <v>46274</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62237,7 +62237,7 @@
         <v>45408</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62310,7 +62310,7 @@
         <v>46036</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62383,7 +62383,7 @@
         <v>45476</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62456,7 +62456,7 @@
         <v>44834</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62534,7 +62534,7 @@
         <v>45281</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62607,7 +62607,7 @@
         <v>46281</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62680,7 +62680,7 @@
         <v>45306</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62753,7 +62753,7 @@
         <v>44854</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62826,7 +62826,7 @@
         <v>44540</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62899,7 +62899,7 @@
         <v>45791</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62972,7 +62972,7 @@
         <v>46280</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63045,7 +63045,7 @@
         <v>46237</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63118,7 +63118,7 @@
         <v>45496</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63196,7 +63196,7 @@
         <v>46238</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63269,7 +63269,7 @@
         <v>46238</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63342,7 +63342,7 @@
         <v>46280</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63415,7 +63415,7 @@
         <v>46238</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63488,7 +63488,7 @@
         <v>45231</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63561,7 +63561,7 @@
         <v>45790</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63634,7 +63634,7 @@
         <v>46237</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63707,7 +63707,7 @@
         <v>45169</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63780,7 +63780,7 @@
         <v>45618</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63853,7 +63853,7 @@
         <v>45567</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63926,7 +63926,7 @@
         <v>45792</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -63999,7 +63999,7 @@
         <v>46281</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64072,7 +64072,7 @@
         <v>45418</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64145,7 +64145,7 @@
         <v>45415</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64218,7 +64218,7 @@
         <v>44503</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64291,7 +64291,7 @@
         <v>44804</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64364,7 +64364,7 @@
         <v>45435</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64442,7 +64442,7 @@
         <v>46239</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64515,7 +64515,7 @@
         <v>45797</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64588,7 +64588,7 @@
         <v>46239</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64661,7 +64661,7 @@
         <v>45552</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64734,7 +64734,7 @@
         <v>45797</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64807,7 +64807,7 @@
         <v>45798</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64885,7 +64885,7 @@
         <v>46240</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -64958,7 +64958,7 @@
         <v>45799</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65036,7 +65036,7 @@
         <v>46241</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65114,7 +65114,7 @@
         <v>45799</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65192,7 +65192,7 @@
         <v>46239</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65265,7 +65265,7 @@
         <v>46283</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65338,7 +65338,7 @@
         <v>44903</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65411,7 +65411,7 @@
         <v>45799</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65484,7 +65484,7 @@
         <v>45803</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65557,7 +65557,7 @@
         <v>45475</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65630,7 +65630,7 @@
         <v>44834</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65708,7 +65708,7 @@
         <v>45036</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65781,7 +65781,7 @@
         <v>45805</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65854,7 +65854,7 @@
         <v>45805</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -65927,7 +65927,7 @@
         <v>45643</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66000,7 +66000,7 @@
         <v>45807</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66078,7 +66078,7 @@
         <v>45726</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66151,7 +66151,7 @@
         <v>45734</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66224,7 +66224,7 @@
         <v>45654</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66297,7 +66297,7 @@
         <v>45712</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66370,7 +66370,7 @@
         <v>45678</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66443,7 +66443,7 @@
         <v>45593</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66516,7 +66516,7 @@
         <v>45813</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66589,7 +66589,7 @@
         <v>45782</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66662,7 +66662,7 @@
         <v>45813</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66735,7 +66735,7 @@
         <v>45653</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66808,7 +66808,7 @@
         <v>45753</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66881,7 +66881,7 @@
         <v>45768</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -66954,7 +66954,7 @@
         <v>45818</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67032,7 +67032,7 @@
         <v>45819</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67105,7 +67105,7 @@
         <v>45825</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67178,7 +67178,7 @@
         <v>45825</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67251,7 +67251,7 @@
         <v>45825</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67324,7 +67324,7 @@
         <v>45825</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67397,7 +67397,7 @@
         <v>45825</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67470,7 +67470,7 @@
         <v>45825</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67543,7 +67543,7 @@
         <v>45825</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67616,7 +67616,7 @@
         <v>45825</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67689,7 +67689,7 @@
         <v>45825</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67762,7 +67762,7 @@
         <v>45825</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67835,7 +67835,7 @@
         <v>45833</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -67913,7 +67913,7 @@
         <v>45832</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -67986,7 +67986,7 @@
         <v>45833</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68059,7 +68059,7 @@
         <v>45834</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68137,7 +68137,7 @@
         <v>45838</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68210,7 +68210,7 @@
         <v>45838</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68288,7 +68288,7 @@
         <v>45841</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68366,7 +68366,7 @@
         <v>45840</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68444,7 +68444,7 @@
         <v>45841</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68522,7 +68522,7 @@
         <v>45840</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68595,7 +68595,7 @@
         <v>45840</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68673,7 +68673,7 @@
         <v>45841</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68746,7 +68746,7 @@
         <v>45841</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68819,7 +68819,7 @@
         <v>45842</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -68892,7 +68892,7 @@
         <v>45852</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -68965,7 +68965,7 @@
         <v>45855</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69038,7 +69038,7 @@
         <v>45799</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69111,7 +69111,7 @@
         <v>45859</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69184,7 +69184,7 @@
         <v>45860</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69257,7 +69257,7 @@
         <v>45799</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69330,7 +69330,7 @@
         <v>45749</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69403,7 +69403,7 @@
         <v>45825</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69476,7 +69476,7 @@
         <v>45873</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69549,7 +69549,7 @@
         <v>45875</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69622,7 +69622,7 @@
         <v>45874</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69695,7 +69695,7 @@
         <v>45874</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69768,7 +69768,7 @@
         <v>45874</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -69841,7 +69841,7 @@
         <v>45877</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -69914,7 +69914,7 @@
         <v>45876</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -69987,7 +69987,7 @@
         <v>45881</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70060,7 +70060,7 @@
         <v>45881</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70133,7 +70133,7 @@
         <v>45883</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70206,7 +70206,7 @@
         <v>45883</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70279,7 +70279,7 @@
         <v>45883</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70352,7 +70352,7 @@
         <v>45883</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70425,7 +70425,7 @@
         <v>44880</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70498,7 +70498,7 @@
         <v>44971</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70571,7 +70571,7 @@
         <v>44467</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70644,7 +70644,7 @@
         <v>45751</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70717,7 +70717,7 @@
         <v>45751</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -70795,7 +70795,7 @@
         <v>45790</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -70873,7 +70873,7 @@
         <v>46041</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -70946,7 +70946,7 @@
         <v>46078</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71019,7 +71019,7 @@
         <v>46073</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71092,7 +71092,7 @@
         <v>46142</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>

--- a/Översikt KRAMFORS.xlsx
+++ b/Översikt KRAMFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45544</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>46183</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>46029</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45974</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>46003</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>46094</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>46197</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>45763</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>44810</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>46196</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>45831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>46287</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>45763</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>46044</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>46197</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>46241</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>46136</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45056</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>46002</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>45511</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>46203</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>45763</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>46181</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>46196</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>46136</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>45723</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>46265</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>44713</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>45973</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>45985</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>45818</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>45399</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>45974</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         <v>45785</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>45484</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44524</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>45356</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>45660</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>45733</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>45996</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>44629</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>45957</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>45959</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>45818</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>45985</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>45516</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>46195</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         <v>46258</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         <v>44813</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>45806</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>46046</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>45282</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>46036</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>45898</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         <v>45898</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>45468</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>45729</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>44967</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         <v>45511</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7398,7 +7398,7 @@
         <v>45840</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>46178</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>46254</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>45182</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>46273</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>45665</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>46241</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>46244</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>45114</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>45551</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>45786</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>45750</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>44803</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>45400</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>45114</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>46020</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>46021</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>46024</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>46030</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>46030</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>46048</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>45924</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>46071</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>45943</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>46098</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>44965</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>45979</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>45998</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>45670</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>45764</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>45645</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>45764</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
         <v>45156</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>46281</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>45636</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>45344</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44852</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>45243</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
         <v>45199</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         <v>45071</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>44817</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>44804</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>44634</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11931,7 +11931,7 @@
         <v>44859</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>44469</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>44508</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>44508</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>44594</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>44608</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>44509</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>44496</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>44587</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>44511</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>44592</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>44592</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>44722</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>44688</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>44556</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         <v>44852</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>44508</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>44817</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>44817</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>44762</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>44859</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>44509</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>44581</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>44516</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13688,7 +13688,7 @@
         <v>44509</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>44539</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         <v>44566</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>44687</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         <v>44594</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>44719</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>44715</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>44484</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>44803</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>44629</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>44594</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>44802</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>44509</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>44540</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>44482</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>44465</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>44550</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44607</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>44628</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>44876</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>44616</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>44749</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>44697</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>44581</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>44503</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>44859</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15591,7 +15591,7 @@
         <v>44484</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         <v>44601</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>44782</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>44474</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>44581</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>44804</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>45205</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>45712</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>45513</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>44741</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>44840</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>45672</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
         <v>45572</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>45043</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>45721</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>45044</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>44853</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>45724</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>45365</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>45209</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>45225</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>45496</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         <v>45450</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         <v>45265</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17353,7 +17353,7 @@
         <v>44901</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         <v>45261</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         <v>44477</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>44907</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>45089</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>44880</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>45278</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>45771</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>45415</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>45099</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>45883</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>45450</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>45883</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18302,7 +18302,7 @@
         <v>46014</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>44466</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>44958</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>45418</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>46022</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>44804</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18740,7 +18740,7 @@
         <v>44894</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         <v>45552</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>46024</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>46024</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19032,7 +19032,7 @@
         <v>46024</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19105,7 +19105,7 @@
         <v>46024</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19178,7 +19178,7 @@
         <v>44503</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19251,7 +19251,7 @@
         <v>45273</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19324,7 +19324,7 @@
         <v>45328</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>46029</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>44942</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>45435</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         <v>45482</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45797</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>45797</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>45365</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         <v>44903</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>45798</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>45883</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>46031</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>45469</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>44519</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>46034</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>46031</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20512,7 +20512,7 @@
         <v>45888</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>44529</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>45645</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>45799</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>45616</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>45890</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20955,7 +20955,7 @@
         <v>45890</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21028,7 +21028,7 @@
         <v>45890</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>44536</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>45674</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>44574</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21325,7 +21325,7 @@
         <v>46042</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>44634</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
         <v>45632</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>46041</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         <v>46041</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>46041</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>45898</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>46043</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>45545</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>46043</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>46044</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>44909</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22201,7 +22201,7 @@
         <v>45538</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>45898</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>45898</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         <v>45898</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>46043</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22571,7 +22571,7 @@
         <v>46043</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22644,7 +22644,7 @@
         <v>46043</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>46044</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>45898</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>45898</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>45898</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>46043</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>46048</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>45901</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23233,7 +23233,7 @@
         <v>46046</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>45425</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>45898</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>45898</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>45901</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
         <v>45898</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
         <v>44503</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23749,7 +23749,7 @@
         <v>46046</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23822,7 +23822,7 @@
         <v>46046</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23895,7 +23895,7 @@
         <v>46047</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23968,7 +23968,7 @@
         <v>45901</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>46049</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24114,7 +24114,7 @@
         <v>45799</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24187,7 +24187,7 @@
         <v>44908</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         <v>46049</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>46049</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>45664</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24479,7 +24479,7 @@
         <v>45799</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>45909</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>45909</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24703,7 +24703,7 @@
         <v>46046</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24776,7 +24776,7 @@
         <v>45491</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>44959</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>45909</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25005,7 +25005,7 @@
         <v>44872</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>46054</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>46054</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
         <v>45420</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>46046</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25370,7 +25370,7 @@
         <v>46054</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>45912</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>44958</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>44958</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>45518</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>46062</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25813,7 +25813,7 @@
         <v>44991</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>45918</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>46063</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>46063</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>44629</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>44546</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>44956</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>46069</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26402,7 +26402,7 @@
         <v>45750</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>45750</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>45803</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>45036</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>44834</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>46069</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>45805</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>45805</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>46071</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>46043</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27137,7 +27137,7 @@
         <v>46072</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>45513</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27283,7 +27283,7 @@
         <v>46072</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>45320</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>46077</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>45475</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>45225</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>45926</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>45926</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>44888</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27872,7 +27872,7 @@
         <v>45552</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27945,7 +27945,7 @@
         <v>45526</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>44638</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28091,7 +28091,7 @@
         <v>45643</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28164,7 +28164,7 @@
         <v>45932</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>45712</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>45190</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>45734</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>45678</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28534,7 +28534,7 @@
         <v>45807</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>45935</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28690,7 +28690,7 @@
         <v>45593</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>45324</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>44894</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>45936</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28982,7 +28982,7 @@
         <v>45723</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29055,7 +29055,7 @@
         <v>45654</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29128,7 +29128,7 @@
         <v>45937</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29201,7 +29201,7 @@
         <v>45936</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29274,7 +29274,7 @@
         <v>45937</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>44916</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29420,7 +29420,7 @@
         <v>44949</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29493,7 +29493,7 @@
         <v>46093</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>46094</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>46052</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29712,7 +29712,7 @@
         <v>45726</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29785,7 +29785,7 @@
         <v>45392</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29858,7 +29858,7 @@
         <v>45189</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29931,7 +29931,7 @@
         <v>45943</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>46098</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30077,7 +30077,7 @@
         <v>45162</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30150,7 +30150,7 @@
         <v>45162</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30223,7 +30223,7 @@
         <v>45753</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30296,7 +30296,7 @@
         <v>46098</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30369,7 +30369,7 @@
         <v>46099</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30447,7 +30447,7 @@
         <v>46099</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30520,7 +30520,7 @@
         <v>45946</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30593,7 +30593,7 @@
         <v>46100</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30666,7 +30666,7 @@
         <v>45782</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30739,7 +30739,7 @@
         <v>45653</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30812,7 +30812,7 @@
         <v>45589</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>45947</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>46104</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31031,7 +31031,7 @@
         <v>45713</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>46104</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>45189</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>45952</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>46105</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31396,7 +31396,7 @@
         <v>45356</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31469,7 +31469,7 @@
         <v>45952</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>45461</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31620,7 +31620,7 @@
         <v>45951</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31693,7 +31693,7 @@
         <v>45957</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31771,7 +31771,7 @@
         <v>45034</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31844,7 +31844,7 @@
         <v>44956</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>45608</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>46119</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32063,7 +32063,7 @@
         <v>45960</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>45964</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>45964</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>45964</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>45964</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>45964</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>45964</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32584,7 +32584,7 @@
         <v>44469</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32657,7 +32657,7 @@
         <v>45964</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32735,7 +32735,7 @@
         <v>45964</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>45884</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32881,7 +32881,7 @@
         <v>46127</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>44998</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45950</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>46112</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33173,7 +33173,7 @@
         <v>46071</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>45950</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>45968</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33392,7 +33392,7 @@
         <v>45968</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33465,7 +33465,7 @@
         <v>44965</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33538,7 +33538,7 @@
         <v>44965</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>45813</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>45813</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>45684</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33830,7 +33830,7 @@
         <v>45971</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>45062</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>45974</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34049,7 +34049,7 @@
         <v>45974</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34122,7 +34122,7 @@
         <v>45768</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34195,7 +34195,7 @@
         <v>45974</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34268,7 +34268,7 @@
         <v>45974</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34341,7 +34341,7 @@
         <v>45974</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>45974</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34487,7 +34487,7 @@
         <v>45974</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>46127</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34633,7 +34633,7 @@
         <v>44571</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
         <v>45324</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34779,7 +34779,7 @@
         <v>45818</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34857,7 +34857,7 @@
         <v>46128</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34930,7 +34930,7 @@
         <v>45036</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35003,7 +35003,7 @@
         <v>45365</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35076,7 +35076,7 @@
         <v>45979</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35149,7 +35149,7 @@
         <v>45979</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35222,7 +35222,7 @@
         <v>45979</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>45979</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35368,7 +35368,7 @@
         <v>46134</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>45979</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35514,7 +35514,7 @@
         <v>45979</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35587,7 +35587,7 @@
         <v>45979</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35660,7 +35660,7 @@
         <v>45981</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35733,7 +35733,7 @@
         <v>45982</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35806,7 +35806,7 @@
         <v>45982</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35879,7 +35879,7 @@
         <v>45636</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35952,7 +35952,7 @@
         <v>45981</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36025,7 +36025,7 @@
         <v>46134</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36098,7 +36098,7 @@
         <v>45981</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36171,7 +36171,7 @@
         <v>45986</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36244,7 +36244,7 @@
         <v>44971</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36317,7 +36317,7 @@
         <v>45797</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36390,7 +36390,7 @@
         <v>45987</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36463,7 +36463,7 @@
         <v>45987</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36536,7 +36536,7 @@
         <v>45988</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>45988</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36682,7 +36682,7 @@
         <v>45960</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36755,7 +36755,7 @@
         <v>45180</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36828,7 +36828,7 @@
         <v>44826</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36921,7 +36921,7 @@
         <v>46136</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36994,7 +36994,7 @@
         <v>45645</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>45645</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>45994</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37213,7 +37213,7 @@
         <v>45876</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37286,7 +37286,7 @@
         <v>45771</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37359,7 +37359,7 @@
         <v>45959</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
         <v>45996</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37505,7 +37505,7 @@
         <v>45896</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37578,7 +37578,7 @@
         <v>46069</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>45425</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37724,7 +37724,7 @@
         <v>44769</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37797,7 +37797,7 @@
         <v>46107</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>45198</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>45909</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>45999</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38094,7 +38094,7 @@
         <v>45743</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>45999</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38240,7 +38240,7 @@
         <v>46000</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
         <v>45153</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>46001</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38459,7 +38459,7 @@
         <v>46002</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38532,7 +38532,7 @@
         <v>46000</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>46000</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44819</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>44608</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38824,7 +38824,7 @@
         <v>45040</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38897,7 +38897,7 @@
         <v>45943</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>45714</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>46140</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>45973</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>45821</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39262,7 +39262,7 @@
         <v>45819</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39335,7 +39335,7 @@
         <v>45476</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39408,7 +39408,7 @@
         <v>45685</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39481,7 +39481,7 @@
         <v>45685</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39554,7 +39554,7 @@
         <v>46008</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39627,7 +39627,7 @@
         <v>46008</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39700,7 +39700,7 @@
         <v>46007</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39773,7 +39773,7 @@
         <v>46008</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>46008</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39919,7 +39919,7 @@
         <v>45875</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39992,7 +39992,7 @@
         <v>45763</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40070,7 +40070,7 @@
         <v>46007</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40143,7 +40143,7 @@
         <v>46008</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40216,7 +40216,7 @@
         <v>46008</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         <v>46008</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40362,7 +40362,7 @@
         <v>45008</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40435,7 +40435,7 @@
         <v>46009</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40508,7 +40508,7 @@
         <v>44855</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>46009</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40654,7 +40654,7 @@
         <v>46009</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40727,7 +40727,7 @@
         <v>46009</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40800,7 +40800,7 @@
         <v>46009</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>45660</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40946,7 +40946,7 @@
         <v>45544</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41019,7 +41019,7 @@
         <v>45483</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>44830</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41165,7 +41165,7 @@
         <v>45813</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41238,7 +41238,7 @@
         <v>45729</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41311,7 +41311,7 @@
         <v>44865</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>45750</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41457,7 +41457,7 @@
         <v>46029</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>45685</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41603,7 +41603,7 @@
         <v>45841</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>46064</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>45733</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41822,7 +41822,7 @@
         <v>46084</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41895,7 +41895,7 @@
         <v>45959</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41968,7 +41968,7 @@
         <v>45173</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>45825</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>45825</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42187,7 +42187,7 @@
         <v>45825</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42260,7 +42260,7 @@
         <v>45825</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>45825</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42406,7 +42406,7 @@
         <v>45825</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42479,7 +42479,7 @@
         <v>45672</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42552,7 +42552,7 @@
         <v>45825</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42625,7 +42625,7 @@
         <v>45825</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>45818</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42771,7 +42771,7 @@
         <v>45553</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42844,7 +42844,7 @@
         <v>46142</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>45502</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>45825</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43063,7 +43063,7 @@
         <v>45825</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43136,7 +43136,7 @@
         <v>45044</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43209,7 +43209,7 @@
         <v>45989</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43282,7 +43282,7 @@
         <v>45842</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43355,7 +43355,7 @@
         <v>45959</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43428,7 +43428,7 @@
         <v>45474</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43501,7 +43501,7 @@
         <v>45931</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43574,7 +43574,7 @@
         <v>45894</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43647,7 +43647,7 @@
         <v>45763</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43725,7 +43725,7 @@
         <v>45881</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43798,7 +43798,7 @@
         <v>45320</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43871,7 +43871,7 @@
         <v>45173</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43944,7 +43944,7 @@
         <v>45764</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44022,7 +44022,7 @@
         <v>44529</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44095,7 +44095,7 @@
         <v>46146</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44168,7 +44168,7 @@
         <v>46146</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44241,7 +44241,7 @@
         <v>46146</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>44978</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44387,7 +44387,7 @@
         <v>45832</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>46148</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44538,7 +44538,7 @@
         <v>46147</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44616,7 +44616,7 @@
         <v>46149</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44689,7 +44689,7 @@
         <v>44880</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>45833</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44835,7 +44835,7 @@
         <v>44943</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44913,7 +44913,7 @@
         <v>45833</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44991,7 +44991,7 @@
         <v>45834</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45069,7 +45069,7 @@
         <v>45120</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45142,7 +45142,7 @@
         <v>45190</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45215,7 +45215,7 @@
         <v>46153</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>45959</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45361,7 +45361,7 @@
         <v>44775</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45434,7 +45434,7 @@
         <v>44608</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45507,7 +45507,7 @@
         <v>46155</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45580,7 +45580,7 @@
         <v>45950</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45653,7 +45653,7 @@
         <v>46155</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45726,7 +45726,7 @@
         <v>45754</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45799,7 +45799,7 @@
         <v>45148</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45872,7 +45872,7 @@
         <v>46155</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45945,7 +45945,7 @@
         <v>45916</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46018,7 +46018,7 @@
         <v>46160</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46096,7 +46096,7 @@
         <v>46160</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46169,7 +46169,7 @@
         <v>45679</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46242,7 +46242,7 @@
         <v>45351</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46315,7 +46315,7 @@
         <v>46157</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46388,7 +46388,7 @@
         <v>45392</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46461,7 +46461,7 @@
         <v>45554</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46534,7 +46534,7 @@
         <v>45707</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46607,7 +46607,7 @@
         <v>45838</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46680,7 +46680,7 @@
         <v>46160</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46753,7 +46753,7 @@
         <v>45740</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>44915</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>45433</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46972,7 +46972,7 @@
         <v>45838</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>45947</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47123,7 +47123,7 @@
         <v>45947</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47196,7 +47196,7 @@
         <v>46098</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47269,7 +47269,7 @@
         <v>46047</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47342,7 +47342,7 @@
         <v>46161</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>45447</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>45840</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45840</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47644,7 +47644,7 @@
         <v>45840</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47717,7 +47717,7 @@
         <v>45842</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45947</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47863,7 +47863,7 @@
         <v>45841</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47936,7 +47936,7 @@
         <v>45841</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48009,7 +48009,7 @@
         <v>45726</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45728</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48155,7 +48155,7 @@
         <v>45841</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48233,7 +48233,7 @@
         <v>45957</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48306,7 +48306,7 @@
         <v>46064</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48379,7 +48379,7 @@
         <v>45841</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48457,7 +48457,7 @@
         <v>45959</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48530,7 +48530,7 @@
         <v>46164</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48603,7 +48603,7 @@
         <v>45034</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48676,7 +48676,7 @@
         <v>46164</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48749,7 +48749,7 @@
         <v>46163</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48822,7 +48822,7 @@
         <v>46163</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>46164</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48968,7 +48968,7 @@
         <v>44965</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>45240</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49114,7 +49114,7 @@
         <v>45852</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49187,7 +49187,7 @@
         <v>45623</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49265,7 +49265,7 @@
         <v>46146</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49338,7 +49338,7 @@
         <v>44946</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>45952</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49484,7 +49484,7 @@
         <v>45981</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49557,7 +49557,7 @@
         <v>46168</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49630,7 +49630,7 @@
         <v>44956</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>44956</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49776,7 +49776,7 @@
         <v>46167</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49849,7 +49849,7 @@
         <v>45589</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49922,7 +49922,7 @@
         <v>45173</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49995,7 +49995,7 @@
         <v>45099</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50068,7 +50068,7 @@
         <v>44556</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50141,7 +50141,7 @@
         <v>45855</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50214,7 +50214,7 @@
         <v>46169</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50287,7 +50287,7 @@
         <v>46168</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45329</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50433,7 +50433,7 @@
         <v>45799</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50506,7 +50506,7 @@
         <v>45271</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50579,7 +50579,7 @@
         <v>45860</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50652,7 +50652,7 @@
         <v>45859</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50725,7 +50725,7 @@
         <v>45799</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50798,7 +50798,7 @@
         <v>44537</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50871,7 +50871,7 @@
         <v>44908</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50944,7 +50944,7 @@
         <v>46170</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51017,7 +51017,7 @@
         <v>45825</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51090,7 +51090,7 @@
         <v>46174</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51163,7 +51163,7 @@
         <v>45749</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51236,7 +51236,7 @@
         <v>45771</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>45294</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51382,7 +51382,7 @@
         <v>45345</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51460,7 +51460,7 @@
         <v>46174</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51533,7 +51533,7 @@
         <v>45519</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51606,7 +51606,7 @@
         <v>46174</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51679,7 +51679,7 @@
         <v>46174</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51752,7 +51752,7 @@
         <v>46174</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51825,7 +51825,7 @@
         <v>46177</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51898,7 +51898,7 @@
         <v>46176</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51971,7 +51971,7 @@
         <v>46176</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52044,7 +52044,7 @@
         <v>44613</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52122,7 +52122,7 @@
         <v>46181</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52200,7 +52200,7 @@
         <v>45034</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52273,7 +52273,7 @@
         <v>45744</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52351,7 +52351,7 @@
         <v>45062</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52424,7 +52424,7 @@
         <v>45247</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52497,7 +52497,7 @@
         <v>46181</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52570,7 +52570,7 @@
         <v>46181</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52643,7 +52643,7 @@
         <v>46181</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52716,7 +52716,7 @@
         <v>46181</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52789,7 +52789,7 @@
         <v>46181</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52862,7 +52862,7 @@
         <v>45546</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52935,7 +52935,7 @@
         <v>45034</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53008,7 +53008,7 @@
         <v>45182</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53081,7 +53081,7 @@
         <v>45874</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53154,7 +53154,7 @@
         <v>45874</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53227,7 +53227,7 @@
         <v>45236</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53300,7 +53300,7 @@
         <v>45588</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53373,7 +53373,7 @@
         <v>45588</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53446,7 +53446,7 @@
         <v>45588</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53519,7 +53519,7 @@
         <v>45873</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53592,7 +53592,7 @@
         <v>45034</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53665,7 +53665,7 @@
         <v>46188</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53738,7 +53738,7 @@
         <v>45454</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53811,7 +53811,7 @@
         <v>44610</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53884,7 +53884,7 @@
         <v>46188</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53962,7 +53962,7 @@
         <v>46188</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54035,7 +54035,7 @@
         <v>46190</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54108,7 +54108,7 @@
         <v>45874</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54181,7 +54181,7 @@
         <v>46190</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54254,7 +54254,7 @@
         <v>46190</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54327,7 +54327,7 @@
         <v>46190</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54400,7 +54400,7 @@
         <v>45008</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54473,7 +54473,7 @@
         <v>45876</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54546,7 +54546,7 @@
         <v>46195</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54619,7 +54619,7 @@
         <v>45764</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54697,7 +54697,7 @@
         <v>45875</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54770,7 +54770,7 @@
         <v>44998</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54843,7 +54843,7 @@
         <v>46195</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54916,7 +54916,7 @@
         <v>46195</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54989,7 +54989,7 @@
         <v>45162</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55062,7 +55062,7 @@
         <v>46199</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55135,7 +55135,7 @@
         <v>46198</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55208,7 +55208,7 @@
         <v>46199</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55281,7 +55281,7 @@
         <v>46198</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55354,7 +55354,7 @@
         <v>46198</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55427,7 +55427,7 @@
         <v>46199</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55500,7 +55500,7 @@
         <v>46034</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55573,7 +55573,7 @@
         <v>46198</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55646,7 +55646,7 @@
         <v>46198</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55719,7 +55719,7 @@
         <v>45881</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55792,7 +55792,7 @@
         <v>45881</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55865,7 +55865,7 @@
         <v>44564</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55938,7 +55938,7 @@
         <v>46204</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56011,7 +56011,7 @@
         <v>45883</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56084,7 +56084,7 @@
         <v>46205</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56157,7 +56157,7 @@
         <v>45726</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56230,7 +56230,7 @@
         <v>46251</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56308,7 +56308,7 @@
         <v>45623</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56381,7 +56381,7 @@
         <v>44606</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56454,7 +56454,7 @@
         <v>45764</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56527,7 +56527,7 @@
         <v>46251</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56600,7 +56600,7 @@
         <v>46251</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56673,7 +56673,7 @@
         <v>44813</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56746,7 +56746,7 @@
         <v>46209</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56819,7 +56819,7 @@
         <v>46209</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56892,7 +56892,7 @@
         <v>46209</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56965,7 +56965,7 @@
         <v>46253</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57038,7 +57038,7 @@
         <v>46253</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57111,7 +57111,7 @@
         <v>45202</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57184,7 +57184,7 @@
         <v>46210</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57257,7 +57257,7 @@
         <v>46254</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57335,7 +57335,7 @@
         <v>46254</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57413,7 +57413,7 @@
         <v>46253</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57486,7 +57486,7 @@
         <v>46210</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57559,7 +57559,7 @@
         <v>46256</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57632,7 +57632,7 @@
         <v>45729</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57705,7 +57705,7 @@
         <v>46256</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57778,7 +57778,7 @@
         <v>45232</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57851,7 +57851,7 @@
         <v>45366</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57924,7 +57924,7 @@
         <v>44573</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57997,7 +57997,7 @@
         <v>46258</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58075,7 +58075,7 @@
         <v>45758</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58148,7 +58148,7 @@
         <v>45237</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58221,7 +58221,7 @@
         <v>45707</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58294,7 +58294,7 @@
         <v>45161</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58367,7 +58367,7 @@
         <v>45724</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58440,7 +58440,7 @@
         <v>45763</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58518,7 +58518,7 @@
         <v>46262</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58591,7 +58591,7 @@
         <v>45302</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58664,7 +58664,7 @@
         <v>44739</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58737,7 +58737,7 @@
         <v>45280</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58810,7 +58810,7 @@
         <v>44792</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58883,7 +58883,7 @@
         <v>46265</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58961,7 +58961,7 @@
         <v>45279</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59034,7 +59034,7 @@
         <v>46265</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59107,7 +59107,7 @@
         <v>46265</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59185,7 +59185,7 @@
         <v>46265</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59263,7 +59263,7 @@
         <v>46140</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59336,7 +59336,7 @@
         <v>46265</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59414,7 +59414,7 @@
         <v>46265</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59487,7 +59487,7 @@
         <v>46265</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59565,7 +59565,7 @@
         <v>46164</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59638,7 +59638,7 @@
         <v>46266</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59711,7 +59711,7 @@
         <v>46262</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59784,7 +59784,7 @@
         <v>46266</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59857,7 +59857,7 @@
         <v>45327</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59930,7 +59930,7 @@
         <v>46253</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60008,7 +60008,7 @@
         <v>46268</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60081,7 +60081,7 @@
         <v>46224</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60159,7 +60159,7 @@
         <v>46267</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60232,7 +60232,7 @@
         <v>45770</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60310,7 +60310,7 @@
         <v>46254</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60383,7 +60383,7 @@
         <v>46254</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60456,7 +60456,7 @@
         <v>44804</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60529,7 +60529,7 @@
         <v>45336</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60602,7 +60602,7 @@
         <v>45684</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60675,7 +60675,7 @@
         <v>45680</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60748,7 +60748,7 @@
         <v>46225</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60821,7 +60821,7 @@
         <v>44803</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60894,7 +60894,7 @@
         <v>46253</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60972,7 +60972,7 @@
         <v>46266</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61045,7 +61045,7 @@
         <v>45512</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61123,7 +61123,7 @@
         <v>46266</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         <v>45294</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61269,7 +61269,7 @@
         <v>45323</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61342,7 +61342,7 @@
         <v>45763</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61420,7 +61420,7 @@
         <v>45763</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61498,7 +61498,7 @@
         <v>45365</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61571,7 +61571,7 @@
         <v>45365</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61644,7 +61644,7 @@
         <v>46262</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61717,7 +61717,7 @@
         <v>46273</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61790,7 +61790,7 @@
         <v>46273</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61863,7 +61863,7 @@
         <v>46274</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61941,7 +61941,7 @@
         <v>45712</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62014,7 +62014,7 @@
         <v>44782</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62087,7 +62087,7 @@
         <v>46274</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62160,7 +62160,7 @@
         <v>46120</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62233,7 +62233,7 @@
         <v>46232</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62306,7 +62306,7 @@
         <v>46036</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62379,7 +62379,7 @@
         <v>45541</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62452,7 +62452,7 @@
         <v>45163</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62530,7 +62530,7 @@
         <v>46237</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62603,7 +62603,7 @@
         <v>46280</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62676,7 +62676,7 @@
         <v>44854</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62749,7 +62749,7 @@
         <v>46237</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62822,7 +62822,7 @@
         <v>44540</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62895,7 +62895,7 @@
         <v>46280</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62968,7 +62968,7 @@
         <v>45328</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63041,7 +63041,7 @@
         <v>46238</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63114,7 +63114,7 @@
         <v>46238</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63187,7 +63187,7 @@
         <v>46281</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63260,7 +63260,7 @@
         <v>46240</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63333,7 +63333,7 @@
         <v>46239</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63406,7 +63406,7 @@
         <v>46239</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63479,7 +63479,7 @@
         <v>45273</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63552,7 +63552,7 @@
         <v>46281</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63625,7 +63625,7 @@
         <v>46238</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63698,7 +63698,7 @@
         <v>46239</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63771,7 +63771,7 @@
         <v>45418</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63844,7 +63844,7 @@
         <v>45300</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63917,7 +63917,7 @@
         <v>46284</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -63990,7 +63990,7 @@
         <v>46284</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64063,7 +64063,7 @@
         <v>44573</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64136,7 +64136,7 @@
         <v>45734</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64209,7 +64209,7 @@
         <v>45400</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64282,7 +64282,7 @@
         <v>44879</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64355,7 +64355,7 @@
         <v>46283</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64428,7 +64428,7 @@
         <v>46241</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64506,7 +64506,7 @@
         <v>46287</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64579,7 +64579,7 @@
         <v>46288</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64657,7 +64657,7 @@
         <v>46266</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64730,7 +64730,7 @@
         <v>44951</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64803,7 +64803,7 @@
         <v>44482</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64876,7 +64876,7 @@
         <v>46244</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -64949,7 +64949,7 @@
         <v>45561</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65022,7 +65022,7 @@
         <v>44727</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65095,7 +65095,7 @@
         <v>46287</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65168,7 +65168,7 @@
         <v>46287</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65241,7 +65241,7 @@
         <v>46244</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65314,7 +65314,7 @@
         <v>46247</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65392,7 +65392,7 @@
         <v>44788</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65465,7 +65465,7 @@
         <v>44860</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65538,7 +65538,7 @@
         <v>46289</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65611,7 +65611,7 @@
         <v>46248</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65684,7 +65684,7 @@
         <v>45419</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65757,7 +65757,7 @@
         <v>46248</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65835,7 +65835,7 @@
         <v>46268</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -65908,7 +65908,7 @@
         <v>45239</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -65981,7 +65981,7 @@
         <v>46287</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66054,7 +66054,7 @@
         <v>44897</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66127,7 +66127,7 @@
         <v>45232</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66205,7 +66205,7 @@
         <v>44883</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66278,7 +66278,7 @@
         <v>45282</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66351,7 +66351,7 @@
         <v>44750</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66424,7 +66424,7 @@
         <v>45678</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66497,7 +66497,7 @@
         <v>44574</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66570,7 +66570,7 @@
         <v>45757</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66648,7 +66648,7 @@
         <v>45034</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66721,7 +66721,7 @@
         <v>45000</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66799,7 +66799,7 @@
         <v>44774</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66872,7 +66872,7 @@
         <v>45085</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -66945,7 +66945,7 @@
         <v>44824</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67018,7 +67018,7 @@
         <v>44852</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67091,7 +67091,7 @@
         <v>44834</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67164,7 +67164,7 @@
         <v>45674</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67237,7 +67237,7 @@
         <v>44747</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67310,7 +67310,7 @@
         <v>45390</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67383,7 +67383,7 @@
         <v>45664</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67456,7 +67456,7 @@
         <v>45674</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67529,7 +67529,7 @@
         <v>45034</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67602,7 +67602,7 @@
         <v>45520</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67675,7 +67675,7 @@
         <v>45698</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67748,7 +67748,7 @@
         <v>45307</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67821,7 +67821,7 @@
         <v>44958</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -67894,7 +67894,7 @@
         <v>45534</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -67967,7 +67967,7 @@
         <v>45124</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68040,7 +68040,7 @@
         <v>45524</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68113,7 +68113,7 @@
         <v>45099</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68186,7 +68186,7 @@
         <v>45273</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68259,7 +68259,7 @@
         <v>45324</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68332,7 +68332,7 @@
         <v>45579</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68410,7 +68410,7 @@
         <v>45680</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68483,7 +68483,7 @@
         <v>45236</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68556,7 +68556,7 @@
         <v>44574</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68629,7 +68629,7 @@
         <v>45000</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68707,7 +68707,7 @@
         <v>45153</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68780,7 +68780,7 @@
         <v>45440</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -68853,7 +68853,7 @@
         <v>45271</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -68926,7 +68926,7 @@
         <v>45355</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -68999,7 +68999,7 @@
         <v>45475</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69072,7 +69072,7 @@
         <v>45278</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69145,7 +69145,7 @@
         <v>45644</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69218,7 +69218,7 @@
         <v>45265</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69291,7 +69291,7 @@
         <v>45638</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69364,7 +69364,7 @@
         <v>45754</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69437,7 +69437,7 @@
         <v>45433</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69510,7 +69510,7 @@
         <v>45776</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69588,7 +69588,7 @@
         <v>45782</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69661,7 +69661,7 @@
         <v>45281</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69734,7 +69734,7 @@
         <v>44834</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -69812,7 +69812,7 @@
         <v>45306</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -69885,7 +69885,7 @@
         <v>45408</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -69958,7 +69958,7 @@
         <v>45476</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70031,7 +70031,7 @@
         <v>45496</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70109,7 +70109,7 @@
         <v>45169</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70182,7 +70182,7 @@
         <v>45790</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70255,7 +70255,7 @@
         <v>45496</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70333,7 +70333,7 @@
         <v>45792</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70406,7 +70406,7 @@
         <v>45567</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70479,7 +70479,7 @@
         <v>45618</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70552,7 +70552,7 @@
         <v>45231</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70625,7 +70625,7 @@
         <v>45791</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70698,7 +70698,7 @@
         <v>44880</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -70771,7 +70771,7 @@
         <v>44971</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -70844,7 +70844,7 @@
         <v>44467</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -70917,7 +70917,7 @@
         <v>45751</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -70990,7 +70990,7 @@
         <v>45751</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71068,7 +71068,7 @@
         <v>45790</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71146,7 +71146,7 @@
         <v>46041</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71219,7 +71219,7 @@
         <v>46078</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71292,7 +71292,7 @@
         <v>46073</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71365,7 +71365,7 @@
         <v>46142</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>

--- a/Översikt KRAMFORS.xlsx
+++ b/Översikt KRAMFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45544</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>46183</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>46029</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45974</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>46003</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>46094</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>46197</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>45763</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>44810</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>46196</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>45831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>46287</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>45763</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>46044</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>46197</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>46241</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>46136</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45056</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>46002</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>45511</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>46203</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>45763</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>46181</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>46196</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>46136</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>45723</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>46265</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>44713</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>45973</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>45985</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>45818</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>45399</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>45974</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         <v>45785</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>45484</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44524</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>45356</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>45660</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>45733</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>45996</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>44629</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>45957</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>45959</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>45818</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>45985</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>45516</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>46195</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         <v>46258</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         <v>44813</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>45806</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>46046</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>45282</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>46036</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>45898</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         <v>45898</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>45468</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>45729</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>44967</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         <v>45511</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7398,7 +7398,7 @@
         <v>45840</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>46178</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>46254</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>45182</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>46273</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>45665</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>46241</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>46244</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>45114</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>45551</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>45786</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>45750</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>44803</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>45400</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>45114</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>46020</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>46021</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>46024</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>46030</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>46030</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>46048</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>45924</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>46071</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>45943</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>46098</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>44965</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>45979</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>45998</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>45670</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>45764</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>45645</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>45764</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
         <v>45156</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>46281</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>45636</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>45344</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44852</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>45243</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
         <v>45199</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         <v>45071</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>44817</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>44804</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>44634</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11931,7 +11931,7 @@
         <v>44859</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>44469</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>44508</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>44508</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>44594</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>44608</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>44509</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>44496</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>44587</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>44511</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>44592</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>44592</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>44722</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>44688</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>44556</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         <v>44852</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>44508</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>44817</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>44817</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>44762</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>44859</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>44509</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>44581</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>44516</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13688,7 +13688,7 @@
         <v>44509</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>44539</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         <v>44566</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>44687</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         <v>44594</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>44719</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>44715</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>44484</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>44803</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>44629</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>44594</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>44802</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>44509</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>44540</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>44482</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>44465</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>44550</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44607</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>44628</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>44876</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>44616</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>44749</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>44697</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>44581</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>44503</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>44859</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15591,7 +15591,7 @@
         <v>44484</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         <v>44601</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>44782</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>44474</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>44581</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>44804</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>45205</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>45712</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>45513</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>44741</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>44840</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>45672</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
         <v>45572</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>45043</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>45721</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>45044</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>44853</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>45724</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>45365</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>45209</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>45225</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>45496</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         <v>45450</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         <v>45265</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17353,7 +17353,7 @@
         <v>44901</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         <v>45261</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         <v>44477</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>44907</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>45089</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>44880</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>45278</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>45771</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>45415</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>45099</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>45883</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>45450</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>45883</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18302,7 +18302,7 @@
         <v>46014</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>44466</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>44958</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>45418</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>46022</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>44804</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18740,7 +18740,7 @@
         <v>44894</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         <v>45552</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>46024</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>46024</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19032,7 +19032,7 @@
         <v>46024</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19105,7 +19105,7 @@
         <v>46024</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19178,7 +19178,7 @@
         <v>44503</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19251,7 +19251,7 @@
         <v>45273</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19324,7 +19324,7 @@
         <v>45328</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>46029</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>44942</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>45435</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         <v>45482</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45797</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>45797</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>45365</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         <v>44903</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>45798</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>45883</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>46031</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>45469</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>44519</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>46034</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>46031</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20512,7 +20512,7 @@
         <v>45888</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>44529</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>45645</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>45799</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>45616</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>45890</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20955,7 +20955,7 @@
         <v>45890</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21028,7 +21028,7 @@
         <v>45890</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>44536</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>45674</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>44574</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21325,7 +21325,7 @@
         <v>46042</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>44634</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
         <v>45632</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>46041</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         <v>46041</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>46041</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>45898</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>46043</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>45545</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>46043</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>46044</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>44909</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22201,7 +22201,7 @@
         <v>45538</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>45898</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>45898</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         <v>45898</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>46043</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22571,7 +22571,7 @@
         <v>46043</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22644,7 +22644,7 @@
         <v>46043</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>46044</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>45898</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>45898</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>45898</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>46043</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>46048</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>45901</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23233,7 +23233,7 @@
         <v>46046</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>45425</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>45898</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>45898</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>45901</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
         <v>45898</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
         <v>44503</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23749,7 +23749,7 @@
         <v>46046</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23822,7 +23822,7 @@
         <v>46046</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23895,7 +23895,7 @@
         <v>46047</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23968,7 +23968,7 @@
         <v>45901</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>46049</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24114,7 +24114,7 @@
         <v>45799</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24187,7 +24187,7 @@
         <v>44908</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         <v>46049</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>46049</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>45664</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24479,7 +24479,7 @@
         <v>45799</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>45909</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>45909</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24703,7 +24703,7 @@
         <v>46046</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24776,7 +24776,7 @@
         <v>45491</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>44959</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>45909</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25005,7 +25005,7 @@
         <v>44872</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>46054</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>46054</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
         <v>45420</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>46046</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25370,7 +25370,7 @@
         <v>46054</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>45912</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>44958</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>44958</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>45518</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>46062</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25813,7 +25813,7 @@
         <v>44991</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>45918</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>46063</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>46063</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>44629</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>44546</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>44956</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>46069</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26402,7 +26402,7 @@
         <v>45750</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>45750</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>45803</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>45036</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>44834</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>46069</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>45805</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>45805</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>46071</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>46043</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27137,7 +27137,7 @@
         <v>46072</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>45513</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27283,7 +27283,7 @@
         <v>46072</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>45320</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>46077</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>45475</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>45225</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>45926</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>45926</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>44888</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27872,7 +27872,7 @@
         <v>45552</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27945,7 +27945,7 @@
         <v>45526</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>44638</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28091,7 +28091,7 @@
         <v>45643</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28164,7 +28164,7 @@
         <v>45932</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>45712</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>45190</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>45734</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>45678</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28534,7 +28534,7 @@
         <v>45807</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>45935</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28690,7 +28690,7 @@
         <v>45593</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>45324</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>44894</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>45936</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28982,7 +28982,7 @@
         <v>45723</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29055,7 +29055,7 @@
         <v>45654</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29128,7 +29128,7 @@
         <v>45937</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29201,7 +29201,7 @@
         <v>45936</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29274,7 +29274,7 @@
         <v>45937</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>44916</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29420,7 +29420,7 @@
         <v>44949</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29493,7 +29493,7 @@
         <v>46093</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>46094</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>46052</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29712,7 +29712,7 @@
         <v>45726</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29785,7 +29785,7 @@
         <v>45392</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29858,7 +29858,7 @@
         <v>45189</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29931,7 +29931,7 @@
         <v>45943</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>46098</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30077,7 +30077,7 @@
         <v>45162</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30150,7 +30150,7 @@
         <v>45162</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30223,7 +30223,7 @@
         <v>45753</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30296,7 +30296,7 @@
         <v>46098</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30369,7 +30369,7 @@
         <v>46099</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30447,7 +30447,7 @@
         <v>46099</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30520,7 +30520,7 @@
         <v>45946</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30593,7 +30593,7 @@
         <v>46100</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30666,7 +30666,7 @@
         <v>45782</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30739,7 +30739,7 @@
         <v>45653</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30812,7 +30812,7 @@
         <v>45589</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>45947</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>46104</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31031,7 +31031,7 @@
         <v>45713</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>46104</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>45189</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>45952</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>46105</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31396,7 +31396,7 @@
         <v>45356</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31469,7 +31469,7 @@
         <v>45952</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>45461</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31620,7 +31620,7 @@
         <v>45951</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31693,7 +31693,7 @@
         <v>45957</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31771,7 +31771,7 @@
         <v>45034</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31844,7 +31844,7 @@
         <v>44956</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>45608</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>46119</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32063,7 +32063,7 @@
         <v>45960</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>45964</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>45964</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>45964</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>45964</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>45964</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>45964</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32584,7 +32584,7 @@
         <v>44469</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32657,7 +32657,7 @@
         <v>45964</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32735,7 +32735,7 @@
         <v>45964</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>45884</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32881,7 +32881,7 @@
         <v>46127</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>44998</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45950</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>46112</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33173,7 +33173,7 @@
         <v>46071</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>45950</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>45968</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33392,7 +33392,7 @@
         <v>45968</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33465,7 +33465,7 @@
         <v>44965</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33538,7 +33538,7 @@
         <v>44965</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>45813</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>45813</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>45684</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33830,7 +33830,7 @@
         <v>45971</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>45062</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>45974</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34049,7 +34049,7 @@
         <v>45974</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34122,7 +34122,7 @@
         <v>45768</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34195,7 +34195,7 @@
         <v>45974</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34268,7 +34268,7 @@
         <v>45974</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34341,7 +34341,7 @@
         <v>45974</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>45974</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34487,7 +34487,7 @@
         <v>45974</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>46127</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34633,7 +34633,7 @@
         <v>44571</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
         <v>45324</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34779,7 +34779,7 @@
         <v>45818</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34857,7 +34857,7 @@
         <v>46128</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34930,7 +34930,7 @@
         <v>45036</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35003,7 +35003,7 @@
         <v>45365</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35076,7 +35076,7 @@
         <v>45979</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35149,7 +35149,7 @@
         <v>45979</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35222,7 +35222,7 @@
         <v>45979</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>45979</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35368,7 +35368,7 @@
         <v>46134</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>45979</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35514,7 +35514,7 @@
         <v>45979</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35587,7 +35587,7 @@
         <v>45979</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35660,7 +35660,7 @@
         <v>45981</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35733,7 +35733,7 @@
         <v>45982</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35806,7 +35806,7 @@
         <v>45982</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35879,7 +35879,7 @@
         <v>45636</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35952,7 +35952,7 @@
         <v>45981</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36025,7 +36025,7 @@
         <v>46134</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36098,7 +36098,7 @@
         <v>45981</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36171,7 +36171,7 @@
         <v>45986</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36244,7 +36244,7 @@
         <v>44971</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36317,7 +36317,7 @@
         <v>45797</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36390,7 +36390,7 @@
         <v>45987</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36463,7 +36463,7 @@
         <v>45987</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36536,7 +36536,7 @@
         <v>45988</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>45988</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36682,7 +36682,7 @@
         <v>45960</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36755,7 +36755,7 @@
         <v>45180</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36828,7 +36828,7 @@
         <v>44826</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36921,7 +36921,7 @@
         <v>46136</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36994,7 +36994,7 @@
         <v>45645</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>45645</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>45994</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37213,7 +37213,7 @@
         <v>45876</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37286,7 +37286,7 @@
         <v>45771</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37359,7 +37359,7 @@
         <v>45959</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
         <v>45996</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37505,7 +37505,7 @@
         <v>45896</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37578,7 +37578,7 @@
         <v>46069</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>45425</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37724,7 +37724,7 @@
         <v>44769</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37797,7 +37797,7 @@
         <v>46107</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>45198</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>45909</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>45999</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38094,7 +38094,7 @@
         <v>45743</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>45999</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38240,7 +38240,7 @@
         <v>46000</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
         <v>45153</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>46001</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38459,7 +38459,7 @@
         <v>46002</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38532,7 +38532,7 @@
         <v>46000</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>46000</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44819</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>44608</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38824,7 +38824,7 @@
         <v>45040</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38897,7 +38897,7 @@
         <v>45943</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>45714</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>46140</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>45973</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>45821</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39262,7 +39262,7 @@
         <v>45819</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39335,7 +39335,7 @@
         <v>45476</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39408,7 +39408,7 @@
         <v>45685</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39481,7 +39481,7 @@
         <v>45685</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39554,7 +39554,7 @@
         <v>46008</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39627,7 +39627,7 @@
         <v>46008</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39700,7 +39700,7 @@
         <v>46007</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39773,7 +39773,7 @@
         <v>46008</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>46008</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39919,7 +39919,7 @@
         <v>45875</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39992,7 +39992,7 @@
         <v>45763</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40070,7 +40070,7 @@
         <v>46007</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40143,7 +40143,7 @@
         <v>46008</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40216,7 +40216,7 @@
         <v>46008</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         <v>46008</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40362,7 +40362,7 @@
         <v>45008</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40435,7 +40435,7 @@
         <v>46009</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40508,7 +40508,7 @@
         <v>44855</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>46009</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40654,7 +40654,7 @@
         <v>46009</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40727,7 +40727,7 @@
         <v>46009</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40800,7 +40800,7 @@
         <v>46009</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>45660</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40946,7 +40946,7 @@
         <v>45544</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41019,7 +41019,7 @@
         <v>45483</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>44830</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41165,7 +41165,7 @@
         <v>45813</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41238,7 +41238,7 @@
         <v>45729</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41311,7 +41311,7 @@
         <v>44865</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>45750</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41457,7 +41457,7 @@
         <v>46029</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>45685</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41603,7 +41603,7 @@
         <v>45841</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>46064</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>45733</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41822,7 +41822,7 @@
         <v>46084</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41895,7 +41895,7 @@
         <v>45959</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41968,7 +41968,7 @@
         <v>45173</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>45825</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>45825</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42187,7 +42187,7 @@
         <v>45825</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42260,7 +42260,7 @@
         <v>45825</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>45825</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42406,7 +42406,7 @@
         <v>45825</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42479,7 +42479,7 @@
         <v>45672</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42552,7 +42552,7 @@
         <v>45825</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42625,7 +42625,7 @@
         <v>45825</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>45818</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42771,7 +42771,7 @@
         <v>45553</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42844,7 +42844,7 @@
         <v>46142</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>45502</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>45825</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43063,7 +43063,7 @@
         <v>45825</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43136,7 +43136,7 @@
         <v>45044</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43209,7 +43209,7 @@
         <v>45989</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43282,7 +43282,7 @@
         <v>45842</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43355,7 +43355,7 @@
         <v>45959</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43428,7 +43428,7 @@
         <v>45474</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43501,7 +43501,7 @@
         <v>45931</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43574,7 +43574,7 @@
         <v>45894</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43647,7 +43647,7 @@
         <v>45763</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43725,7 +43725,7 @@
         <v>45881</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43798,7 +43798,7 @@
         <v>45320</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43871,7 +43871,7 @@
         <v>45173</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43944,7 +43944,7 @@
         <v>45764</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44022,7 +44022,7 @@
         <v>44529</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44095,7 +44095,7 @@
         <v>46146</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44168,7 +44168,7 @@
         <v>46146</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44241,7 +44241,7 @@
         <v>46146</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>44978</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44387,7 +44387,7 @@
         <v>45832</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>46148</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44538,7 +44538,7 @@
         <v>46147</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44616,7 +44616,7 @@
         <v>46149</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44689,7 +44689,7 @@
         <v>44880</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>45833</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44835,7 +44835,7 @@
         <v>44943</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44913,7 +44913,7 @@
         <v>45833</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44991,7 +44991,7 @@
         <v>45834</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45069,7 +45069,7 @@
         <v>45120</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45142,7 +45142,7 @@
         <v>45190</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45215,7 +45215,7 @@
         <v>46153</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>45959</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45361,7 +45361,7 @@
         <v>44775</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45434,7 +45434,7 @@
         <v>44608</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45507,7 +45507,7 @@
         <v>46155</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45580,7 +45580,7 @@
         <v>45950</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45653,7 +45653,7 @@
         <v>46155</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45726,7 +45726,7 @@
         <v>45754</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45799,7 +45799,7 @@
         <v>45148</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45872,7 +45872,7 @@
         <v>46155</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45945,7 +45945,7 @@
         <v>45916</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46018,7 +46018,7 @@
         <v>46160</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46096,7 +46096,7 @@
         <v>46160</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46169,7 +46169,7 @@
         <v>45679</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46242,7 +46242,7 @@
         <v>45351</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46315,7 +46315,7 @@
         <v>46157</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46388,7 +46388,7 @@
         <v>45392</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46461,7 +46461,7 @@
         <v>45554</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46534,7 +46534,7 @@
         <v>45707</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46607,7 +46607,7 @@
         <v>45838</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46680,7 +46680,7 @@
         <v>46160</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46753,7 +46753,7 @@
         <v>45740</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>44915</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>45433</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46972,7 +46972,7 @@
         <v>45838</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>45947</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47123,7 +47123,7 @@
         <v>45947</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47196,7 +47196,7 @@
         <v>46098</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47269,7 +47269,7 @@
         <v>46047</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47342,7 +47342,7 @@
         <v>46161</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>45447</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>45840</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45840</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47644,7 +47644,7 @@
         <v>45840</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47717,7 +47717,7 @@
         <v>45842</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45947</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47863,7 +47863,7 @@
         <v>45841</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47936,7 +47936,7 @@
         <v>45841</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48009,7 +48009,7 @@
         <v>45726</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45728</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48155,7 +48155,7 @@
         <v>45841</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48233,7 +48233,7 @@
         <v>45957</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48306,7 +48306,7 @@
         <v>46064</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48379,7 +48379,7 @@
         <v>45841</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48457,7 +48457,7 @@
         <v>45959</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48530,7 +48530,7 @@
         <v>46164</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48603,7 +48603,7 @@
         <v>45034</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48676,7 +48676,7 @@
         <v>46164</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48749,7 +48749,7 @@
         <v>46163</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48822,7 +48822,7 @@
         <v>46163</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>46164</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48968,7 +48968,7 @@
         <v>44965</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>45240</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49114,7 +49114,7 @@
         <v>45852</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49187,7 +49187,7 @@
         <v>45623</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49265,7 +49265,7 @@
         <v>46146</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49338,7 +49338,7 @@
         <v>44946</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>45952</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49484,7 +49484,7 @@
         <v>45981</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49557,7 +49557,7 @@
         <v>46168</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49630,7 +49630,7 @@
         <v>44956</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>44956</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49776,7 +49776,7 @@
         <v>46167</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49849,7 +49849,7 @@
         <v>45589</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49922,7 +49922,7 @@
         <v>45173</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49995,7 +49995,7 @@
         <v>45099</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50068,7 +50068,7 @@
         <v>44556</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50141,7 +50141,7 @@
         <v>45855</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50214,7 +50214,7 @@
         <v>46169</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50287,7 +50287,7 @@
         <v>46168</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45329</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50433,7 +50433,7 @@
         <v>45799</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50506,7 +50506,7 @@
         <v>45271</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50579,7 +50579,7 @@
         <v>45860</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50652,7 +50652,7 @@
         <v>45859</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50725,7 +50725,7 @@
         <v>45799</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50798,7 +50798,7 @@
         <v>44537</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50871,7 +50871,7 @@
         <v>44908</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50944,7 +50944,7 @@
         <v>46170</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51017,7 +51017,7 @@
         <v>45825</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51090,7 +51090,7 @@
         <v>46174</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51163,7 +51163,7 @@
         <v>45749</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51236,7 +51236,7 @@
         <v>45771</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>45294</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51382,7 +51382,7 @@
         <v>45345</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51460,7 +51460,7 @@
         <v>46174</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51533,7 +51533,7 @@
         <v>45519</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51606,7 +51606,7 @@
         <v>46174</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51679,7 +51679,7 @@
         <v>46174</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51752,7 +51752,7 @@
         <v>46174</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51825,7 +51825,7 @@
         <v>46177</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51898,7 +51898,7 @@
         <v>46176</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51971,7 +51971,7 @@
         <v>46176</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52044,7 +52044,7 @@
         <v>44613</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52122,7 +52122,7 @@
         <v>46181</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52200,7 +52200,7 @@
         <v>45034</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52273,7 +52273,7 @@
         <v>45744</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52351,7 +52351,7 @@
         <v>45062</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52424,7 +52424,7 @@
         <v>45247</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52497,7 +52497,7 @@
         <v>46181</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52570,7 +52570,7 @@
         <v>46181</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52643,7 +52643,7 @@
         <v>46181</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52716,7 +52716,7 @@
         <v>46181</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52789,7 +52789,7 @@
         <v>46181</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52862,7 +52862,7 @@
         <v>45546</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52935,7 +52935,7 @@
         <v>45034</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53008,7 +53008,7 @@
         <v>45182</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53081,7 +53081,7 @@
         <v>45874</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53154,7 +53154,7 @@
         <v>45874</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53227,7 +53227,7 @@
         <v>45236</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53300,7 +53300,7 @@
         <v>45588</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53373,7 +53373,7 @@
         <v>45588</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53446,7 +53446,7 @@
         <v>45588</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53519,7 +53519,7 @@
         <v>45873</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53592,7 +53592,7 @@
         <v>45034</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53665,7 +53665,7 @@
         <v>46188</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53738,7 +53738,7 @@
         <v>45454</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53811,7 +53811,7 @@
         <v>44610</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53884,7 +53884,7 @@
         <v>46188</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53962,7 +53962,7 @@
         <v>46188</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54035,7 +54035,7 @@
         <v>46190</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54108,7 +54108,7 @@
         <v>45874</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54181,7 +54181,7 @@
         <v>46190</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54254,7 +54254,7 @@
         <v>46190</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54327,7 +54327,7 @@
         <v>46190</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54400,7 +54400,7 @@
         <v>45008</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54473,7 +54473,7 @@
         <v>45876</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54546,7 +54546,7 @@
         <v>46195</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54619,7 +54619,7 @@
         <v>45764</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54697,7 +54697,7 @@
         <v>45875</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54770,7 +54770,7 @@
         <v>44998</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54843,7 +54843,7 @@
         <v>46195</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54916,7 +54916,7 @@
         <v>46195</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54989,7 +54989,7 @@
         <v>45162</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55062,7 +55062,7 @@
         <v>46199</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55135,7 +55135,7 @@
         <v>46198</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55208,7 +55208,7 @@
         <v>46199</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55281,7 +55281,7 @@
         <v>46198</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55354,7 +55354,7 @@
         <v>46198</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55427,7 +55427,7 @@
         <v>46199</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55500,7 +55500,7 @@
         <v>46034</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55573,7 +55573,7 @@
         <v>46198</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55646,7 +55646,7 @@
         <v>46198</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55719,7 +55719,7 @@
         <v>45881</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55792,7 +55792,7 @@
         <v>45881</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55865,7 +55865,7 @@
         <v>44564</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55938,7 +55938,7 @@
         <v>46204</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56011,7 +56011,7 @@
         <v>45883</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56084,7 +56084,7 @@
         <v>46205</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56157,7 +56157,7 @@
         <v>45726</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56230,7 +56230,7 @@
         <v>46251</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56308,7 +56308,7 @@
         <v>45623</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56381,7 +56381,7 @@
         <v>44606</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56454,7 +56454,7 @@
         <v>45764</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56527,7 +56527,7 @@
         <v>46251</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56600,7 +56600,7 @@
         <v>46251</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56673,7 +56673,7 @@
         <v>44813</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56746,7 +56746,7 @@
         <v>46209</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56819,7 +56819,7 @@
         <v>46209</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56892,7 +56892,7 @@
         <v>46209</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56965,7 +56965,7 @@
         <v>46253</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57038,7 +57038,7 @@
         <v>46253</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57111,7 +57111,7 @@
         <v>45202</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57184,7 +57184,7 @@
         <v>46210</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57257,7 +57257,7 @@
         <v>46254</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57335,7 +57335,7 @@
         <v>46254</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57413,7 +57413,7 @@
         <v>46253</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57486,7 +57486,7 @@
         <v>46210</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57559,7 +57559,7 @@
         <v>46256</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57632,7 +57632,7 @@
         <v>45729</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57705,7 +57705,7 @@
         <v>46256</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57778,7 +57778,7 @@
         <v>45232</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57851,7 +57851,7 @@
         <v>45366</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57924,7 +57924,7 @@
         <v>44573</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57997,7 +57997,7 @@
         <v>46258</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58075,7 +58075,7 @@
         <v>45758</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58148,7 +58148,7 @@
         <v>45237</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58221,7 +58221,7 @@
         <v>45707</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58294,7 +58294,7 @@
         <v>45161</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58367,7 +58367,7 @@
         <v>45724</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58440,7 +58440,7 @@
         <v>45763</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58518,7 +58518,7 @@
         <v>46262</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58591,7 +58591,7 @@
         <v>45302</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58664,7 +58664,7 @@
         <v>44739</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58737,7 +58737,7 @@
         <v>45280</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58810,7 +58810,7 @@
         <v>44792</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58883,7 +58883,7 @@
         <v>46265</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58961,7 +58961,7 @@
         <v>45279</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59034,7 +59034,7 @@
         <v>46265</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59107,7 +59107,7 @@
         <v>46265</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59185,7 +59185,7 @@
         <v>46265</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59263,7 +59263,7 @@
         <v>46140</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59336,7 +59336,7 @@
         <v>46265</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59414,7 +59414,7 @@
         <v>46265</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59487,7 +59487,7 @@
         <v>46265</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59565,7 +59565,7 @@
         <v>46164</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59638,7 +59638,7 @@
         <v>46266</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59711,7 +59711,7 @@
         <v>46262</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59784,7 +59784,7 @@
         <v>46266</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59857,7 +59857,7 @@
         <v>45327</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59930,7 +59930,7 @@
         <v>46253</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60008,7 +60008,7 @@
         <v>46268</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60081,7 +60081,7 @@
         <v>46224</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60159,7 +60159,7 @@
         <v>46267</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60232,7 +60232,7 @@
         <v>45770</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60310,7 +60310,7 @@
         <v>46254</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60383,7 +60383,7 @@
         <v>46254</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60456,7 +60456,7 @@
         <v>44804</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60529,7 +60529,7 @@
         <v>45336</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60602,7 +60602,7 @@
         <v>45684</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60675,7 +60675,7 @@
         <v>45680</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60748,7 +60748,7 @@
         <v>46225</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60821,7 +60821,7 @@
         <v>44803</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60894,7 +60894,7 @@
         <v>46253</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60972,7 +60972,7 @@
         <v>46266</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61045,7 +61045,7 @@
         <v>45512</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61123,7 +61123,7 @@
         <v>46266</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         <v>45294</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61269,7 +61269,7 @@
         <v>45323</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61342,7 +61342,7 @@
         <v>45763</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61420,7 +61420,7 @@
         <v>45763</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61498,7 +61498,7 @@
         <v>45365</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61571,7 +61571,7 @@
         <v>45365</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61644,7 +61644,7 @@
         <v>46262</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61717,7 +61717,7 @@
         <v>46273</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61790,7 +61790,7 @@
         <v>46273</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61863,7 +61863,7 @@
         <v>46274</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61941,7 +61941,7 @@
         <v>45712</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62014,7 +62014,7 @@
         <v>44782</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62087,7 +62087,7 @@
         <v>46274</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62160,7 +62160,7 @@
         <v>46120</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62233,7 +62233,7 @@
         <v>46232</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62306,7 +62306,7 @@
         <v>46036</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62379,7 +62379,7 @@
         <v>45541</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62452,7 +62452,7 @@
         <v>45163</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62530,7 +62530,7 @@
         <v>46237</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62603,7 +62603,7 @@
         <v>46280</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62676,7 +62676,7 @@
         <v>44854</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62749,7 +62749,7 @@
         <v>46237</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62822,7 +62822,7 @@
         <v>44540</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62895,7 +62895,7 @@
         <v>46280</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62968,7 +62968,7 @@
         <v>45328</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63041,7 +63041,7 @@
         <v>46238</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63114,7 +63114,7 @@
         <v>46238</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63187,7 +63187,7 @@
         <v>46281</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63260,7 +63260,7 @@
         <v>46240</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63333,7 +63333,7 @@
         <v>46239</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63406,7 +63406,7 @@
         <v>46239</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63479,7 +63479,7 @@
         <v>45273</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63552,7 +63552,7 @@
         <v>46281</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63625,7 +63625,7 @@
         <v>46238</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63698,7 +63698,7 @@
         <v>46239</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63771,7 +63771,7 @@
         <v>45418</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63844,7 +63844,7 @@
         <v>45300</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63917,7 +63917,7 @@
         <v>46284</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -63990,7 +63990,7 @@
         <v>46284</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64063,7 +64063,7 @@
         <v>44573</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64136,7 +64136,7 @@
         <v>45734</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64209,7 +64209,7 @@
         <v>45400</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64282,7 +64282,7 @@
         <v>44879</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64355,7 +64355,7 @@
         <v>46283</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64428,7 +64428,7 @@
         <v>46241</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64506,7 +64506,7 @@
         <v>46287</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64579,7 +64579,7 @@
         <v>46288</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64657,7 +64657,7 @@
         <v>46266</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64730,7 +64730,7 @@
         <v>44951</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64803,7 +64803,7 @@
         <v>44482</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64876,7 +64876,7 @@
         <v>46244</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -64949,7 +64949,7 @@
         <v>45561</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65022,7 +65022,7 @@
         <v>44727</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65095,7 +65095,7 @@
         <v>46287</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65168,7 +65168,7 @@
         <v>46287</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65241,7 +65241,7 @@
         <v>46244</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65314,7 +65314,7 @@
         <v>46247</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65392,7 +65392,7 @@
         <v>44788</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65465,7 +65465,7 @@
         <v>44860</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65538,7 +65538,7 @@
         <v>46289</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65611,7 +65611,7 @@
         <v>46248</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65684,7 +65684,7 @@
         <v>45419</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65757,7 +65757,7 @@
         <v>46248</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65835,7 +65835,7 @@
         <v>46268</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -65908,7 +65908,7 @@
         <v>45239</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -65981,7 +65981,7 @@
         <v>46287</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66054,7 +66054,7 @@
         <v>44897</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66127,7 +66127,7 @@
         <v>45232</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66205,7 +66205,7 @@
         <v>44883</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66278,7 +66278,7 @@
         <v>45282</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66351,7 +66351,7 @@
         <v>44750</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66424,7 +66424,7 @@
         <v>45678</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66497,7 +66497,7 @@
         <v>44574</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66570,7 +66570,7 @@
         <v>45757</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66648,7 +66648,7 @@
         <v>45034</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66721,7 +66721,7 @@
         <v>45000</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66799,7 +66799,7 @@
         <v>44774</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66872,7 +66872,7 @@
         <v>45085</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -66945,7 +66945,7 @@
         <v>44824</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67018,7 +67018,7 @@
         <v>44852</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67091,7 +67091,7 @@
         <v>44834</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67164,7 +67164,7 @@
         <v>45674</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67237,7 +67237,7 @@
         <v>44747</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67310,7 +67310,7 @@
         <v>45390</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67383,7 +67383,7 @@
         <v>45664</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67456,7 +67456,7 @@
         <v>45674</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67529,7 +67529,7 @@
         <v>45034</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67602,7 +67602,7 @@
         <v>45520</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67675,7 +67675,7 @@
         <v>45698</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67748,7 +67748,7 @@
         <v>45307</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67821,7 +67821,7 @@
         <v>44958</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -67894,7 +67894,7 @@
         <v>45534</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -67967,7 +67967,7 @@
         <v>45124</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68040,7 +68040,7 @@
         <v>45524</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68113,7 +68113,7 @@
         <v>45099</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68186,7 +68186,7 @@
         <v>45273</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68259,7 +68259,7 @@
         <v>45324</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68332,7 +68332,7 @@
         <v>45579</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68410,7 +68410,7 @@
         <v>45680</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68483,7 +68483,7 @@
         <v>45236</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68556,7 +68556,7 @@
         <v>44574</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68629,7 +68629,7 @@
         <v>45000</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68707,7 +68707,7 @@
         <v>45153</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68780,7 +68780,7 @@
         <v>45440</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -68853,7 +68853,7 @@
         <v>45271</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -68926,7 +68926,7 @@
         <v>45355</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -68999,7 +68999,7 @@
         <v>45475</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69072,7 +69072,7 @@
         <v>45278</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69145,7 +69145,7 @@
         <v>45644</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69218,7 +69218,7 @@
         <v>45265</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69291,7 +69291,7 @@
         <v>45638</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69364,7 +69364,7 @@
         <v>45754</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69437,7 +69437,7 @@
         <v>45433</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69510,7 +69510,7 @@
         <v>45776</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69588,7 +69588,7 @@
         <v>45782</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69661,7 +69661,7 @@
         <v>45281</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69734,7 +69734,7 @@
         <v>44834</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -69812,7 +69812,7 @@
         <v>45306</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -69885,7 +69885,7 @@
         <v>45408</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -69958,7 +69958,7 @@
         <v>45476</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70031,7 +70031,7 @@
         <v>45496</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70109,7 +70109,7 @@
         <v>45169</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70182,7 +70182,7 @@
         <v>45790</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70255,7 +70255,7 @@
         <v>45496</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70333,7 +70333,7 @@
         <v>45792</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70406,7 +70406,7 @@
         <v>45567</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70479,7 +70479,7 @@
         <v>45618</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70552,7 +70552,7 @@
         <v>45231</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70625,7 +70625,7 @@
         <v>45791</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70698,7 +70698,7 @@
         <v>44880</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -70771,7 +70771,7 @@
         <v>44971</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -70844,7 +70844,7 @@
         <v>44467</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -70917,7 +70917,7 @@
         <v>45751</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -70990,7 +70990,7 @@
         <v>45751</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71068,7 +71068,7 @@
         <v>45790</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71146,7 +71146,7 @@
         <v>46041</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71219,7 +71219,7 @@
         <v>46078</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71292,7 +71292,7 @@
         <v>46073</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71365,7 +71365,7 @@
         <v>46142</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>

--- a/Översikt KRAMFORS.xlsx
+++ b/Översikt KRAMFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45544</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>46183</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>46029</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>46003</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>46094</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>46197</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>45763</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>44810</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45831</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>46196</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>46287</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>45763</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>46197</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>46044</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>46241</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>46136</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>45056</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>46002</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>46203</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>45763</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>46181</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>45511</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>46196</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>46136</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45723</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>46265</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>44713</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>45484</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>45973</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>45818</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>45985</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>45399</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>45785</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>44524</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>45356</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>45660</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>45733</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>45996</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>44629</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>45957</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>45959</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>45818</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>45985</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>45516</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>46195</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>45282</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>46258</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>44813</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>46046</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>45806</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>45551</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>45786</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>45898</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>45898</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>46036</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>45468</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>45729</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>45840</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>46178</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>45511</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>45114</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>46273</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>45665</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>46241</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>46244</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>45182</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>46254</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>45750</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>45156</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>45645</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>45344</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>46020</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>46021</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>46024</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>46030</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>46030</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>46048</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>45924</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>45943</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>46071</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>46098</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>45979</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>45764</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>44965</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>45998</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>44852</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>45199</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
         <v>45670</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>44803</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>46281</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>45636</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>45764</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>45243</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>45114</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>45400</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>45071</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>44817</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>44804</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>44634</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>44859</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11653,7 +11653,7 @@
         <v>44508</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>44508</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>44594</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11872,7 +11872,7 @@
         <v>44608</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11945,7 +11945,7 @@
         <v>44509</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>44496</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>44587</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>44511</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>44592</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>44592</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>44722</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>44688</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>44556</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>44852</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>44508</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44817</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>44817</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>44509</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>44762</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>44859</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>44581</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>44516</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>44509</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
         <v>44539</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
         <v>44566</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>44687</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>44594</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>44719</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>44715</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>44484</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>44803</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>44629</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13994,7 +13994,7 @@
         <v>44802</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
         <v>44594</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>44509</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>44540</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         <v>44482</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>44550</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>44607</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>44876</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>44628</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>44616</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>44749</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>44697</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>44581</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>44503</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>44859</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>44601</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>44484</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>44782</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>44474</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>44581</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>44804</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>44958</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>44610</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>44482</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>45365</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>45534</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>45440</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>44978</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>45279</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>45588</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>45588</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>45588</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>44608</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>44634</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>45124</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>45205</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>44629</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>44991</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>45664</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>45721</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         <v>44573</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>44958</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>45307</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>45281</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>45148</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
         <v>45190</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>44830</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17440,7 +17440,7 @@
         <v>45265</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>45000</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>45306</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
         <v>45329</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>46002</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17810,7 +17810,7 @@
         <v>45327</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>45791</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>46007</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>45712</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>45526</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>46007</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>46009</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>46008</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>46009</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>45099</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>45225</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>46008</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>46009</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>46008</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>46008</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>46008</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>46008</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>46008</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>46009</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>45518</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>46009</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>45724</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>45496</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>46014</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>45616</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>45483</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>45888</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>45890</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>45890</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>46022</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>45890</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>45674</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>46024</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>46024</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>46024</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>46024</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>45232</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>45231</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>45790</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>46029</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>46031</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>46031</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45898</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45169</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>45901</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45898</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>45898</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         <v>45618</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>45898</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>45901</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>45898</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>45901</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>45898</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>45898</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>45567</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>45898</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>46034</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21981,7 +21981,7 @@
         <v>45898</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         <v>45898</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>44958</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>45482</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>46041</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>46041</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>46041</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>45351</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>45909</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>44909</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>45792</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>45909</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>45909</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>46043</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23008,7 +23008,7 @@
         <v>46043</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         <v>44792</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>46043</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>46043</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>45418</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>45415</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>46042</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         <v>46043</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23592,7 +23592,7 @@
         <v>44503</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>44804</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>45435</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>45797</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>46044</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45552</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>45912</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>45797</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>46044</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>46049</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>46048</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>46049</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>46046</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>45798</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>46049</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24707,7 +24707,7 @@
         <v>45512</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         <v>46043</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>46046</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45799</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>46046</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>46047</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>45799</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>45918</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>44903</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>45799</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>45475</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>44834</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>45036</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25676,7 +25676,7 @@
         <v>45805</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25749,7 +25749,7 @@
         <v>45805</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25822,7 +25822,7 @@
         <v>45643</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>45491</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>45807</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>46054</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>46046</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>45726</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>46054</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>46054</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>45202</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>46046</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>45225</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>45926</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>45926</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>45734</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         <v>45754</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>45654</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>46063</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>46063</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27146,7 +27146,7 @@
         <v>45323</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>45712</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>46062</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>45678</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
         <v>45469</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         <v>45932</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>46069</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>46069</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>45461</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>45935</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27891,7 +27891,7 @@
         <v>45936</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27964,7 +27964,7 @@
         <v>45937</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>45936</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28110,7 +28110,7 @@
         <v>46043</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>45937</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>46071</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28329,7 +28329,7 @@
         <v>45623</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>45623</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28480,7 +28480,7 @@
         <v>45943</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>46072</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>46072</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28699,7 +28699,7 @@
         <v>44879</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28772,7 +28772,7 @@
         <v>45345</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>46077</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
         <v>45946</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>45947</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>44606</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29142,7 +29142,7 @@
         <v>45294</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>45593</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29288,7 +29288,7 @@
         <v>45951</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29361,7 +29361,7 @@
         <v>44956</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>44946</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>45952</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         <v>45952</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29653,7 +29653,7 @@
         <v>45433</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>45813</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
         <v>45782</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>45813</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29945,7 +29945,7 @@
         <v>45957</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30023,7 +30023,7 @@
         <v>45653</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30096,7 +30096,7 @@
         <v>44546</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>45273</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>44998</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30315,7 +30315,7 @@
         <v>45753</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30388,7 +30388,7 @@
         <v>45034</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30461,7 +30461,7 @@
         <v>45085</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>44574</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>45960</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>45964</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>45964</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>45964</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30899,7 +30899,7 @@
         <v>45757</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>45964</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>45964</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31133,7 +31133,7 @@
         <v>45964</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>45964</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31284,7 +31284,7 @@
         <v>46094</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>45964</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>46093</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>44826</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31596,7 +31596,7 @@
         <v>45950</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>45768</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>45950</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31815,7 +31815,7 @@
         <v>45884</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>46052</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31961,7 +31961,7 @@
         <v>46098</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32034,7 +32034,7 @@
         <v>46098</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32107,7 +32107,7 @@
         <v>45968</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32180,7 +32180,7 @@
         <v>45000</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>45968</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>45153</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32404,7 +32404,7 @@
         <v>45153</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>45971</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>46099</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32628,7 +32628,7 @@
         <v>46099</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32701,7 +32701,7 @@
         <v>45273</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32774,7 +32774,7 @@
         <v>46100</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32847,7 +32847,7 @@
         <v>45974</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>45974</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32993,7 +32993,7 @@
         <v>45974</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33066,7 +33066,7 @@
         <v>46104</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33139,7 +33139,7 @@
         <v>45974</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33212,7 +33212,7 @@
         <v>44949</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33285,7 +33285,7 @@
         <v>45714</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33358,7 +33358,7 @@
         <v>45974</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>46104</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33504,7 +33504,7 @@
         <v>45974</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33577,7 +33577,7 @@
         <v>44908</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>45974</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33723,7 +33723,7 @@
         <v>46105</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33796,7 +33796,7 @@
         <v>45979</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33869,7 +33869,7 @@
         <v>45979</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33942,7 +33942,7 @@
         <v>45979</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34015,7 +34015,7 @@
         <v>45979</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34088,7 +34088,7 @@
         <v>45008</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34161,7 +34161,7 @@
         <v>45979</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>44503</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>45979</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34380,7 +34380,7 @@
         <v>45818</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>45979</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34531,7 +34531,7 @@
         <v>45685</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>45685</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>45819</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>45981</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>45981</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>45981</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34969,7 +34969,7 @@
         <v>45036</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>45982</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>45982</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>44894</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35261,7 +35261,7 @@
         <v>45986</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35334,7 +35334,7 @@
         <v>45987</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35407,7 +35407,7 @@
         <v>45987</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>45825</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>45825</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35626,7 +35626,7 @@
         <v>45988</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>45988</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>45825</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>45825</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>45825</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>45825</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36064,7 +36064,7 @@
         <v>45825</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36137,7 +36137,7 @@
         <v>46119</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36210,7 +36210,7 @@
         <v>45825</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>45825</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>45825</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>44942</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36502,7 +36502,7 @@
         <v>44965</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36575,7 +36575,7 @@
         <v>44965</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>45707</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>46071</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36794,7 +36794,7 @@
         <v>45994</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>45324</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36940,7 +36940,7 @@
         <v>46127</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>46128</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>45999</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37159,7 +37159,7 @@
         <v>45999</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37232,7 +37232,7 @@
         <v>46112</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37305,7 +37305,7 @@
         <v>45959</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37378,7 +37378,7 @@
         <v>45996</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>46127</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37524,7 +37524,7 @@
         <v>45684</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37597,7 +37597,7 @@
         <v>46000</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37670,7 +37670,7 @@
         <v>46000</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37743,7 +37743,7 @@
         <v>46000</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37816,7 +37816,7 @@
         <v>46001</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37889,7 +37889,7 @@
         <v>45754</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37962,7 +37962,7 @@
         <v>45833</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38040,7 +38040,7 @@
         <v>45832</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38113,7 +38113,7 @@
         <v>45524</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38186,7 +38186,7 @@
         <v>45833</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>45247</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38332,7 +38332,7 @@
         <v>45589</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38405,7 +38405,7 @@
         <v>46134</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>46134</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38551,7 +38551,7 @@
         <v>45834</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38629,7 +38629,7 @@
         <v>45008</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>45726</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>45454</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38848,7 +38848,7 @@
         <v>45838</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38921,7 +38921,7 @@
         <v>45636</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38994,7 +38994,7 @@
         <v>45838</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>44574</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>45043</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39218,7 +39218,7 @@
         <v>45841</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>45840</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39374,7 +39374,7 @@
         <v>45841</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39452,7 +39452,7 @@
         <v>45840</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39525,7 +39525,7 @@
         <v>45840</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>45841</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         <v>45841</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39749,7 +39749,7 @@
         <v>45733</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39822,7 +39822,7 @@
         <v>45842</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>45943</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>45554</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>45425</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>45729</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40187,7 +40187,7 @@
         <v>44727</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40260,7 +40260,7 @@
         <v>45475</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>46029</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40406,7 +40406,7 @@
         <v>46136</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40479,7 +40479,7 @@
         <v>45062</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>45513</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40625,7 +40625,7 @@
         <v>45852</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40698,7 +40698,7 @@
         <v>45797</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40771,7 +40771,7 @@
         <v>46069</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40844,7 +40844,7 @@
         <v>45959</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40917,7 +40917,7 @@
         <v>44840</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40990,7 +40990,7 @@
         <v>45855</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41063,7 +41063,7 @@
         <v>44852</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41136,7 +41136,7 @@
         <v>44519</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41209,7 +41209,7 @@
         <v>45282</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>45280</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>45698</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41428,7 +41428,7 @@
         <v>45644</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41501,7 +41501,7 @@
         <v>45973</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41574,7 +41574,7 @@
         <v>45672</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41647,7 +41647,7 @@
         <v>45960</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41720,7 +41720,7 @@
         <v>45821</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41793,7 +41793,7 @@
         <v>45909</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41866,7 +41866,7 @@
         <v>44782</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>44943</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42017,7 +42017,7 @@
         <v>45799</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42090,7 +42090,7 @@
         <v>45278</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42163,7 +42163,7 @@
         <v>45859</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42236,7 +42236,7 @@
         <v>45841</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>45881</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42382,7 +42382,7 @@
         <v>45744</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>45894</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42533,7 +42533,7 @@
         <v>45860</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42606,7 +42606,7 @@
         <v>45799</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>46107</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45418</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42825,7 +42825,7 @@
         <v>45771</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42898,7 +42898,7 @@
         <v>45685</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42971,7 +42971,7 @@
         <v>45989</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43044,7 +43044,7 @@
         <v>45190</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>45749</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>45825</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43263,7 +43263,7 @@
         <v>44883</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>45959</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43409,7 +43409,7 @@
         <v>45544</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>46084</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43555,7 +43555,7 @@
         <v>44774</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43628,7 +43628,7 @@
         <v>45876</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>45842</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>45541</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43847,7 +43847,7 @@
         <v>45355</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>46064</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43993,7 +43993,7 @@
         <v>44855</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44066,7 +44066,7 @@
         <v>45875</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44139,7 +44139,7 @@
         <v>45931</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>45173</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>45818</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44358,7 +44358,7 @@
         <v>44747</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44431,7 +44431,7 @@
         <v>45896</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44504,7 +44504,7 @@
         <v>45813</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44577,7 +44577,7 @@
         <v>45553</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44650,7 +44650,7 @@
         <v>46140</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44723,7 +44723,7 @@
         <v>46142</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>45638</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>46147</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>46146</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45020,7 +45020,7 @@
         <v>45873</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>46146</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>46148</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>45672</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>45740</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45390,7 +45390,7 @@
         <v>45680</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         <v>45674</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>45120</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45609,7 +45609,7 @@
         <v>44956</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45682,7 +45682,7 @@
         <v>44956</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>44897</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>46153</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45950</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>45743</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>45261</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46120,7 +46120,7 @@
         <v>45294</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>46155</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>45561</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46339,7 +46339,7 @@
         <v>45959</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>44834</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>46155</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         <v>46155</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46631,7 +46631,7 @@
         <v>45750</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>45320</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46777,7 +46777,7 @@
         <v>46157</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46850,7 +46850,7 @@
         <v>45433</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46923,7 +46923,7 @@
         <v>44803</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46996,7 +46996,7 @@
         <v>45392</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47069,7 +47069,7 @@
         <v>46098</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>46160</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47215,7 +47215,7 @@
         <v>46064</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
         <v>45947</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47361,7 +47361,7 @@
         <v>45947</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47434,7 +47434,7 @@
         <v>45679</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47507,7 +47507,7 @@
         <v>45875</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47580,7 +47580,7 @@
         <v>45874</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47653,7 +47653,7 @@
         <v>45707</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47726,7 +47726,7 @@
         <v>45959</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>46160</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47877,7 +47877,7 @@
         <v>46160</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47950,7 +47950,7 @@
         <v>45916</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45874</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48096,7 +48096,7 @@
         <v>45874</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48169,7 +48169,7 @@
         <v>46161</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48242,7 +48242,7 @@
         <v>45044</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48315,7 +48315,7 @@
         <v>45957</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48388,7 +48388,7 @@
         <v>45728</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>45947</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48534,7 +48534,7 @@
         <v>46163</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48607,7 +48607,7 @@
         <v>45496</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48685,7 +48685,7 @@
         <v>46047</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48758,7 +48758,7 @@
         <v>46163</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48831,7 +48831,7 @@
         <v>45758</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48904,7 +48904,7 @@
         <v>46164</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48977,7 +48977,7 @@
         <v>45876</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>46167</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>46164</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49196,7 +49196,7 @@
         <v>46164</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>44813</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49342,7 +49342,7 @@
         <v>45952</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49415,7 +49415,7 @@
         <v>46146</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49488,7 +49488,7 @@
         <v>45763</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>46168</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49639,7 +49639,7 @@
         <v>46169</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49712,7 +49712,7 @@
         <v>45328</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45173</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49863,7 +49863,7 @@
         <v>45881</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49936,7 +49936,7 @@
         <v>45764</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50009,7 +50009,7 @@
         <v>46168</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50082,7 +50082,7 @@
         <v>45981</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>45881</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50228,7 +50228,7 @@
         <v>46170</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50301,7 +50301,7 @@
         <v>45476</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50374,7 +50374,7 @@
         <v>44901</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50447,7 +50447,7 @@
         <v>44804</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50520,7 +50520,7 @@
         <v>45545</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50593,7 +50593,7 @@
         <v>46174</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50666,7 +50666,7 @@
         <v>46174</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50739,7 +50739,7 @@
         <v>46174</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50812,7 +50812,7 @@
         <v>46174</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50885,7 +50885,7 @@
         <v>45763</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50963,7 +50963,7 @@
         <v>45763</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51041,7 +51041,7 @@
         <v>45502</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51114,7 +51114,7 @@
         <v>46174</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51187,7 +51187,7 @@
         <v>44529</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>45883</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51333,7 +51333,7 @@
         <v>45883</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51406,7 +51406,7 @@
         <v>45883</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51479,7 +51479,7 @@
         <v>45883</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51552,7 +51552,7 @@
         <v>46176</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51625,7 +51625,7 @@
         <v>46176</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51698,7 +51698,7 @@
         <v>45336</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51771,7 +51771,7 @@
         <v>46177</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51844,7 +51844,7 @@
         <v>46181</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51917,7 +51917,7 @@
         <v>46181</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>46181</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52063,7 +52063,7 @@
         <v>46181</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52136,7 +52136,7 @@
         <v>46181</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52214,7 +52214,7 @@
         <v>46181</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52287,7 +52287,7 @@
         <v>44956</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52360,7 +52360,7 @@
         <v>44959</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52438,7 +52438,7 @@
         <v>46188</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>46188</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52584,7 +52584,7 @@
         <v>44915</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52657,7 +52657,7 @@
         <v>46188</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52735,7 +52735,7 @@
         <v>45278</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52808,7 +52808,7 @@
         <v>46190</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52881,7 +52881,7 @@
         <v>46190</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52954,7 +52954,7 @@
         <v>46190</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53027,7 +53027,7 @@
         <v>46190</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53100,7 +53100,7 @@
         <v>45552</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53173,7 +53173,7 @@
         <v>45771</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53246,7 +53246,7 @@
         <v>45771</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53319,7 +53319,7 @@
         <v>44739</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53392,7 +53392,7 @@
         <v>46195</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53465,7 +53465,7 @@
         <v>45034</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53538,7 +53538,7 @@
         <v>46195</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53611,7 +53611,7 @@
         <v>46195</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53684,7 +53684,7 @@
         <v>44872</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53757,7 +53757,7 @@
         <v>46198</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53830,7 +53830,7 @@
         <v>46198</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53903,7 +53903,7 @@
         <v>45474</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53976,7 +53976,7 @@
         <v>46198</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54049,7 +54049,7 @@
         <v>46198</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54122,7 +54122,7 @@
         <v>45546</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54195,7 +54195,7 @@
         <v>44775</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54268,7 +54268,7 @@
         <v>45300</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54341,7 +54341,7 @@
         <v>45608</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54414,7 +54414,7 @@
         <v>46199</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54487,7 +54487,7 @@
         <v>46199</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54560,7 +54560,7 @@
         <v>44529</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54633,7 +54633,7 @@
         <v>46034</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54706,7 +54706,7 @@
         <v>45712</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54779,7 +54779,7 @@
         <v>46199</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54852,7 +54852,7 @@
         <v>45034</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54925,7 +54925,7 @@
         <v>45040</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54998,7 +54998,7 @@
         <v>46204</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55071,7 +55071,7 @@
         <v>44741</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55144,7 +55144,7 @@
         <v>46205</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55217,7 +55217,7 @@
         <v>44894</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55290,7 +55290,7 @@
         <v>45265</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55363,7 +55363,7 @@
         <v>46209</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55436,7 +55436,7 @@
         <v>46209</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55509,7 +55509,7 @@
         <v>46209</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55582,7 +55582,7 @@
         <v>46210</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55655,7 +55655,7 @@
         <v>46210</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55728,7 +55728,7 @@
         <v>44571</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55801,7 +55801,7 @@
         <v>45034</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55874,7 +55874,7 @@
         <v>45664</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55947,7 +55947,7 @@
         <v>46256</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56020,7 +56020,7 @@
         <v>46256</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56093,7 +56093,7 @@
         <v>45572</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56166,7 +56166,7 @@
         <v>44556</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56239,7 +56239,7 @@
         <v>45182</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56312,7 +56312,7 @@
         <v>46258</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56390,7 +56390,7 @@
         <v>45161</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56463,7 +56463,7 @@
         <v>45302</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56536,7 +56536,7 @@
         <v>44916</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56609,7 +56609,7 @@
         <v>45425</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56687,7 +56687,7 @@
         <v>46265</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56765,7 +56765,7 @@
         <v>45763</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56843,7 +56843,7 @@
         <v>46265</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56921,7 +56921,7 @@
         <v>45044</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -56994,7 +56994,7 @@
         <v>46265</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57072,7 +57072,7 @@
         <v>46265</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57145,7 +57145,7 @@
         <v>45674</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57218,7 +57218,7 @@
         <v>46262</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57291,7 +57291,7 @@
         <v>46164</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57364,7 +57364,7 @@
         <v>46140</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57437,7 +57437,7 @@
         <v>46265</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57515,7 +57515,7 @@
         <v>46265</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57593,7 +57593,7 @@
         <v>46262</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57666,7 +57666,7 @@
         <v>45356</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57739,7 +57739,7 @@
         <v>44971</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57812,7 +57812,7 @@
         <v>45450</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57885,7 +57885,7 @@
         <v>45660</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -57958,7 +57958,7 @@
         <v>46266</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58031,7 +58031,7 @@
         <v>45173</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58104,7 +58104,7 @@
         <v>45770</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58182,7 +58182,7 @@
         <v>46265</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58255,7 +58255,7 @@
         <v>45419</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58328,7 +58328,7 @@
         <v>45729</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58401,7 +58401,7 @@
         <v>46267</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>46224</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58552,7 +58552,7 @@
         <v>46225</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58625,7 +58625,7 @@
         <v>46268</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58698,7 +58698,7 @@
         <v>45513</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58771,7 +58771,7 @@
         <v>45764</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58849,7 +58849,7 @@
         <v>45420</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -58922,7 +58922,7 @@
         <v>45632</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -58995,7 +58995,7 @@
         <v>45189</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59068,7 +59068,7 @@
         <v>44880</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         <v>46273</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59214,7 +59214,7 @@
         <v>46273</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45163</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59365,7 +59365,7 @@
         <v>46274</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59443,7 +59443,7 @@
         <v>46232</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59516,7 +59516,7 @@
         <v>46281</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59589,7 +59589,7 @@
         <v>44854</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59662,7 +59662,7 @@
         <v>44540</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59735,7 +59735,7 @@
         <v>46280</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59808,7 +59808,7 @@
         <v>46237</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59881,7 +59881,7 @@
         <v>46238</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>46238</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60027,7 +60027,7 @@
         <v>46280</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60100,7 +60100,7 @@
         <v>46238</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60173,7 +60173,7 @@
         <v>45239</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60246,7 +60246,7 @@
         <v>46237</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60319,7 +60319,7 @@
         <v>45645</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60392,7 +60392,7 @@
         <v>46281</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60465,7 +60465,7 @@
         <v>45579</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60543,7 +60543,7 @@
         <v>45538</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60616,7 +60616,7 @@
         <v>45450</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60689,7 +60689,7 @@
         <v>44769</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60762,7 +60762,7 @@
         <v>44965</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60835,7 +60835,7 @@
         <v>45724</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -60908,7 +60908,7 @@
         <v>46239</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -60981,7 +60981,7 @@
         <v>45365</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61054,7 +61054,7 @@
         <v>46240</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61127,7 +61127,7 @@
         <v>46239</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61200,7 +61200,7 @@
         <v>46283</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61273,7 +61273,7 @@
         <v>44888</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61346,7 +61346,7 @@
         <v>44908</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61419,7 +61419,7 @@
         <v>45365</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61492,7 +61492,7 @@
         <v>45034</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61565,7 +61565,7 @@
         <v>46266</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61638,7 +61638,7 @@
         <v>46287</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61711,7 +61711,7 @@
         <v>46284</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61784,7 +61784,7 @@
         <v>46284</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -61857,7 +61857,7 @@
         <v>46244</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>46241</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62008,7 +62008,7 @@
         <v>46244</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62081,7 +62081,7 @@
         <v>46287</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62154,7 +62154,7 @@
         <v>46287</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62227,7 +62227,7 @@
         <v>46288</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62305,7 +62305,7 @@
         <v>46287</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62378,7 +62378,7 @@
         <v>44536</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62456,7 +62456,7 @@
         <v>46289</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62529,7 +62529,7 @@
         <v>44613</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62607,7 +62607,7 @@
         <v>45750</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62680,7 +62680,7 @@
         <v>44608</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62753,7 +62753,7 @@
         <v>46248</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62826,7 +62826,7 @@
         <v>45764</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -62904,7 +62904,7 @@
         <v>46293</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -62977,7 +62977,7 @@
         <v>45726</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63050,7 +63050,7 @@
         <v>46247</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63128,7 +63128,7 @@
         <v>45803</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63201,7 +63201,7 @@
         <v>44880</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63274,7 +63274,7 @@
         <v>45589</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63347,7 +63347,7 @@
         <v>46248</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63425,7 +63425,7 @@
         <v>45034</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63498,7 +63498,7 @@
         <v>44477</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63571,7 +63571,7 @@
         <v>46120</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63644,7 +63644,7 @@
         <v>45365</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63717,7 +63717,7 @@
         <v>45089</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63790,7 +63790,7 @@
         <v>44853</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -63863,7 +63863,7 @@
         <v>46251</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -63936,7 +63936,7 @@
         <v>46251</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64009,7 +64009,7 @@
         <v>45366</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64082,7 +64082,7 @@
         <v>45684</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64155,7 +64155,7 @@
         <v>45680</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64228,7 +64228,7 @@
         <v>44865</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64301,7 +64301,7 @@
         <v>45390</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64374,7 +64374,7 @@
         <v>46251</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64452,7 +64452,7 @@
         <v>46266</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64525,7 +64525,7 @@
         <v>46254</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64603,7 +64603,7 @@
         <v>45324</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64676,7 +64676,7 @@
         <v>45447</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64749,7 +64749,7 @@
         <v>45236</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -64822,7 +64822,7 @@
         <v>44537</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -64895,7 +64895,7 @@
         <v>45723</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -64968,7 +64968,7 @@
         <v>46266</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65041,7 +65041,7 @@
         <v>46254</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65114,7 +65114,7 @@
         <v>45713</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65187,7 +65187,7 @@
         <v>45236</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65260,7 +65260,7 @@
         <v>46296</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65338,7 +65338,7 @@
         <v>45162</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65411,7 +65411,7 @@
         <v>45062</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65484,7 +65484,7 @@
         <v>45734</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65557,7 +65557,7 @@
         <v>44750</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65630,7 +65630,7 @@
         <v>45240</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65703,7 +65703,7 @@
         <v>46268</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -65776,7 +65776,7 @@
         <v>46036</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -65849,7 +65849,7 @@
         <v>44958</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -65922,7 +65922,7 @@
         <v>45678</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -65995,7 +65995,7 @@
         <v>46253</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66068,7 +66068,7 @@
         <v>46296</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66146,7 +66146,7 @@
         <v>46239</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66219,7 +66219,7 @@
         <v>46253</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66297,7 +66297,7 @@
         <v>46254</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66375,7 +66375,7 @@
         <v>46262</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66448,7 +66448,7 @@
         <v>46266</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66521,7 +66521,7 @@
         <v>46297</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66594,7 +66594,7 @@
         <v>46253</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66667,7 +66667,7 @@
         <v>46274</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66740,7 +66740,7 @@
         <v>46254</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -66813,7 +66813,7 @@
         <v>46253</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -66886,7 +66886,7 @@
         <v>46253</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -66964,7 +66964,7 @@
         <v>45189</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67037,7 +67037,7 @@
         <v>45392</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67110,7 +67110,7 @@
         <v>45237</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67183,7 +67183,7 @@
         <v>44907</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67256,7 +67256,7 @@
         <v>45198</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67334,7 +67334,7 @@
         <v>45324</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67407,7 +67407,7 @@
         <v>45209</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67480,7 +67480,7 @@
         <v>45162</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67553,7 +67553,7 @@
         <v>45162</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67626,7 +67626,7 @@
         <v>45520</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67699,7 +67699,7 @@
         <v>45271</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -67772,7 +67772,7 @@
         <v>44824</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -67845,7 +67845,7 @@
         <v>45320</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -67923,7 +67923,7 @@
         <v>44573</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -67996,7 +67996,7 @@
         <v>44574</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68069,7 +68069,7 @@
         <v>45273</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68142,7 +68142,7 @@
         <v>45519</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68215,7 +68215,7 @@
         <v>44819</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68288,7 +68288,7 @@
         <v>44638</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68361,7 +68361,7 @@
         <v>45763</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68439,7 +68439,7 @@
         <v>45099</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68512,7 +68512,7 @@
         <v>45365</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68585,7 +68585,7 @@
         <v>45180</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68658,7 +68658,7 @@
         <v>45400</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -68731,7 +68731,7 @@
         <v>44860</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -68804,7 +68804,7 @@
         <v>45099</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -68877,7 +68877,7 @@
         <v>45232</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -68955,7 +68955,7 @@
         <v>45271</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69028,7 +69028,7 @@
         <v>45328</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69101,7 +69101,7 @@
         <v>44788</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69174,7 +69174,7 @@
         <v>44564</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69247,7 +69247,7 @@
         <v>45034</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69320,7 +69320,7 @@
         <v>44998</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69393,7 +69393,7 @@
         <v>45645</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69466,7 +69466,7 @@
         <v>45645</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69539,7 +69539,7 @@
         <v>45776</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69617,7 +69617,7 @@
         <v>45782</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -69690,7 +69690,7 @@
         <v>45496</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -69768,7 +69768,7 @@
         <v>45408</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -69841,7 +69841,7 @@
         <v>45476</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -69914,7 +69914,7 @@
         <v>44834</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -69992,7 +69992,7 @@
         <v>44880</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70065,7 +70065,7 @@
         <v>44971</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70138,7 +70138,7 @@
         <v>45751</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70211,7 +70211,7 @@
         <v>45751</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70289,7 +70289,7 @@
         <v>45790</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70367,7 +70367,7 @@
         <v>46041</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70440,7 +70440,7 @@
         <v>46078</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70513,7 +70513,7 @@
         <v>46073</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70586,7 +70586,7 @@
         <v>46142</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>

--- a/Översikt KRAMFORS.xlsx
+++ b/Översikt KRAMFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45544</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>46183</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>46029</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>46003</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>46094</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>46197</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>45763</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>44810</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45831</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>46196</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>46287</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>45763</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>46197</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>46044</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>46241</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>46136</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>45056</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>46002</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>46203</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>45763</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>46181</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>45511</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>46196</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>46136</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45723</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>46265</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>44713</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>45484</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>45973</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>45818</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>45985</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>45399</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>45785</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>44524</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>45356</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>45660</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>45733</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>45996</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>44629</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>45957</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>45959</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>45818</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>45985</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>45516</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>46195</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>45282</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>46258</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>44813</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>46046</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>45806</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>45551</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>45786</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>45898</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>45898</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>46036</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>45468</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>45729</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>45840</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>46178</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>45511</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>45114</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>46273</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>45665</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>46241</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>46244</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>45182</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>46254</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>45750</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>45156</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>45645</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>45344</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>46020</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>46021</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>46024</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>46030</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>46030</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>46048</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>45924</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>45943</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>46071</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>46098</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>45979</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>45764</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>44965</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>45998</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>44852</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>45199</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
         <v>45670</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>44803</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>46281</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>45636</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>45764</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>45243</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>45114</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>45400</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>45071</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>44817</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>44804</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>44634</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>44859</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11653,7 +11653,7 @@
         <v>44508</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>44508</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>44594</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11872,7 +11872,7 @@
         <v>44608</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11945,7 +11945,7 @@
         <v>44509</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>44496</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>44587</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>44511</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>44592</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>44592</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>44722</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>44688</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>44556</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>44852</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>44508</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44817</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>44817</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>44509</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>44762</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>44859</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>44581</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>44516</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>44509</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
         <v>44539</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
         <v>44566</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>44687</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>44594</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>44719</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>44715</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>44484</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>44803</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>44629</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13994,7 +13994,7 @@
         <v>44802</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
         <v>44594</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>44509</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>44540</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         <v>44482</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>44550</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>44607</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>44876</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>44628</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>44616</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>44749</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>44697</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>44581</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>44503</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>44859</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>44601</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>44484</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>44782</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>44474</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>44581</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>44804</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>44958</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>44610</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>44482</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>45365</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>45534</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>45440</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>44978</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>45279</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>45588</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>45588</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>45588</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>44608</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>44634</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>45124</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>45205</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>44629</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>44991</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>45664</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>45721</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         <v>44573</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>44958</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>45307</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>45281</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>45148</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
         <v>45190</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>44830</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17440,7 +17440,7 @@
         <v>45265</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>45000</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>45306</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
         <v>45329</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>46002</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17810,7 +17810,7 @@
         <v>45327</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>45791</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>46007</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>45712</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>45526</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>46007</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>46009</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>46008</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>46009</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>45099</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>45225</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>46008</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>46009</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>46008</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>46008</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>46008</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>46008</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>46008</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>46009</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>45518</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>46009</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>45724</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>45496</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>46014</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>45616</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>45483</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>45888</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>45890</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>45890</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>46022</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>45890</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>45674</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>46024</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>46024</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>46024</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>46024</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>45232</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>45231</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>45790</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>46029</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>46031</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>46031</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45898</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45169</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>45901</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45898</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>45898</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         <v>45618</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>45898</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>45901</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>45898</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>45901</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>45898</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>45898</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>45567</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>45898</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>46034</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21981,7 +21981,7 @@
         <v>45898</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         <v>45898</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>44958</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>45482</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>46041</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>46041</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>46041</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>45351</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>45909</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>44909</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>45792</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>45909</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>45909</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>46043</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23008,7 +23008,7 @@
         <v>46043</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         <v>44792</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>46043</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>46043</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>45418</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>45415</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>46042</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         <v>46043</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23592,7 +23592,7 @@
         <v>44503</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>44804</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>45435</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>45797</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>46044</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45552</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>45912</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>45797</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>46044</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>46049</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>46048</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>46049</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>46046</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>45798</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>46049</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24707,7 +24707,7 @@
         <v>45512</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         <v>46043</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>46046</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45799</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>46046</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>46047</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>45799</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>45918</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>44903</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>45799</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>45475</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>44834</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>45036</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25676,7 +25676,7 @@
         <v>45805</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25749,7 +25749,7 @@
         <v>45805</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25822,7 +25822,7 @@
         <v>45643</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>45491</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>45807</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>46054</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>46046</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>45726</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>46054</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>46054</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>45202</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>46046</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>45225</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>45926</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>45926</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>45734</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         <v>45754</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>45654</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>46063</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>46063</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27146,7 +27146,7 @@
         <v>45323</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>45712</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>46062</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>45678</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
         <v>45469</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         <v>45932</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>46069</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>46069</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>45461</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>45935</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27891,7 +27891,7 @@
         <v>45936</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27964,7 +27964,7 @@
         <v>45937</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>45936</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28110,7 +28110,7 @@
         <v>46043</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>45937</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>46071</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28329,7 +28329,7 @@
         <v>45623</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>45623</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28480,7 +28480,7 @@
         <v>45943</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>46072</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>46072</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28699,7 +28699,7 @@
         <v>44879</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28772,7 +28772,7 @@
         <v>45345</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>46077</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
         <v>45946</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>45947</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>44606</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29142,7 +29142,7 @@
         <v>45294</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>45593</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29288,7 +29288,7 @@
         <v>45951</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29361,7 +29361,7 @@
         <v>44956</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>44946</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>45952</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         <v>45952</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29653,7 +29653,7 @@
         <v>45433</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>45813</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
         <v>45782</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>45813</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29945,7 +29945,7 @@
         <v>45957</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30023,7 +30023,7 @@
         <v>45653</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30096,7 +30096,7 @@
         <v>44546</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>45273</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>44998</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30315,7 +30315,7 @@
         <v>45753</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30388,7 +30388,7 @@
         <v>45034</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30461,7 +30461,7 @@
         <v>45085</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>44574</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>45960</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>45964</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>45964</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>45964</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30899,7 +30899,7 @@
         <v>45757</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>45964</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>45964</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31133,7 +31133,7 @@
         <v>45964</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>45964</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31284,7 +31284,7 @@
         <v>46094</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>45964</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>46093</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>44826</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31596,7 +31596,7 @@
         <v>45950</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>45768</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>45950</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31815,7 +31815,7 @@
         <v>45884</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>46052</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31961,7 +31961,7 @@
         <v>46098</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32034,7 +32034,7 @@
         <v>46098</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32107,7 +32107,7 @@
         <v>45968</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32180,7 +32180,7 @@
         <v>45000</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>45968</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>45153</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32404,7 +32404,7 @@
         <v>45153</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>45971</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>46099</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32628,7 +32628,7 @@
         <v>46099</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32701,7 +32701,7 @@
         <v>45273</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32774,7 +32774,7 @@
         <v>46100</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32847,7 +32847,7 @@
         <v>45974</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>45974</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32993,7 +32993,7 @@
         <v>45974</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33066,7 +33066,7 @@
         <v>46104</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33139,7 +33139,7 @@
         <v>45974</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33212,7 +33212,7 @@
         <v>44949</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33285,7 +33285,7 @@
         <v>45714</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33358,7 +33358,7 @@
         <v>45974</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>46104</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33504,7 +33504,7 @@
         <v>45974</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33577,7 +33577,7 @@
         <v>44908</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>45974</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33723,7 +33723,7 @@
         <v>46105</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33796,7 +33796,7 @@
         <v>45979</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33869,7 +33869,7 @@
         <v>45979</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33942,7 +33942,7 @@
         <v>45979</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34015,7 +34015,7 @@
         <v>45979</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34088,7 +34088,7 @@
         <v>45008</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34161,7 +34161,7 @@
         <v>45979</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>44503</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>45979</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34380,7 +34380,7 @@
         <v>45818</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>45979</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34531,7 +34531,7 @@
         <v>45685</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>45685</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>45819</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>45981</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>45981</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>45981</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34969,7 +34969,7 @@
         <v>45036</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>45982</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>45982</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>44894</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35261,7 +35261,7 @@
         <v>45986</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35334,7 +35334,7 @@
         <v>45987</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35407,7 +35407,7 @@
         <v>45987</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>45825</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>45825</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35626,7 +35626,7 @@
         <v>45988</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>45988</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>45825</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>45825</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>45825</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>45825</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36064,7 +36064,7 @@
         <v>45825</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36137,7 +36137,7 @@
         <v>46119</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36210,7 +36210,7 @@
         <v>45825</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>45825</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>45825</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>44942</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36502,7 +36502,7 @@
         <v>44965</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36575,7 +36575,7 @@
         <v>44965</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>45707</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>46071</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36794,7 +36794,7 @@
         <v>45994</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>45324</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36940,7 +36940,7 @@
         <v>46127</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>46128</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>45999</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37159,7 +37159,7 @@
         <v>45999</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37232,7 +37232,7 @@
         <v>46112</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37305,7 +37305,7 @@
         <v>45959</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37378,7 +37378,7 @@
         <v>45996</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>46127</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37524,7 +37524,7 @@
         <v>45684</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37597,7 +37597,7 @@
         <v>46000</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37670,7 +37670,7 @@
         <v>46000</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37743,7 +37743,7 @@
         <v>46000</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37816,7 +37816,7 @@
         <v>46001</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37889,7 +37889,7 @@
         <v>45754</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37962,7 +37962,7 @@
         <v>45833</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38040,7 +38040,7 @@
         <v>45832</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38113,7 +38113,7 @@
         <v>45524</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38186,7 +38186,7 @@
         <v>45833</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>45247</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38332,7 +38332,7 @@
         <v>45589</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38405,7 +38405,7 @@
         <v>46134</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>46134</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38551,7 +38551,7 @@
         <v>45834</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38629,7 +38629,7 @@
         <v>45008</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>45726</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>45454</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38848,7 +38848,7 @@
         <v>45838</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38921,7 +38921,7 @@
         <v>45636</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38994,7 +38994,7 @@
         <v>45838</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>44574</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>45043</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39218,7 +39218,7 @@
         <v>45841</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>45840</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39374,7 +39374,7 @@
         <v>45841</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39452,7 +39452,7 @@
         <v>45840</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39525,7 +39525,7 @@
         <v>45840</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>45841</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         <v>45841</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39749,7 +39749,7 @@
         <v>45733</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39822,7 +39822,7 @@
         <v>45842</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>45943</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>45554</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>45425</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>45729</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40187,7 +40187,7 @@
         <v>44727</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40260,7 +40260,7 @@
         <v>45475</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>46029</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40406,7 +40406,7 @@
         <v>46136</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40479,7 +40479,7 @@
         <v>45062</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>45513</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40625,7 +40625,7 @@
         <v>45852</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40698,7 +40698,7 @@
         <v>45797</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40771,7 +40771,7 @@
         <v>46069</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40844,7 +40844,7 @@
         <v>45959</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40917,7 +40917,7 @@
         <v>44840</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40990,7 +40990,7 @@
         <v>45855</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41063,7 +41063,7 @@
         <v>44852</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41136,7 +41136,7 @@
         <v>44519</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41209,7 +41209,7 @@
         <v>45282</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>45280</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>45698</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41428,7 +41428,7 @@
         <v>45644</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41501,7 +41501,7 @@
         <v>45973</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41574,7 +41574,7 @@
         <v>45672</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41647,7 +41647,7 @@
         <v>45960</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41720,7 +41720,7 @@
         <v>45821</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41793,7 +41793,7 @@
         <v>45909</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41866,7 +41866,7 @@
         <v>44782</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>44943</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42017,7 +42017,7 @@
         <v>45799</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42090,7 +42090,7 @@
         <v>45278</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42163,7 +42163,7 @@
         <v>45859</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42236,7 +42236,7 @@
         <v>45841</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>45881</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42382,7 +42382,7 @@
         <v>45744</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>45894</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42533,7 +42533,7 @@
         <v>45860</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42606,7 +42606,7 @@
         <v>45799</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>46107</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45418</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42825,7 +42825,7 @@
         <v>45771</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42898,7 +42898,7 @@
         <v>45685</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42971,7 +42971,7 @@
         <v>45989</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43044,7 +43044,7 @@
         <v>45190</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>45749</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>45825</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43263,7 +43263,7 @@
         <v>44883</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>45959</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43409,7 +43409,7 @@
         <v>45544</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>46084</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43555,7 +43555,7 @@
         <v>44774</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43628,7 +43628,7 @@
         <v>45876</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>45842</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>45541</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43847,7 +43847,7 @@
         <v>45355</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>46064</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43993,7 +43993,7 @@
         <v>44855</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44066,7 +44066,7 @@
         <v>45875</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44139,7 +44139,7 @@
         <v>45931</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>45173</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>45818</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44358,7 +44358,7 @@
         <v>44747</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44431,7 +44431,7 @@
         <v>45896</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44504,7 +44504,7 @@
         <v>45813</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44577,7 +44577,7 @@
         <v>45553</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44650,7 +44650,7 @@
         <v>46140</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44723,7 +44723,7 @@
         <v>46142</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>45638</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>46147</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>46146</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45020,7 +45020,7 @@
         <v>45873</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>46146</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>46148</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>45672</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>45740</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45390,7 +45390,7 @@
         <v>45680</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         <v>45674</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>45120</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45609,7 +45609,7 @@
         <v>44956</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45682,7 +45682,7 @@
         <v>44956</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>44897</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>46153</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45950</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>45743</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>45261</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46120,7 +46120,7 @@
         <v>45294</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>46155</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>45561</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46339,7 +46339,7 @@
         <v>45959</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>44834</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>46155</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         <v>46155</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46631,7 +46631,7 @@
         <v>45750</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>45320</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46777,7 +46777,7 @@
         <v>46157</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46850,7 +46850,7 @@
         <v>45433</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46923,7 +46923,7 @@
         <v>44803</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46996,7 +46996,7 @@
         <v>45392</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47069,7 +47069,7 @@
         <v>46098</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>46160</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47215,7 +47215,7 @@
         <v>46064</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
         <v>45947</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47361,7 +47361,7 @@
         <v>45947</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47434,7 +47434,7 @@
         <v>45679</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47507,7 +47507,7 @@
         <v>45875</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47580,7 +47580,7 @@
         <v>45874</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47653,7 +47653,7 @@
         <v>45707</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47726,7 +47726,7 @@
         <v>45959</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>46160</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47877,7 +47877,7 @@
         <v>46160</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47950,7 +47950,7 @@
         <v>45916</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45874</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48096,7 +48096,7 @@
         <v>45874</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48169,7 +48169,7 @@
         <v>46161</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48242,7 +48242,7 @@
         <v>45044</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48315,7 +48315,7 @@
         <v>45957</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48388,7 +48388,7 @@
         <v>45728</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>45947</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48534,7 +48534,7 @@
         <v>46163</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48607,7 +48607,7 @@
         <v>45496</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48685,7 +48685,7 @@
         <v>46047</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48758,7 +48758,7 @@
         <v>46163</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48831,7 +48831,7 @@
         <v>45758</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48904,7 +48904,7 @@
         <v>46164</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48977,7 +48977,7 @@
         <v>45876</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>46167</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>46164</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49196,7 +49196,7 @@
         <v>46164</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>44813</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49342,7 +49342,7 @@
         <v>45952</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49415,7 +49415,7 @@
         <v>46146</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49488,7 +49488,7 @@
         <v>45763</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>46168</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49639,7 +49639,7 @@
         <v>46169</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49712,7 +49712,7 @@
         <v>45328</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45173</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49863,7 +49863,7 @@
         <v>45881</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49936,7 +49936,7 @@
         <v>45764</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50009,7 +50009,7 @@
         <v>46168</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50082,7 +50082,7 @@
         <v>45981</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>45881</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50228,7 +50228,7 @@
         <v>46170</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50301,7 +50301,7 @@
         <v>45476</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50374,7 +50374,7 @@
         <v>44901</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50447,7 +50447,7 @@
         <v>44804</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50520,7 +50520,7 @@
         <v>45545</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50593,7 +50593,7 @@
         <v>46174</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50666,7 +50666,7 @@
         <v>46174</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50739,7 +50739,7 @@
         <v>46174</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50812,7 +50812,7 @@
         <v>46174</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50885,7 +50885,7 @@
         <v>45763</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50963,7 +50963,7 @@
         <v>45763</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51041,7 +51041,7 @@
         <v>45502</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51114,7 +51114,7 @@
         <v>46174</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51187,7 +51187,7 @@
         <v>44529</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>45883</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51333,7 +51333,7 @@
         <v>45883</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51406,7 +51406,7 @@
         <v>45883</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51479,7 +51479,7 @@
         <v>45883</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51552,7 +51552,7 @@
         <v>46176</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51625,7 +51625,7 @@
         <v>46176</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51698,7 +51698,7 @@
         <v>45336</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51771,7 +51771,7 @@
         <v>46177</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51844,7 +51844,7 @@
         <v>46181</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51917,7 +51917,7 @@
         <v>46181</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>46181</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52063,7 +52063,7 @@
         <v>46181</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52136,7 +52136,7 @@
         <v>46181</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52214,7 +52214,7 @@
         <v>46181</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52287,7 +52287,7 @@
         <v>44956</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52360,7 +52360,7 @@
         <v>44959</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52438,7 +52438,7 @@
         <v>46188</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>46188</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52584,7 +52584,7 @@
         <v>44915</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52657,7 +52657,7 @@
         <v>46188</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52735,7 +52735,7 @@
         <v>45278</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52808,7 +52808,7 @@
         <v>46190</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52881,7 +52881,7 @@
         <v>46190</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52954,7 +52954,7 @@
         <v>46190</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53027,7 +53027,7 @@
         <v>46190</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53100,7 +53100,7 @@
         <v>45552</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53173,7 +53173,7 @@
         <v>45771</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53246,7 +53246,7 @@
         <v>45771</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53319,7 +53319,7 @@
         <v>44739</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53392,7 +53392,7 @@
         <v>46195</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53465,7 +53465,7 @@
         <v>45034</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53538,7 +53538,7 @@
         <v>46195</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53611,7 +53611,7 @@
         <v>46195</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53684,7 +53684,7 @@
         <v>44872</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53757,7 +53757,7 @@
         <v>46198</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53830,7 +53830,7 @@
         <v>46198</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53903,7 +53903,7 @@
         <v>45474</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53976,7 +53976,7 @@
         <v>46198</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54049,7 +54049,7 @@
         <v>46198</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54122,7 +54122,7 @@
         <v>45546</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54195,7 +54195,7 @@
         <v>44775</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54268,7 +54268,7 @@
         <v>45300</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54341,7 +54341,7 @@
         <v>45608</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54414,7 +54414,7 @@
         <v>46199</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54487,7 +54487,7 @@
         <v>46199</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54560,7 +54560,7 @@
         <v>44529</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54633,7 +54633,7 @@
         <v>46034</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54706,7 +54706,7 @@
         <v>45712</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54779,7 +54779,7 @@
         <v>46199</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54852,7 +54852,7 @@
         <v>45034</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54925,7 +54925,7 @@
         <v>45040</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54998,7 +54998,7 @@
         <v>46204</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55071,7 +55071,7 @@
         <v>44741</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55144,7 +55144,7 @@
         <v>46205</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55217,7 +55217,7 @@
         <v>44894</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55290,7 +55290,7 @@
         <v>45265</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55363,7 +55363,7 @@
         <v>46209</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55436,7 +55436,7 @@
         <v>46209</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55509,7 +55509,7 @@
         <v>46209</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55582,7 +55582,7 @@
         <v>46210</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55655,7 +55655,7 @@
         <v>46210</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55728,7 +55728,7 @@
         <v>44571</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55801,7 +55801,7 @@
         <v>45034</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55874,7 +55874,7 @@
         <v>45664</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55947,7 +55947,7 @@
         <v>46256</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56020,7 +56020,7 @@
         <v>46256</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56093,7 +56093,7 @@
         <v>45572</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56166,7 +56166,7 @@
         <v>44556</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56239,7 +56239,7 @@
         <v>45182</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56312,7 +56312,7 @@
         <v>46258</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56390,7 +56390,7 @@
         <v>45161</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56463,7 +56463,7 @@
         <v>45302</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56536,7 +56536,7 @@
         <v>44916</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56609,7 +56609,7 @@
         <v>45425</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56687,7 +56687,7 @@
         <v>46265</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56765,7 +56765,7 @@
         <v>45763</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56843,7 +56843,7 @@
         <v>46265</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56921,7 +56921,7 @@
         <v>45044</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -56994,7 +56994,7 @@
         <v>46265</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57072,7 +57072,7 @@
         <v>46265</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57145,7 +57145,7 @@
         <v>45674</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57218,7 +57218,7 @@
         <v>46262</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57291,7 +57291,7 @@
         <v>46164</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57364,7 +57364,7 @@
         <v>46140</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57437,7 +57437,7 @@
         <v>46265</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57515,7 +57515,7 @@
         <v>46265</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57593,7 +57593,7 @@
         <v>46262</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57666,7 +57666,7 @@
         <v>45356</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57739,7 +57739,7 @@
         <v>44971</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57812,7 +57812,7 @@
         <v>45450</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57885,7 +57885,7 @@
         <v>45660</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -57958,7 +57958,7 @@
         <v>46266</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58031,7 +58031,7 @@
         <v>45173</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58104,7 +58104,7 @@
         <v>45770</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58182,7 +58182,7 @@
         <v>46265</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58255,7 +58255,7 @@
         <v>45419</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58328,7 +58328,7 @@
         <v>45729</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58401,7 +58401,7 @@
         <v>46267</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>46224</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58552,7 +58552,7 @@
         <v>46225</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58625,7 +58625,7 @@
         <v>46268</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58698,7 +58698,7 @@
         <v>45513</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58771,7 +58771,7 @@
         <v>45764</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58849,7 +58849,7 @@
         <v>45420</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -58922,7 +58922,7 @@
         <v>45632</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -58995,7 +58995,7 @@
         <v>45189</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59068,7 +59068,7 @@
         <v>44880</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         <v>46273</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59214,7 +59214,7 @@
         <v>46273</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45163</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59365,7 +59365,7 @@
         <v>46274</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59443,7 +59443,7 @@
         <v>46232</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59516,7 +59516,7 @@
         <v>46281</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59589,7 +59589,7 @@
         <v>44854</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59662,7 +59662,7 @@
         <v>44540</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59735,7 +59735,7 @@
         <v>46280</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59808,7 +59808,7 @@
         <v>46237</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59881,7 +59881,7 @@
         <v>46238</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>46238</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60027,7 +60027,7 @@
         <v>46280</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60100,7 +60100,7 @@
         <v>46238</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60173,7 +60173,7 @@
         <v>45239</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60246,7 +60246,7 @@
         <v>46237</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60319,7 +60319,7 @@
         <v>45645</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60392,7 +60392,7 @@
         <v>46281</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60465,7 +60465,7 @@
         <v>45579</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60543,7 +60543,7 @@
         <v>45538</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60616,7 +60616,7 @@
         <v>45450</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60689,7 +60689,7 @@
         <v>44769</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60762,7 +60762,7 @@
         <v>44965</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60835,7 +60835,7 @@
         <v>45724</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -60908,7 +60908,7 @@
         <v>46239</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -60981,7 +60981,7 @@
         <v>45365</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61054,7 +61054,7 @@
         <v>46240</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61127,7 +61127,7 @@
         <v>46239</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61200,7 +61200,7 @@
         <v>46283</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61273,7 +61273,7 @@
         <v>44888</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61346,7 +61346,7 @@
         <v>44908</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61419,7 +61419,7 @@
         <v>45365</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61492,7 +61492,7 @@
         <v>45034</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61565,7 +61565,7 @@
         <v>46266</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61638,7 +61638,7 @@
         <v>46287</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61711,7 +61711,7 @@
         <v>46284</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61784,7 +61784,7 @@
         <v>46284</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -61857,7 +61857,7 @@
         <v>46244</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>46241</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62008,7 +62008,7 @@
         <v>46244</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62081,7 +62081,7 @@
         <v>46287</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62154,7 +62154,7 @@
         <v>46287</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62227,7 +62227,7 @@
         <v>46288</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62305,7 +62305,7 @@
         <v>46287</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62378,7 +62378,7 @@
         <v>44536</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62456,7 +62456,7 @@
         <v>46289</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62529,7 +62529,7 @@
         <v>44613</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62607,7 +62607,7 @@
         <v>45750</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62680,7 +62680,7 @@
         <v>44608</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62753,7 +62753,7 @@
         <v>46248</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62826,7 +62826,7 @@
         <v>45764</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -62904,7 +62904,7 @@
         <v>46293</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -62977,7 +62977,7 @@
         <v>45726</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63050,7 +63050,7 @@
         <v>46247</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63128,7 +63128,7 @@
         <v>45803</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63201,7 +63201,7 @@
         <v>44880</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63274,7 +63274,7 @@
         <v>45589</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63347,7 +63347,7 @@
         <v>46248</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63425,7 +63425,7 @@
         <v>45034</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63498,7 +63498,7 @@
         <v>44477</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63571,7 +63571,7 @@
         <v>46120</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63644,7 +63644,7 @@
         <v>45365</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63717,7 +63717,7 @@
         <v>45089</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63790,7 +63790,7 @@
         <v>44853</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -63863,7 +63863,7 @@
         <v>46251</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -63936,7 +63936,7 @@
         <v>46251</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64009,7 +64009,7 @@
         <v>45366</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64082,7 +64082,7 @@
         <v>45684</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64155,7 +64155,7 @@
         <v>45680</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64228,7 +64228,7 @@
         <v>44865</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64301,7 +64301,7 @@
         <v>45390</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64374,7 +64374,7 @@
         <v>46251</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64452,7 +64452,7 @@
         <v>46266</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64525,7 +64525,7 @@
         <v>46254</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64603,7 +64603,7 @@
         <v>45324</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64676,7 +64676,7 @@
         <v>45447</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64749,7 +64749,7 @@
         <v>45236</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -64822,7 +64822,7 @@
         <v>44537</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -64895,7 +64895,7 @@
         <v>45723</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -64968,7 +64968,7 @@
         <v>46266</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65041,7 +65041,7 @@
         <v>46254</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65114,7 +65114,7 @@
         <v>45713</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65187,7 +65187,7 @@
         <v>45236</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65260,7 +65260,7 @@
         <v>46296</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65338,7 +65338,7 @@
         <v>45162</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65411,7 +65411,7 @@
         <v>45062</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65484,7 +65484,7 @@
         <v>45734</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65557,7 +65557,7 @@
         <v>44750</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65630,7 +65630,7 @@
         <v>45240</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65703,7 +65703,7 @@
         <v>46268</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -65776,7 +65776,7 @@
         <v>46036</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -65849,7 +65849,7 @@
         <v>44958</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -65922,7 +65922,7 @@
         <v>45678</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -65995,7 +65995,7 @@
         <v>46253</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66068,7 +66068,7 @@
         <v>46296</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66146,7 +66146,7 @@
         <v>46239</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66219,7 +66219,7 @@
         <v>46253</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66297,7 +66297,7 @@
         <v>46254</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66375,7 +66375,7 @@
         <v>46262</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66448,7 +66448,7 @@
         <v>46266</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66521,7 +66521,7 @@
         <v>46297</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66594,7 +66594,7 @@
         <v>46253</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66667,7 +66667,7 @@
         <v>46274</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66740,7 +66740,7 @@
         <v>46254</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -66813,7 +66813,7 @@
         <v>46253</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -66886,7 +66886,7 @@
         <v>46253</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -66964,7 +66964,7 @@
         <v>45189</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67037,7 +67037,7 @@
         <v>45392</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67110,7 +67110,7 @@
         <v>45237</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67183,7 +67183,7 @@
         <v>44907</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67256,7 +67256,7 @@
         <v>45198</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67334,7 +67334,7 @@
         <v>45324</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67407,7 +67407,7 @@
         <v>45209</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67480,7 +67480,7 @@
         <v>45162</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67553,7 +67553,7 @@
         <v>45162</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67626,7 +67626,7 @@
         <v>45520</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67699,7 +67699,7 @@
         <v>45271</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -67772,7 +67772,7 @@
         <v>44824</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -67845,7 +67845,7 @@
         <v>45320</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -67923,7 +67923,7 @@
         <v>44573</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -67996,7 +67996,7 @@
         <v>44574</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68069,7 +68069,7 @@
         <v>45273</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68142,7 +68142,7 @@
         <v>45519</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68215,7 +68215,7 @@
         <v>44819</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68288,7 +68288,7 @@
         <v>44638</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68361,7 +68361,7 @@
         <v>45763</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68439,7 +68439,7 @@
         <v>45099</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68512,7 +68512,7 @@
         <v>45365</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68585,7 +68585,7 @@
         <v>45180</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68658,7 +68658,7 @@
         <v>45400</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -68731,7 +68731,7 @@
         <v>44860</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -68804,7 +68804,7 @@
         <v>45099</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -68877,7 +68877,7 @@
         <v>45232</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -68955,7 +68955,7 @@
         <v>45271</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69028,7 +69028,7 @@
         <v>45328</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69101,7 +69101,7 @@
         <v>44788</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69174,7 +69174,7 @@
         <v>44564</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69247,7 +69247,7 @@
         <v>45034</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69320,7 +69320,7 @@
         <v>44998</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69393,7 +69393,7 @@
         <v>45645</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69466,7 +69466,7 @@
         <v>45645</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69539,7 +69539,7 @@
         <v>45776</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69617,7 +69617,7 @@
         <v>45782</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -69690,7 +69690,7 @@
         <v>45496</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -69768,7 +69768,7 @@
         <v>45408</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -69841,7 +69841,7 @@
         <v>45476</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -69914,7 +69914,7 @@
         <v>44834</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -69992,7 +69992,7 @@
         <v>44880</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70065,7 +70065,7 @@
         <v>44971</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70138,7 +70138,7 @@
         <v>45751</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70211,7 +70211,7 @@
         <v>45751</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70289,7 +70289,7 @@
         <v>45790</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70367,7 +70367,7 @@
         <v>46041</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70440,7 +70440,7 @@
         <v>46078</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70513,7 +70513,7 @@
         <v>46073</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70586,7 +70586,7 @@
         <v>46142</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>

--- a/Översikt KRAMFORS.xlsx
+++ b/Översikt KRAMFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45544</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>46183</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>46029</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>46003</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>46094</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>46197</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>45763</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>44810</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45831</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>46287</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>46196</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>45763</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>46044</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>46197</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>46241</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>45511</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>45056</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>46136</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>46002</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>46203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>45763</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>46181</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>46196</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>45723</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>46136</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>46265</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>44713</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>45399</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>45785</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>45484</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>45818</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>45973</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>45985</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>45660</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>44524</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>45356</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>45733</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>45996</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>44629</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>45818</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>45957</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>45959</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>44813</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>45985</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>45516</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>45282</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>46195</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>46046</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>45806</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>46258</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>45114</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>45898</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>45898</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>45551</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>45786</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>45468</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>45729</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>45840</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>45511</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>46036</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>46178</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>46273</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>45665</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>46241</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>46244</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>46254</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>45182</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>45750</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>45243</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>44803</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>45199</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>45400</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>45114</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>45924</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>45764</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>45645</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>45943</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>44965</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>45764</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>45979</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>45156</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>46098</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>45998</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>46020</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>46021</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>46024</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>46030</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>45344</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>44852</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>46048</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>45670</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>46071</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>46281</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         <v>45636</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>45071</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>44817</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>44804</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>44634</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>44859</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>44508</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>44508</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>44608</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>44509</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>44594</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>44496</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>44587</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>44511</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>44592</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>44592</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         <v>44722</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12352,7 +12352,7 @@
         <v>44688</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>44556</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12498,7 +12498,7 @@
         <v>44852</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         <v>44508</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>44817</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>44817</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>44762</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>44509</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>44859</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>44581</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>44516</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>44509</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>44539</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>44859</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>44581</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>44509</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>44540</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>44566</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>44482</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44550</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>44503</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>44687</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>44594</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>44484</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>44719</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>44607</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>44715</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>44601</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>44484</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>44803</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>44876</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>44628</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14693,7 +14693,7 @@
         <v>44782</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>44629</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44616</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>44594</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>44802</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>44749</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>44697</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>44581</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>45209</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>45225</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>45674</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         <v>44747</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>44804</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>44880</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>45496</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         <v>44943</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>45390</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>45664</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>45674</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>45190</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>44775</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>44608</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>45721</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>45034</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>45520</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>45698</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>45754</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>45148</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>45307</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>45205</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>45513</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>45351</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>45392</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>45554</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>44840</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>45672</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>45712</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>44741</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>44901</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>45740</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>44915</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45450</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>45265</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>45447</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>44958</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45572</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>45261</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>45726</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>45534</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>45124</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>45524</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>45099</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>45089</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>45034</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         <v>44853</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>45724</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>44880</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>44965</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>44907</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19015,7 +19015,7 @@
         <v>45043</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19088,7 +19088,7 @@
         <v>45044</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>45365</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>45240</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         <v>45623</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19385,7 +19385,7 @@
         <v>44946</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>45278</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19531,7 +19531,7 @@
         <v>45771</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>44956</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>44956</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>45589</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         <v>45883</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19896,7 +19896,7 @@
         <v>45273</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>45099</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>44556</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>45324</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>45579</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>45883</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         <v>45680</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>45883</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>45099</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20558,7 +20558,7 @@
         <v>45236</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>45450</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20704,7 +20704,7 @@
         <v>44958</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>44574</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>44894</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>45329</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>45883</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>45000</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45271</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>45888</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>45153</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>45273</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         <v>45328</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21517,7 +21517,7 @@
         <v>45440</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         <v>45616</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>44537</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>44942</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21809,7 +21809,7 @@
         <v>44908</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
         <v>45890</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>45771</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22028,7 +22028,7 @@
         <v>45294</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22101,7 +22101,7 @@
         <v>45890</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22174,7 +22174,7 @@
         <v>45345</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>45482</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>45271</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>45365</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>45355</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>45475</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>45519</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>45890</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>45674</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>45898</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>45898</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>45898</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         <v>45898</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>45898</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23211,7 +23211,7 @@
         <v>45469</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>44519</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>45278</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>45898</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>45898</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23576,7 +23576,7 @@
         <v>45901</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23649,7 +23649,7 @@
         <v>44529</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23722,7 +23722,7 @@
         <v>45644</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>45645</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23868,7 +23868,7 @@
         <v>45898</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>45898</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24014,7 +24014,7 @@
         <v>45901</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24087,7 +24087,7 @@
         <v>45265</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>45898</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>45901</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>44536</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>44574</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>45638</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>44634</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45632</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45754</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>45545</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>45433</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>44909</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45538</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>45909</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>45909</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>44613</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25265,7 +25265,7 @@
         <v>45909</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>45425</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>45776</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25494,7 +25494,7 @@
         <v>45034</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>45744</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>45062</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>44503</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>45247</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45912</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>44908</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>45782</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26088,7 +26088,7 @@
         <v>45546</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26161,7 +26161,7 @@
         <v>45664</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26234,7 +26234,7 @@
         <v>45034</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26307,7 +26307,7 @@
         <v>45182</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>45491</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>44959</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>44872</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26609,7 +26609,7 @@
         <v>45420</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>45236</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>45588</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26828,7 +26828,7 @@
         <v>45588</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26901,7 +26901,7 @@
         <v>45588</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26974,7 +26974,7 @@
         <v>44958</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>44958</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>45281</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27193,7 +27193,7 @@
         <v>44834</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>45306</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         <v>45518</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>45918</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         <v>45034</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>45408</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         <v>45476</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>45496</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>45454</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         <v>44991</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27938,7 +27938,7 @@
         <v>44610</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28011,7 +28011,7 @@
         <v>45169</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>44629</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28157,7 +28157,7 @@
         <v>44546</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>44956</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28303,7 +28303,7 @@
         <v>45790</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28376,7 +28376,7 @@
         <v>45750</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
         <v>45008</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>45496</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28600,7 +28600,7 @@
         <v>45764</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>44998</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28751,7 +28751,7 @@
         <v>45792</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>45513</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>45567</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>45320</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>45926</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>45926</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>45225</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>45618</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>45231</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>45162</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29486,7 +29486,7 @@
         <v>44888</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29559,7 +29559,7 @@
         <v>45552</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29632,7 +29632,7 @@
         <v>45791</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29705,7 +29705,7 @@
         <v>45415</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>45418</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>44804</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>45552</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>45526</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>44503</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30143,7 +30143,7 @@
         <v>44638</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30216,7 +30216,7 @@
         <v>45435</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30294,7 +30294,7 @@
         <v>45190</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>45797</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>45932</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>45797</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>44903</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>45798</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30742,7 +30742,7 @@
         <v>45324</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>44894</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>45723</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30961,7 +30961,7 @@
         <v>45799</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>45935</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>44916</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31190,7 +31190,7 @@
         <v>45799</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>44949</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>44564</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>45799</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>45936</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>45726</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>45392</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>45623</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>45189</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31852,7 +31852,7 @@
         <v>45036</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31925,7 +31925,7 @@
         <v>44834</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
         <v>44606</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>45162</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>45162</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>45805</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>45805</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>45475</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32441,7 +32441,7 @@
         <v>45643</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32514,7 +32514,7 @@
         <v>45764</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>45712</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>44813</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32733,7 +32733,7 @@
         <v>45589</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32806,7 +32806,7 @@
         <v>45937</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32879,7 +32879,7 @@
         <v>45734</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32952,7 +32952,7 @@
         <v>45713</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>45936</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>45678</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>45937</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>45807</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33322,7 +33322,7 @@
         <v>45189</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>45593</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33468,7 +33468,7 @@
         <v>45654</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>45726</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>45753</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33687,7 +33687,7 @@
         <v>45782</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33760,7 +33760,7 @@
         <v>45356</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33833,7 +33833,7 @@
         <v>45653</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>45943</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33979,7 +33979,7 @@
         <v>45461</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34057,7 +34057,7 @@
         <v>45202</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34130,7 +34130,7 @@
         <v>45946</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>45813</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34276,7 +34276,7 @@
         <v>45813</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34349,7 +34349,7 @@
         <v>45768</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34422,7 +34422,7 @@
         <v>45947</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>45818</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34573,7 +34573,7 @@
         <v>45729</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34646,7 +34646,7 @@
         <v>45034</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34719,7 +34719,7 @@
         <v>44956</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34792,7 +34792,7 @@
         <v>45608</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34865,7 +34865,7 @@
         <v>45819</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34938,7 +34938,7 @@
         <v>45232</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35011,7 +35011,7 @@
         <v>45366</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35084,7 +35084,7 @@
         <v>44573</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35157,7 +35157,7 @@
         <v>45825</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35230,7 +35230,7 @@
         <v>45825</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>45825</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>45825</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35449,7 +35449,7 @@
         <v>45825</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35522,7 +35522,7 @@
         <v>45825</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>45952</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>45825</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>45825</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35814,7 +35814,7 @@
         <v>45825</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35887,7 +35887,7 @@
         <v>45825</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35960,7 +35960,7 @@
         <v>44998</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
         <v>45758</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36106,7 +36106,7 @@
         <v>45237</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>44965</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>44965</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36325,7 +36325,7 @@
         <v>45832</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36398,7 +36398,7 @@
         <v>45952</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36471,7 +36471,7 @@
         <v>45684</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36544,7 +36544,7 @@
         <v>45062</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>45951</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>45957</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>45960</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36841,7 +36841,7 @@
         <v>45833</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36919,7 +36919,7 @@
         <v>45834</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36997,7 +36997,7 @@
         <v>44571</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37070,7 +37070,7 @@
         <v>45324</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>45964</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37216,7 +37216,7 @@
         <v>45707</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37289,7 +37289,7 @@
         <v>45964</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>45964</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>45161</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>45964</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37581,7 +37581,7 @@
         <v>45036</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37654,7 +37654,7 @@
         <v>45724</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37727,7 +37727,7 @@
         <v>45964</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37805,7 +37805,7 @@
         <v>45964</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37883,7 +37883,7 @@
         <v>45964</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37961,7 +37961,7 @@
         <v>45964</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>45763</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>45838</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>45838</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38263,7 +38263,7 @@
         <v>45365</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>45840</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38414,7 +38414,7 @@
         <v>45884</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>45840</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>45636</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38638,7 +38638,7 @@
         <v>45840</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38711,7 +38711,7 @@
         <v>45950</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38784,7 +38784,7 @@
         <v>45842</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38857,7 +38857,7 @@
         <v>45950</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38930,7 +38930,7 @@
         <v>45968</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39003,7 +39003,7 @@
         <v>44971</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39076,7 +39076,7 @@
         <v>45302</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39149,7 +39149,7 @@
         <v>45841</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39222,7 +39222,7 @@
         <v>45841</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>45968</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39368,7 +39368,7 @@
         <v>45841</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39446,7 +39446,7 @@
         <v>45841</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>44739</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39597,7 +39597,7 @@
         <v>45280</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>44792</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>45971</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39816,7 +39816,7 @@
         <v>45180</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39889,7 +39889,7 @@
         <v>45974</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>45974</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40035,7 +40035,7 @@
         <v>44826</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40128,7 +40128,7 @@
         <v>45974</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45279</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40274,7 +40274,7 @@
         <v>45974</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40347,7 +40347,7 @@
         <v>45974</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40420,7 +40420,7 @@
         <v>45974</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40493,7 +40493,7 @@
         <v>45645</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
         <v>45645</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40639,7 +40639,7 @@
         <v>45974</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40712,7 +40712,7 @@
         <v>45852</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40785,7 +40785,7 @@
         <v>45327</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40858,7 +40858,7 @@
         <v>44769</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>45855</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         <v>45198</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>45799</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41155,7 +41155,7 @@
         <v>44804</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41228,7 +41228,7 @@
         <v>45336</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41301,7 +41301,7 @@
         <v>45860</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41374,7 +41374,7 @@
         <v>45859</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41447,7 +41447,7 @@
         <v>45743</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41520,7 +41520,7 @@
         <v>45684</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>45799</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41666,7 +41666,7 @@
         <v>45680</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41739,7 +41739,7 @@
         <v>44803</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41812,7 +41812,7 @@
         <v>45825</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41885,7 +41885,7 @@
         <v>45749</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41958,7 +41958,7 @@
         <v>45153</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42031,7 +42031,7 @@
         <v>45512</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42109,7 +42109,7 @@
         <v>44819</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42182,7 +42182,7 @@
         <v>44608</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42255,7 +42255,7 @@
         <v>45294</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42328,7 +42328,7 @@
         <v>45040</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42401,7 +42401,7 @@
         <v>45714</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42474,7 +42474,7 @@
         <v>45979</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>45323</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42620,7 +42620,7 @@
         <v>45476</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42693,7 +42693,7 @@
         <v>45685</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>45685</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42839,7 +42839,7 @@
         <v>45874</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45874</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42985,7 +42985,7 @@
         <v>45763</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43063,7 +43063,7 @@
         <v>45763</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43141,7 +43141,7 @@
         <v>45979</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43214,7 +43214,7 @@
         <v>45873</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>45763</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43365,7 +43365,7 @@
         <v>45365</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43438,7 +43438,7 @@
         <v>45979</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>45008</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>45979</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
         <v>45874</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43730,7 +43730,7 @@
         <v>45979</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45365</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43876,7 +43876,7 @@
         <v>45660</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43949,7 +43949,7 @@
         <v>45483</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44022,7 +44022,7 @@
         <v>45979</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44095,7 +44095,7 @@
         <v>44830</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44168,7 +44168,7 @@
         <v>45876</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44241,7 +44241,7 @@
         <v>45875</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>45729</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44387,7 +44387,7 @@
         <v>45981</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>44865</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44533,7 +44533,7 @@
         <v>45982</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44606,7 +44606,7 @@
         <v>45982</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44679,7 +44679,7 @@
         <v>45712</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44752,7 +44752,7 @@
         <v>45981</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44825,7 +44825,7 @@
         <v>44782</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44898,7 +44898,7 @@
         <v>45881</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44971,7 +44971,7 @@
         <v>45881</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45044,7 +45044,7 @@
         <v>46052</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45541</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45190,7 +45190,7 @@
         <v>45163</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>45173</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>45981</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45414,7 +45414,7 @@
         <v>46098</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         <v>46098</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45560,7 +45560,7 @@
         <v>46099</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45638,7 +45638,7 @@
         <v>45986</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45711,7 +45711,7 @@
         <v>46100</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45784,7 +45784,7 @@
         <v>46104</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45857,7 +45857,7 @@
         <v>45502</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45930,7 +45930,7 @@
         <v>46104</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46003,7 +46003,7 @@
         <v>45328</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>45044</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46149,7 +46149,7 @@
         <v>46105</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46222,7 +46222,7 @@
         <v>45474</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46295,7 +46295,7 @@
         <v>45763</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46373,7 +46373,7 @@
         <v>45320</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46446,7 +46446,7 @@
         <v>45273</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46519,7 +46519,7 @@
         <v>45987</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46592,7 +46592,7 @@
         <v>45987</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46665,7 +46665,7 @@
         <v>45764</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46743,7 +46743,7 @@
         <v>45418</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46816,7 +46816,7 @@
         <v>44529</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46889,7 +46889,7 @@
         <v>45988</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46962,7 +46962,7 @@
         <v>45988</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>45300</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>44573</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47181,7 +47181,7 @@
         <v>44978</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47254,7 +47254,7 @@
         <v>45400</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47327,7 +47327,7 @@
         <v>44879</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47400,7 +47400,7 @@
         <v>46119</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47473,7 +47473,7 @@
         <v>45994</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47546,7 +47546,7 @@
         <v>45959</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>45996</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47692,7 +47692,7 @@
         <v>46127</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47765,7 +47765,7 @@
         <v>45999</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47838,7 +47838,7 @@
         <v>45999</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47911,7 +47911,7 @@
         <v>46000</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47984,7 +47984,7 @@
         <v>46112</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48057,7 +48057,7 @@
         <v>46071</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48130,7 +48130,7 @@
         <v>46127</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48203,7 +48203,7 @@
         <v>46001</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48276,7 +48276,7 @@
         <v>46002</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48349,7 +48349,7 @@
         <v>46000</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>46128</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48495,7 +48495,7 @@
         <v>44482</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48568,7 +48568,7 @@
         <v>46000</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48641,7 +48641,7 @@
         <v>45561</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48714,7 +48714,7 @@
         <v>44727</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48787,7 +48787,7 @@
         <v>46134</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48860,7 +48860,7 @@
         <v>46134</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48933,7 +48933,7 @@
         <v>45797</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49006,7 +49006,7 @@
         <v>46008</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49079,7 +49079,7 @@
         <v>46008</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49152,7 +49152,7 @@
         <v>46007</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49225,7 +49225,7 @@
         <v>46008</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>46008</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49371,7 +49371,7 @@
         <v>46007</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49444,7 +49444,7 @@
         <v>44788</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>46008</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49590,7 +49590,7 @@
         <v>46008</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49663,7 +49663,7 @@
         <v>44860</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>46008</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49809,7 +49809,7 @@
         <v>46009</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49882,7 +49882,7 @@
         <v>45960</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49955,7 +49955,7 @@
         <v>46009</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50028,7 +50028,7 @@
         <v>46009</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50101,7 +50101,7 @@
         <v>46009</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50174,7 +50174,7 @@
         <v>45419</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50247,7 +50247,7 @@
         <v>46009</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>46136</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>45876</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50466,7 +50466,7 @@
         <v>45771</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50539,7 +50539,7 @@
         <v>45896</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50612,7 +50612,7 @@
         <v>46014</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50685,7 +50685,7 @@
         <v>45239</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50758,7 +50758,7 @@
         <v>46069</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50831,7 +50831,7 @@
         <v>45425</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50904,7 +50904,7 @@
         <v>46022</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50977,7 +50977,7 @@
         <v>46107</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>46024</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51123,7 +51123,7 @@
         <v>45909</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51196,7 +51196,7 @@
         <v>46024</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51269,7 +51269,7 @@
         <v>46024</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51342,7 +51342,7 @@
         <v>46024</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51415,7 +51415,7 @@
         <v>44897</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51488,7 +51488,7 @@
         <v>45232</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51566,7 +51566,7 @@
         <v>44883</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         <v>46029</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45943</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51785,7 +51785,7 @@
         <v>46140</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51858,7 +51858,7 @@
         <v>46031</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51931,7 +51931,7 @@
         <v>46034</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52004,7 +52004,7 @@
         <v>45973</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52077,7 +52077,7 @@
         <v>45821</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52150,7 +52150,7 @@
         <v>46031</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52223,7 +52223,7 @@
         <v>45282</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52296,7 +52296,7 @@
         <v>45875</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52369,7 +52369,7 @@
         <v>44750</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52442,7 +52442,7 @@
         <v>44855</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52515,7 +52515,7 @@
         <v>45678</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52588,7 +52588,7 @@
         <v>46042</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52661,7 +52661,7 @@
         <v>45544</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52734,7 +52734,7 @@
         <v>45813</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52807,7 +52807,7 @@
         <v>46041</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52880,7 +52880,7 @@
         <v>46041</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52953,7 +52953,7 @@
         <v>46041</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53026,7 +53026,7 @@
         <v>46043</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53099,7 +53099,7 @@
         <v>44574</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53172,7 +53172,7 @@
         <v>46043</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53245,7 +53245,7 @@
         <v>46044</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53318,7 +53318,7 @@
         <v>46029</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53391,7 +53391,7 @@
         <v>46043</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53464,7 +53464,7 @@
         <v>46043</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53537,7 +53537,7 @@
         <v>45757</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53615,7 +53615,7 @@
         <v>45685</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53688,7 +53688,7 @@
         <v>46043</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53761,7 +53761,7 @@
         <v>45841</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53834,7 +53834,7 @@
         <v>45034</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53907,7 +53907,7 @@
         <v>46044</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53985,7 +53985,7 @@
         <v>46064</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54058,7 +54058,7 @@
         <v>45733</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54131,7 +54131,7 @@
         <v>45000</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54209,7 +54209,7 @@
         <v>46084</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54282,7 +54282,7 @@
         <v>45959</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54355,7 +54355,7 @@
         <v>44774</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54428,7 +54428,7 @@
         <v>46043</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54501,7 +54501,7 @@
         <v>45085</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54574,7 +54574,7 @@
         <v>46048</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54647,7 +54647,7 @@
         <v>44824</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54720,7 +54720,7 @@
         <v>44852</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>46046</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54866,7 +54866,7 @@
         <v>46046</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54939,7 +54939,7 @@
         <v>46046</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55012,7 +55012,7 @@
         <v>46047</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55085,7 +55085,7 @@
         <v>45672</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55158,7 +55158,7 @@
         <v>44834</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55231,7 +55231,7 @@
         <v>45818</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55304,7 +55304,7 @@
         <v>45553</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55377,7 +55377,7 @@
         <v>46049</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55450,7 +55450,7 @@
         <v>46142</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55523,7 +55523,7 @@
         <v>46049</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55596,7 +55596,7 @@
         <v>46049</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55669,7 +55669,7 @@
         <v>45989</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55742,7 +55742,7 @@
         <v>45842</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55815,7 +55815,7 @@
         <v>45959</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55888,7 +55888,7 @@
         <v>45931</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55961,7 +55961,7 @@
         <v>45894</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56034,7 +56034,7 @@
         <v>46046</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56107,7 +56107,7 @@
         <v>46054</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56180,7 +56180,7 @@
         <v>46054</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56253,7 +56253,7 @@
         <v>46046</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56326,7 +56326,7 @@
         <v>46054</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56399,7 +56399,7 @@
         <v>45881</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56472,7 +56472,7 @@
         <v>45173</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56545,7 +56545,7 @@
         <v>46062</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56618,7 +56618,7 @@
         <v>46146</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56691,7 +56691,7 @@
         <v>46146</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56764,7 +56764,7 @@
         <v>46063</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56837,7 +56837,7 @@
         <v>46063</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56910,7 +56910,7 @@
         <v>46148</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -56988,7 +56988,7 @@
         <v>46147</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57066,7 +57066,7 @@
         <v>46069</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57139,7 +57139,7 @@
         <v>46071</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57212,7 +57212,7 @@
         <v>46043</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57285,7 +57285,7 @@
         <v>46072</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57358,7 +57358,7 @@
         <v>46072</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57431,7 +57431,7 @@
         <v>46077</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57504,7 +57504,7 @@
         <v>45120</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57577,7 +57577,7 @@
         <v>46153</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57650,7 +57650,7 @@
         <v>45959</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57723,7 +57723,7 @@
         <v>46155</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57796,7 +57796,7 @@
         <v>45950</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57869,7 +57869,7 @@
         <v>46155</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -57942,7 +57942,7 @@
         <v>46155</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58015,7 +58015,7 @@
         <v>45916</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58088,7 +58088,7 @@
         <v>46160</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58166,7 +58166,7 @@
         <v>46160</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58239,7 +58239,7 @@
         <v>45679</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58312,7 +58312,7 @@
         <v>46157</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58385,7 +58385,7 @@
         <v>45707</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58458,7 +58458,7 @@
         <v>46160</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58531,7 +58531,7 @@
         <v>45433</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58604,7 +58604,7 @@
         <v>45947</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58677,7 +58677,7 @@
         <v>45947</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58750,7 +58750,7 @@
         <v>46098</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58823,7 +58823,7 @@
         <v>46047</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -58896,7 +58896,7 @@
         <v>46093</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -58969,7 +58969,7 @@
         <v>46161</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59042,7 +59042,7 @@
         <v>45947</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59115,7 +59115,7 @@
         <v>46094</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59188,7 +59188,7 @@
         <v>45728</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59261,7 +59261,7 @@
         <v>45957</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59334,7 +59334,7 @@
         <v>46064</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59407,7 +59407,7 @@
         <v>45959</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59480,7 +59480,7 @@
         <v>46164</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59553,7 +59553,7 @@
         <v>46164</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59626,7 +59626,7 @@
         <v>46163</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59699,7 +59699,7 @@
         <v>46163</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59772,7 +59772,7 @@
         <v>46164</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59845,7 +59845,7 @@
         <v>46146</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -59918,7 +59918,7 @@
         <v>45952</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -59991,7 +59991,7 @@
         <v>45981</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60064,7 +60064,7 @@
         <v>46168</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60137,7 +60137,7 @@
         <v>46167</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60210,7 +60210,7 @@
         <v>45173</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60283,7 +60283,7 @@
         <v>46169</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60356,7 +60356,7 @@
         <v>46168</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60429,7 +60429,7 @@
         <v>46170</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60502,7 +60502,7 @@
         <v>46174</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60575,7 +60575,7 @@
         <v>46174</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60648,7 +60648,7 @@
         <v>46174</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60721,7 +60721,7 @@
         <v>46174</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60794,7 +60794,7 @@
         <v>46174</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -60867,7 +60867,7 @@
         <v>46177</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -60940,7 +60940,7 @@
         <v>46176</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61013,7 +61013,7 @@
         <v>46176</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61086,7 +61086,7 @@
         <v>46181</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61164,7 +61164,7 @@
         <v>46181</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61237,7 +61237,7 @@
         <v>46181</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61310,7 +61310,7 @@
         <v>46181</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61383,7 +61383,7 @@
         <v>46181</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61456,7 +61456,7 @@
         <v>46181</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61529,7 +61529,7 @@
         <v>46188</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61602,7 +61602,7 @@
         <v>46188</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61680,7 +61680,7 @@
         <v>46188</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61753,7 +61753,7 @@
         <v>46190</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -61826,7 +61826,7 @@
         <v>46190</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -61899,7 +61899,7 @@
         <v>46190</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -61972,7 +61972,7 @@
         <v>46190</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62045,7 +62045,7 @@
         <v>46195</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62118,7 +62118,7 @@
         <v>46195</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62191,7 +62191,7 @@
         <v>46195</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62264,7 +62264,7 @@
         <v>46199</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62337,7 +62337,7 @@
         <v>46198</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62410,7 +62410,7 @@
         <v>46199</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62483,7 +62483,7 @@
         <v>46198</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62556,7 +62556,7 @@
         <v>46198</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62629,7 +62629,7 @@
         <v>46199</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62702,7 +62702,7 @@
         <v>46034</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62775,7 +62775,7 @@
         <v>46198</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -62848,7 +62848,7 @@
         <v>46204</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -62921,7 +62921,7 @@
         <v>46205</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -62994,7 +62994,7 @@
         <v>46209</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63067,7 +63067,7 @@
         <v>46209</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63140,7 +63140,7 @@
         <v>46209</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63213,7 +63213,7 @@
         <v>46210</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63286,7 +63286,7 @@
         <v>46210</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63359,7 +63359,7 @@
         <v>46265</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63437,7 +63437,7 @@
         <v>46265</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63510,7 +63510,7 @@
         <v>46265</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63588,7 +63588,7 @@
         <v>46265</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63666,7 +63666,7 @@
         <v>46140</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63739,7 +63739,7 @@
         <v>46265</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -63817,7 +63817,7 @@
         <v>46265</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -63890,7 +63890,7 @@
         <v>46265</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -63968,7 +63968,7 @@
         <v>46164</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64041,7 +64041,7 @@
         <v>46266</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64114,7 +64114,7 @@
         <v>46268</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64187,7 +64187,7 @@
         <v>46224</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64265,7 +64265,7 @@
         <v>46267</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64338,7 +64338,7 @@
         <v>45770</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64416,7 +64416,7 @@
         <v>46225</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64489,7 +64489,7 @@
         <v>46273</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64562,7 +64562,7 @@
         <v>46273</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64635,7 +64635,7 @@
         <v>46274</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64713,7 +64713,7 @@
         <v>46232</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -64786,7 +64786,7 @@
         <v>46237</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -64859,7 +64859,7 @@
         <v>46280</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -64932,7 +64932,7 @@
         <v>44854</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65005,7 +65005,7 @@
         <v>46237</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65078,7 +65078,7 @@
         <v>44540</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65151,7 +65151,7 @@
         <v>46280</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65224,7 +65224,7 @@
         <v>46238</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65297,7 +65297,7 @@
         <v>46238</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65370,7 +65370,7 @@
         <v>46281</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65443,7 +65443,7 @@
         <v>46240</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65516,7 +65516,7 @@
         <v>46239</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65589,7 +65589,7 @@
         <v>46239</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65662,7 +65662,7 @@
         <v>46281</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -65735,7 +65735,7 @@
         <v>46238</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -65808,7 +65808,7 @@
         <v>46284</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -65881,7 +65881,7 @@
         <v>46284</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -65954,7 +65954,7 @@
         <v>46283</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66027,7 +66027,7 @@
         <v>46241</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66105,7 +66105,7 @@
         <v>46287</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66178,7 +66178,7 @@
         <v>46288</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66256,7 +66256,7 @@
         <v>46266</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66329,7 +66329,7 @@
         <v>46244</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66402,7 +66402,7 @@
         <v>46287</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66475,7 +66475,7 @@
         <v>46287</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66548,7 +66548,7 @@
         <v>46244</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66621,7 +66621,7 @@
         <v>46247</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66699,7 +66699,7 @@
         <v>46289</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -66772,7 +66772,7 @@
         <v>46287</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -66845,7 +66845,7 @@
         <v>45750</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -66918,7 +66918,7 @@
         <v>46120</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -66991,7 +66991,7 @@
         <v>45803</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67064,7 +67064,7 @@
         <v>46248</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67142,7 +67142,7 @@
         <v>46248</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67215,7 +67215,7 @@
         <v>46239</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67288,7 +67288,7 @@
         <v>46266</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67361,7 +67361,7 @@
         <v>46253</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67434,7 +67434,7 @@
         <v>46251</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67507,7 +67507,7 @@
         <v>46253</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67585,7 +67585,7 @@
         <v>46251</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67663,7 +67663,7 @@
         <v>46253</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -67741,7 +67741,7 @@
         <v>46296</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -67819,7 +67819,7 @@
         <v>46296</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -67897,7 +67897,7 @@
         <v>46251</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -67970,7 +67970,7 @@
         <v>46253</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68043,7 +68043,7 @@
         <v>46253</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68116,7 +68116,7 @@
         <v>46266</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68189,7 +68189,7 @@
         <v>45734</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68262,7 +68262,7 @@
         <v>46254</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68335,7 +68335,7 @@
         <v>46254</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68408,7 +68408,7 @@
         <v>46300</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68481,7 +68481,7 @@
         <v>46300</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68554,7 +68554,7 @@
         <v>46254</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68632,7 +68632,7 @@
         <v>46254</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -68710,7 +68710,7 @@
         <v>46300</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -68783,7 +68783,7 @@
         <v>46256</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -68856,7 +68856,7 @@
         <v>46300</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -68934,7 +68934,7 @@
         <v>46274</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69007,7 +69007,7 @@
         <v>46256</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69080,7 +69080,7 @@
         <v>46297</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69153,7 +69153,7 @@
         <v>46298</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69226,7 +69226,7 @@
         <v>46268</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69299,7 +69299,7 @@
         <v>46258</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69377,7 +69377,7 @@
         <v>46300</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69450,7 +69450,7 @@
         <v>46301</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69523,7 +69523,7 @@
         <v>46301</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69596,7 +69596,7 @@
         <v>46304</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -69669,7 +69669,7 @@
         <v>46304</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -69742,7 +69742,7 @@
         <v>46266</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -69815,7 +69815,7 @@
         <v>46293</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -69888,7 +69888,7 @@
         <v>46262</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -69961,7 +69961,7 @@
         <v>46262</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70034,7 +70034,7 @@
         <v>46036</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70107,7 +70107,7 @@
         <v>46262</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70180,7 +70180,7 @@
         <v>45833</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70253,7 +70253,7 @@
         <v>46069</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70326,7 +70326,7 @@
         <v>44880</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70399,7 +70399,7 @@
         <v>44971</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70472,7 +70472,7 @@
         <v>45751</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70545,7 +70545,7 @@
         <v>45751</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -70623,7 +70623,7 @@
         <v>45790</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -70701,7 +70701,7 @@
         <v>46041</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -70774,7 +70774,7 @@
         <v>46078</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -70847,7 +70847,7 @@
         <v>46073</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -70920,7 +70920,7 @@
         <v>46142</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>

--- a/Översikt KRAMFORS.xlsx
+++ b/Översikt KRAMFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45544</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>46183</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>46029</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>46003</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>46094</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>46197</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>45763</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>44810</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45831</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>46287</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>46196</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>45763</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>46044</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>46197</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>46241</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>45511</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>45056</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>46136</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>46002</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>46203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>45763</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>46181</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>46196</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>45723</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>46136</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>46265</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>44713</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>45399</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>45785</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>45484</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>45818</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>45973</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>45985</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>45660</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>44524</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>45356</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>45733</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>45996</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>44629</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>45818</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>45957</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>45959</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>44813</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>45985</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>45516</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>45282</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>46195</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>46046</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>45806</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>46258</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>45114</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>45898</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>45898</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>45551</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>45786</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>45468</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>45729</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>45840</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>45511</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>46036</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>46178</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>46273</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>45665</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>46241</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>46244</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>46254</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>45182</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>45750</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>45243</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>44803</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>45199</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>45400</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>45114</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>45924</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>45764</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>45645</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>45943</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>44965</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>45764</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>45979</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>45156</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>46098</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>45998</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>46020</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>46021</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>46024</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>46030</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>45344</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>44852</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>46048</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>45670</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>46071</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>46281</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         <v>45636</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>45071</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>44817</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>44804</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>44634</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>44859</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>44508</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>44508</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>44608</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>44509</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>44594</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>44496</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>44587</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>44511</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>44592</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>44592</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         <v>44722</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12352,7 +12352,7 @@
         <v>44688</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>44556</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12498,7 +12498,7 @@
         <v>44852</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         <v>44508</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>44817</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>44817</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>44762</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>44509</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>44859</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>44581</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>44516</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>44509</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>44539</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>44859</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>44581</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>44509</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>44540</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>44566</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>44482</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44550</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>44503</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>44687</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>44594</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>44484</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>44719</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>44607</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>44715</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>44601</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>44484</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>44803</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>44876</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>44628</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14693,7 +14693,7 @@
         <v>44782</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>44629</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44616</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>44594</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>44802</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>44749</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>44697</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>44581</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>45209</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>45225</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>45674</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         <v>44747</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>44804</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>44880</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>45496</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         <v>44943</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>45390</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>45664</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>45674</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>45190</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>44775</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>44608</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>45721</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>45034</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>45520</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>45698</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>45754</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>45148</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>45307</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>45205</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>45513</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>45351</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>45392</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>45554</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>44840</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>45672</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>45712</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>44741</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>44901</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>45740</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>44915</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45450</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>45265</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>45447</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>44958</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45572</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>45261</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>45726</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>45534</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>45124</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>45524</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>45099</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>45089</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>45034</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         <v>44853</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>45724</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>44880</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>44965</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>44907</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19015,7 +19015,7 @@
         <v>45043</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19088,7 +19088,7 @@
         <v>45044</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>45365</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>45240</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         <v>45623</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19385,7 +19385,7 @@
         <v>44946</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>45278</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19531,7 +19531,7 @@
         <v>45771</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>44956</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>44956</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>45589</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         <v>45883</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19896,7 +19896,7 @@
         <v>45273</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>45099</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>44556</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>45324</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>45579</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>45883</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         <v>45680</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>45883</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>45099</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20558,7 +20558,7 @@
         <v>45236</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>45450</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20704,7 +20704,7 @@
         <v>44958</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>44574</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>44894</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>45329</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>45883</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>45000</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45271</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>45888</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>45153</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>45273</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         <v>45328</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21517,7 +21517,7 @@
         <v>45440</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         <v>45616</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>44537</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>44942</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21809,7 +21809,7 @@
         <v>44908</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
         <v>45890</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>45771</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22028,7 +22028,7 @@
         <v>45294</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22101,7 +22101,7 @@
         <v>45890</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22174,7 +22174,7 @@
         <v>45345</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>45482</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>45271</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>45365</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>45355</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>45475</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>45519</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>45890</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>45674</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>45898</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>45898</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>45898</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         <v>45898</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>45898</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23211,7 +23211,7 @@
         <v>45469</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>44519</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>45278</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>45898</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>45898</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23576,7 +23576,7 @@
         <v>45901</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23649,7 +23649,7 @@
         <v>44529</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23722,7 +23722,7 @@
         <v>45644</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>45645</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23868,7 +23868,7 @@
         <v>45898</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>45898</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24014,7 +24014,7 @@
         <v>45901</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24087,7 +24087,7 @@
         <v>45265</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>45898</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>45901</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>44536</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>44574</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>45638</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>44634</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45632</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45754</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>45545</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>45433</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>44909</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45538</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>45909</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>45909</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>44613</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25265,7 +25265,7 @@
         <v>45909</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>45425</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>45776</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25494,7 +25494,7 @@
         <v>45034</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>45744</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>45062</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>44503</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>45247</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45912</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>44908</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>45782</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26088,7 +26088,7 @@
         <v>45546</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26161,7 +26161,7 @@
         <v>45664</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26234,7 +26234,7 @@
         <v>45034</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26307,7 +26307,7 @@
         <v>45182</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>45491</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>44959</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>44872</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26609,7 +26609,7 @@
         <v>45420</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>45236</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>45588</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26828,7 +26828,7 @@
         <v>45588</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26901,7 +26901,7 @@
         <v>45588</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26974,7 +26974,7 @@
         <v>44958</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>44958</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>45281</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27193,7 +27193,7 @@
         <v>44834</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>45306</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         <v>45518</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>45918</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         <v>45034</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>45408</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         <v>45476</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>45496</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>45454</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         <v>44991</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27938,7 +27938,7 @@
         <v>44610</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28011,7 +28011,7 @@
         <v>45169</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>44629</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28157,7 +28157,7 @@
         <v>44546</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>44956</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28303,7 +28303,7 @@
         <v>45790</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28376,7 +28376,7 @@
         <v>45750</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
         <v>45008</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>45496</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28600,7 +28600,7 @@
         <v>45764</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>44998</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28751,7 +28751,7 @@
         <v>45792</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>45513</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>45567</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>45320</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>45926</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>45926</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>45225</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>45618</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>45231</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>45162</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29486,7 +29486,7 @@
         <v>44888</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29559,7 +29559,7 @@
         <v>45552</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29632,7 +29632,7 @@
         <v>45791</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29705,7 +29705,7 @@
         <v>45415</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>45418</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>44804</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>45552</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>45526</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>44503</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30143,7 +30143,7 @@
         <v>44638</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30216,7 +30216,7 @@
         <v>45435</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30294,7 +30294,7 @@
         <v>45190</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>45797</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>45932</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>45797</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>44903</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>45798</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30742,7 +30742,7 @@
         <v>45324</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>44894</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>45723</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30961,7 +30961,7 @@
         <v>45799</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>45935</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>44916</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31190,7 +31190,7 @@
         <v>45799</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>44949</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>44564</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>45799</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>45936</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>45726</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>45392</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>45623</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>45189</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31852,7 +31852,7 @@
         <v>45036</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31925,7 +31925,7 @@
         <v>44834</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
         <v>44606</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>45162</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>45162</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>45805</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>45805</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>45475</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32441,7 +32441,7 @@
         <v>45643</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32514,7 +32514,7 @@
         <v>45764</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>45712</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>44813</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32733,7 +32733,7 @@
         <v>45589</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32806,7 +32806,7 @@
         <v>45937</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32879,7 +32879,7 @@
         <v>45734</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32952,7 +32952,7 @@
         <v>45713</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>45936</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>45678</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>45937</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>45807</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33322,7 +33322,7 @@
         <v>45189</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>45593</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33468,7 +33468,7 @@
         <v>45654</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>45726</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>45753</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33687,7 +33687,7 @@
         <v>45782</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33760,7 +33760,7 @@
         <v>45356</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33833,7 +33833,7 @@
         <v>45653</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>45943</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33979,7 +33979,7 @@
         <v>45461</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34057,7 +34057,7 @@
         <v>45202</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34130,7 +34130,7 @@
         <v>45946</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>45813</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34276,7 +34276,7 @@
         <v>45813</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34349,7 +34349,7 @@
         <v>45768</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34422,7 +34422,7 @@
         <v>45947</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>45818</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34573,7 +34573,7 @@
         <v>45729</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34646,7 +34646,7 @@
         <v>45034</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34719,7 +34719,7 @@
         <v>44956</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34792,7 +34792,7 @@
         <v>45608</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34865,7 +34865,7 @@
         <v>45819</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34938,7 +34938,7 @@
         <v>45232</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35011,7 +35011,7 @@
         <v>45366</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35084,7 +35084,7 @@
         <v>44573</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35157,7 +35157,7 @@
         <v>45825</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35230,7 +35230,7 @@
         <v>45825</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>45825</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>45825</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35449,7 +35449,7 @@
         <v>45825</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35522,7 +35522,7 @@
         <v>45825</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>45952</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>45825</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>45825</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35814,7 +35814,7 @@
         <v>45825</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35887,7 +35887,7 @@
         <v>45825</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35960,7 +35960,7 @@
         <v>44998</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
         <v>45758</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36106,7 +36106,7 @@
         <v>45237</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>44965</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>44965</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36325,7 +36325,7 @@
         <v>45832</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36398,7 +36398,7 @@
         <v>45952</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36471,7 +36471,7 @@
         <v>45684</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36544,7 +36544,7 @@
         <v>45062</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>45951</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>45957</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>45960</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36841,7 +36841,7 @@
         <v>45833</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36919,7 +36919,7 @@
         <v>45834</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36997,7 +36997,7 @@
         <v>44571</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37070,7 +37070,7 @@
         <v>45324</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>45964</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37216,7 +37216,7 @@
         <v>45707</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37289,7 +37289,7 @@
         <v>45964</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>45964</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>45161</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>45964</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37581,7 +37581,7 @@
         <v>45036</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37654,7 +37654,7 @@
         <v>45724</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37727,7 +37727,7 @@
         <v>45964</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37805,7 +37805,7 @@
         <v>45964</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37883,7 +37883,7 @@
         <v>45964</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37961,7 +37961,7 @@
         <v>45964</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>45763</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>45838</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>45838</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38263,7 +38263,7 @@
         <v>45365</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>45840</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38414,7 +38414,7 @@
         <v>45884</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>45840</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>45636</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38638,7 +38638,7 @@
         <v>45840</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38711,7 +38711,7 @@
         <v>45950</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38784,7 +38784,7 @@
         <v>45842</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38857,7 +38857,7 @@
         <v>45950</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38930,7 +38930,7 @@
         <v>45968</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39003,7 +39003,7 @@
         <v>44971</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39076,7 +39076,7 @@
         <v>45302</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39149,7 +39149,7 @@
         <v>45841</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39222,7 +39222,7 @@
         <v>45841</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>45968</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39368,7 +39368,7 @@
         <v>45841</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39446,7 +39446,7 @@
         <v>45841</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>44739</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39597,7 +39597,7 @@
         <v>45280</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>44792</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>45971</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39816,7 +39816,7 @@
         <v>45180</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39889,7 +39889,7 @@
         <v>45974</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>45974</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40035,7 +40035,7 @@
         <v>44826</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40128,7 +40128,7 @@
         <v>45974</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45279</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40274,7 +40274,7 @@
         <v>45974</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40347,7 +40347,7 @@
         <v>45974</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40420,7 +40420,7 @@
         <v>45974</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40493,7 +40493,7 @@
         <v>45645</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
         <v>45645</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40639,7 +40639,7 @@
         <v>45974</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40712,7 +40712,7 @@
         <v>45852</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40785,7 +40785,7 @@
         <v>45327</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40858,7 +40858,7 @@
         <v>44769</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>45855</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         <v>45198</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>45799</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41155,7 +41155,7 @@
         <v>44804</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41228,7 +41228,7 @@
         <v>45336</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41301,7 +41301,7 @@
         <v>45860</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41374,7 +41374,7 @@
         <v>45859</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41447,7 +41447,7 @@
         <v>45743</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41520,7 +41520,7 @@
         <v>45684</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>45799</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41666,7 +41666,7 @@
         <v>45680</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41739,7 +41739,7 @@
         <v>44803</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41812,7 +41812,7 @@
         <v>45825</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41885,7 +41885,7 @@
         <v>45749</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41958,7 +41958,7 @@
         <v>45153</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42031,7 +42031,7 @@
         <v>45512</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42109,7 +42109,7 @@
         <v>44819</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42182,7 +42182,7 @@
         <v>44608</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42255,7 +42255,7 @@
         <v>45294</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42328,7 +42328,7 @@
         <v>45040</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42401,7 +42401,7 @@
         <v>45714</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42474,7 +42474,7 @@
         <v>45979</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>45323</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42620,7 +42620,7 @@
         <v>45476</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42693,7 +42693,7 @@
         <v>45685</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>45685</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42839,7 +42839,7 @@
         <v>45874</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45874</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42985,7 +42985,7 @@
         <v>45763</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43063,7 +43063,7 @@
         <v>45763</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43141,7 +43141,7 @@
         <v>45979</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43214,7 +43214,7 @@
         <v>45873</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>45763</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43365,7 +43365,7 @@
         <v>45365</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43438,7 +43438,7 @@
         <v>45979</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>45008</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>45979</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
         <v>45874</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43730,7 +43730,7 @@
         <v>45979</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45365</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43876,7 +43876,7 @@
         <v>45660</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43949,7 +43949,7 @@
         <v>45483</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44022,7 +44022,7 @@
         <v>45979</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44095,7 +44095,7 @@
         <v>44830</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44168,7 +44168,7 @@
         <v>45876</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44241,7 +44241,7 @@
         <v>45875</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>45729</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44387,7 +44387,7 @@
         <v>45981</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>44865</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44533,7 +44533,7 @@
         <v>45982</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44606,7 +44606,7 @@
         <v>45982</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44679,7 +44679,7 @@
         <v>45712</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44752,7 +44752,7 @@
         <v>45981</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44825,7 +44825,7 @@
         <v>44782</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44898,7 +44898,7 @@
         <v>45881</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44971,7 +44971,7 @@
         <v>45881</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45044,7 +45044,7 @@
         <v>46052</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45541</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45190,7 +45190,7 @@
         <v>45163</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>45173</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>45981</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45414,7 +45414,7 @@
         <v>46098</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         <v>46098</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45560,7 +45560,7 @@
         <v>46099</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45638,7 +45638,7 @@
         <v>45986</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45711,7 +45711,7 @@
         <v>46100</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45784,7 +45784,7 @@
         <v>46104</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45857,7 +45857,7 @@
         <v>45502</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45930,7 +45930,7 @@
         <v>46104</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46003,7 +46003,7 @@
         <v>45328</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>45044</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46149,7 +46149,7 @@
         <v>46105</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46222,7 +46222,7 @@
         <v>45474</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46295,7 +46295,7 @@
         <v>45763</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46373,7 +46373,7 @@
         <v>45320</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46446,7 +46446,7 @@
         <v>45273</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46519,7 +46519,7 @@
         <v>45987</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46592,7 +46592,7 @@
         <v>45987</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46665,7 +46665,7 @@
         <v>45764</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46743,7 +46743,7 @@
         <v>45418</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46816,7 +46816,7 @@
         <v>44529</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46889,7 +46889,7 @@
         <v>45988</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46962,7 +46962,7 @@
         <v>45988</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>45300</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>44573</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47181,7 +47181,7 @@
         <v>44978</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47254,7 +47254,7 @@
         <v>45400</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47327,7 +47327,7 @@
         <v>44879</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47400,7 +47400,7 @@
         <v>46119</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47473,7 +47473,7 @@
         <v>45994</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47546,7 +47546,7 @@
         <v>45959</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>45996</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47692,7 +47692,7 @@
         <v>46127</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47765,7 +47765,7 @@
         <v>45999</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47838,7 +47838,7 @@
         <v>45999</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47911,7 +47911,7 @@
         <v>46000</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47984,7 +47984,7 @@
         <v>46112</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48057,7 +48057,7 @@
         <v>46071</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48130,7 +48130,7 @@
         <v>46127</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48203,7 +48203,7 @@
         <v>46001</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48276,7 +48276,7 @@
         <v>46002</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48349,7 +48349,7 @@
         <v>46000</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>46128</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48495,7 +48495,7 @@
         <v>44482</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48568,7 +48568,7 @@
         <v>46000</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48641,7 +48641,7 @@
         <v>45561</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48714,7 +48714,7 @@
         <v>44727</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48787,7 +48787,7 @@
         <v>46134</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48860,7 +48860,7 @@
         <v>46134</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48933,7 +48933,7 @@
         <v>45797</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49006,7 +49006,7 @@
         <v>46008</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49079,7 +49079,7 @@
         <v>46008</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49152,7 +49152,7 @@
         <v>46007</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49225,7 +49225,7 @@
         <v>46008</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>46008</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49371,7 +49371,7 @@
         <v>46007</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49444,7 +49444,7 @@
         <v>44788</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>46008</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49590,7 +49590,7 @@
         <v>46008</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49663,7 +49663,7 @@
         <v>44860</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>46008</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49809,7 +49809,7 @@
         <v>46009</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49882,7 +49882,7 @@
         <v>45960</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49955,7 +49955,7 @@
         <v>46009</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50028,7 +50028,7 @@
         <v>46009</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50101,7 +50101,7 @@
         <v>46009</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50174,7 +50174,7 @@
         <v>45419</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50247,7 +50247,7 @@
         <v>46009</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>46136</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>45876</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50466,7 +50466,7 @@
         <v>45771</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50539,7 +50539,7 @@
         <v>45896</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50612,7 +50612,7 @@
         <v>46014</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50685,7 +50685,7 @@
         <v>45239</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50758,7 +50758,7 @@
         <v>46069</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50831,7 +50831,7 @@
         <v>45425</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50904,7 +50904,7 @@
         <v>46022</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50977,7 +50977,7 @@
         <v>46107</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>46024</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51123,7 +51123,7 @@
         <v>45909</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51196,7 +51196,7 @@
         <v>46024</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51269,7 +51269,7 @@
         <v>46024</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51342,7 +51342,7 @@
         <v>46024</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51415,7 +51415,7 @@
         <v>44897</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51488,7 +51488,7 @@
         <v>45232</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51566,7 +51566,7 @@
         <v>44883</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         <v>46029</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45943</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51785,7 +51785,7 @@
         <v>46140</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51858,7 +51858,7 @@
         <v>46031</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51931,7 +51931,7 @@
         <v>46034</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52004,7 +52004,7 @@
         <v>45973</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52077,7 +52077,7 @@
         <v>45821</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52150,7 +52150,7 @@
         <v>46031</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52223,7 +52223,7 @@
         <v>45282</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52296,7 +52296,7 @@
         <v>45875</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52369,7 +52369,7 @@
         <v>44750</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52442,7 +52442,7 @@
         <v>44855</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52515,7 +52515,7 @@
         <v>45678</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52588,7 +52588,7 @@
         <v>46042</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52661,7 +52661,7 @@
         <v>45544</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52734,7 +52734,7 @@
         <v>45813</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52807,7 +52807,7 @@
         <v>46041</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52880,7 +52880,7 @@
         <v>46041</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52953,7 +52953,7 @@
         <v>46041</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53026,7 +53026,7 @@
         <v>46043</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53099,7 +53099,7 @@
         <v>44574</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53172,7 +53172,7 @@
         <v>46043</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53245,7 +53245,7 @@
         <v>46044</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53318,7 +53318,7 @@
         <v>46029</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53391,7 +53391,7 @@
         <v>46043</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53464,7 +53464,7 @@
         <v>46043</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53537,7 +53537,7 @@
         <v>45757</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53615,7 +53615,7 @@
         <v>45685</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53688,7 +53688,7 @@
         <v>46043</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53761,7 +53761,7 @@
         <v>45841</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53834,7 +53834,7 @@
         <v>45034</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53907,7 +53907,7 @@
         <v>46044</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53985,7 +53985,7 @@
         <v>46064</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54058,7 +54058,7 @@
         <v>45733</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54131,7 +54131,7 @@
         <v>45000</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54209,7 +54209,7 @@
         <v>46084</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54282,7 +54282,7 @@
         <v>45959</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54355,7 +54355,7 @@
         <v>44774</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54428,7 +54428,7 @@
         <v>46043</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54501,7 +54501,7 @@
         <v>45085</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54574,7 +54574,7 @@
         <v>46048</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54647,7 +54647,7 @@
         <v>44824</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54720,7 +54720,7 @@
         <v>44852</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>46046</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54866,7 +54866,7 @@
         <v>46046</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54939,7 +54939,7 @@
         <v>46046</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55012,7 +55012,7 @@
         <v>46047</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55085,7 +55085,7 @@
         <v>45672</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55158,7 +55158,7 @@
         <v>44834</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55231,7 +55231,7 @@
         <v>45818</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55304,7 +55304,7 @@
         <v>45553</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55377,7 +55377,7 @@
         <v>46049</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55450,7 +55450,7 @@
         <v>46142</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55523,7 +55523,7 @@
         <v>46049</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55596,7 +55596,7 @@
         <v>46049</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55669,7 +55669,7 @@
         <v>45989</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55742,7 +55742,7 @@
         <v>45842</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55815,7 +55815,7 @@
         <v>45959</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55888,7 +55888,7 @@
         <v>45931</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55961,7 +55961,7 @@
         <v>45894</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56034,7 +56034,7 @@
         <v>46046</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56107,7 +56107,7 @@
         <v>46054</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56180,7 +56180,7 @@
         <v>46054</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56253,7 +56253,7 @@
         <v>46046</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56326,7 +56326,7 @@
         <v>46054</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56399,7 +56399,7 @@
         <v>45881</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56472,7 +56472,7 @@
         <v>45173</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56545,7 +56545,7 @@
         <v>46062</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56618,7 +56618,7 @@
         <v>46146</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56691,7 +56691,7 @@
         <v>46146</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56764,7 +56764,7 @@
         <v>46063</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56837,7 +56837,7 @@
         <v>46063</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56910,7 +56910,7 @@
         <v>46148</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -56988,7 +56988,7 @@
         <v>46147</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57066,7 +57066,7 @@
         <v>46069</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57139,7 +57139,7 @@
         <v>46071</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57212,7 +57212,7 @@
         <v>46043</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57285,7 +57285,7 @@
         <v>46072</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57358,7 +57358,7 @@
         <v>46072</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57431,7 +57431,7 @@
         <v>46077</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57504,7 +57504,7 @@
         <v>45120</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57577,7 +57577,7 @@
         <v>46153</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57650,7 +57650,7 @@
         <v>45959</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57723,7 +57723,7 @@
         <v>46155</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57796,7 +57796,7 @@
         <v>45950</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57869,7 +57869,7 @@
         <v>46155</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -57942,7 +57942,7 @@
         <v>46155</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58015,7 +58015,7 @@
         <v>45916</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58088,7 +58088,7 @@
         <v>46160</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58166,7 +58166,7 @@
         <v>46160</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58239,7 +58239,7 @@
         <v>45679</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58312,7 +58312,7 @@
         <v>46157</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58385,7 +58385,7 @@
         <v>45707</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58458,7 +58458,7 @@
         <v>46160</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58531,7 +58531,7 @@
         <v>45433</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58604,7 +58604,7 @@
         <v>45947</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58677,7 +58677,7 @@
         <v>45947</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58750,7 +58750,7 @@
         <v>46098</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58823,7 +58823,7 @@
         <v>46047</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -58896,7 +58896,7 @@
         <v>46093</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -58969,7 +58969,7 @@
         <v>46161</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59042,7 +59042,7 @@
         <v>45947</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59115,7 +59115,7 @@
         <v>46094</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59188,7 +59188,7 @@
         <v>45728</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59261,7 +59261,7 @@
         <v>45957</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59334,7 +59334,7 @@
         <v>46064</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59407,7 +59407,7 @@
         <v>45959</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59480,7 +59480,7 @@
         <v>46164</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59553,7 +59553,7 @@
         <v>46164</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59626,7 +59626,7 @@
         <v>46163</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59699,7 +59699,7 @@
         <v>46163</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59772,7 +59772,7 @@
         <v>46164</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59845,7 +59845,7 @@
         <v>46146</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -59918,7 +59918,7 @@
         <v>45952</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -59991,7 +59991,7 @@
         <v>45981</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60064,7 +60064,7 @@
         <v>46168</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60137,7 +60137,7 @@
         <v>46167</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60210,7 +60210,7 @@
         <v>45173</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60283,7 +60283,7 @@
         <v>46169</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60356,7 +60356,7 @@
         <v>46168</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60429,7 +60429,7 @@
         <v>46170</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60502,7 +60502,7 @@
         <v>46174</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60575,7 +60575,7 @@
         <v>46174</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60648,7 +60648,7 @@
         <v>46174</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60721,7 +60721,7 @@
         <v>46174</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60794,7 +60794,7 @@
         <v>46174</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -60867,7 +60867,7 @@
         <v>46177</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -60940,7 +60940,7 @@
         <v>46176</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61013,7 +61013,7 @@
         <v>46176</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61086,7 +61086,7 @@
         <v>46181</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61164,7 +61164,7 @@
         <v>46181</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61237,7 +61237,7 @@
         <v>46181</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61310,7 +61310,7 @@
         <v>46181</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61383,7 +61383,7 @@
         <v>46181</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61456,7 +61456,7 @@
         <v>46181</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61529,7 +61529,7 @@
         <v>46188</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61602,7 +61602,7 @@
         <v>46188</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61680,7 +61680,7 @@
         <v>46188</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61753,7 +61753,7 @@
         <v>46190</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -61826,7 +61826,7 @@
         <v>46190</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -61899,7 +61899,7 @@
         <v>46190</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -61972,7 +61972,7 @@
         <v>46190</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62045,7 +62045,7 @@
         <v>46195</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62118,7 +62118,7 @@
         <v>46195</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62191,7 +62191,7 @@
         <v>46195</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62264,7 +62264,7 @@
         <v>46199</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62337,7 +62337,7 @@
         <v>46198</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62410,7 +62410,7 @@
         <v>46199</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62483,7 +62483,7 @@
         <v>46198</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62556,7 +62556,7 @@
         <v>46198</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62629,7 +62629,7 @@
         <v>46199</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62702,7 +62702,7 @@
         <v>46034</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62775,7 +62775,7 @@
         <v>46198</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -62848,7 +62848,7 @@
         <v>46204</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -62921,7 +62921,7 @@
         <v>46205</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -62994,7 +62994,7 @@
         <v>46209</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63067,7 +63067,7 @@
         <v>46209</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63140,7 +63140,7 @@
         <v>46209</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63213,7 +63213,7 @@
         <v>46210</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63286,7 +63286,7 @@
         <v>46210</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63359,7 +63359,7 @@
         <v>46265</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63437,7 +63437,7 @@
         <v>46265</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63510,7 +63510,7 @@
         <v>46265</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63588,7 +63588,7 @@
         <v>46265</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63666,7 +63666,7 @@
         <v>46140</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63739,7 +63739,7 @@
         <v>46265</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -63817,7 +63817,7 @@
         <v>46265</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -63890,7 +63890,7 @@
         <v>46265</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -63968,7 +63968,7 @@
         <v>46164</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64041,7 +64041,7 @@
         <v>46266</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64114,7 +64114,7 @@
         <v>46268</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64187,7 +64187,7 @@
         <v>46224</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64265,7 +64265,7 @@
         <v>46267</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64338,7 +64338,7 @@
         <v>45770</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64416,7 +64416,7 @@
         <v>46225</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64489,7 +64489,7 @@
         <v>46273</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64562,7 +64562,7 @@
         <v>46273</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64635,7 +64635,7 @@
         <v>46274</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64713,7 +64713,7 @@
         <v>46232</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -64786,7 +64786,7 @@
         <v>46237</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -64859,7 +64859,7 @@
         <v>46280</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -64932,7 +64932,7 @@
         <v>44854</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65005,7 +65005,7 @@
         <v>46237</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65078,7 +65078,7 @@
         <v>44540</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65151,7 +65151,7 @@
         <v>46280</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65224,7 +65224,7 @@
         <v>46238</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65297,7 +65297,7 @@
         <v>46238</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65370,7 +65370,7 @@
         <v>46281</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65443,7 +65443,7 @@
         <v>46240</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65516,7 +65516,7 @@
         <v>46239</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65589,7 +65589,7 @@
         <v>46239</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65662,7 +65662,7 @@
         <v>46281</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -65735,7 +65735,7 @@
         <v>46238</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -65808,7 +65808,7 @@
         <v>46284</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -65881,7 +65881,7 @@
         <v>46284</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -65954,7 +65954,7 @@
         <v>46283</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66027,7 +66027,7 @@
         <v>46241</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66105,7 +66105,7 @@
         <v>46287</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66178,7 +66178,7 @@
         <v>46288</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66256,7 +66256,7 @@
         <v>46266</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66329,7 +66329,7 @@
         <v>46244</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66402,7 +66402,7 @@
         <v>46287</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66475,7 +66475,7 @@
         <v>46287</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66548,7 +66548,7 @@
         <v>46244</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66621,7 +66621,7 @@
         <v>46247</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66699,7 +66699,7 @@
         <v>46289</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -66772,7 +66772,7 @@
         <v>46287</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -66845,7 +66845,7 @@
         <v>45750</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -66918,7 +66918,7 @@
         <v>46120</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -66991,7 +66991,7 @@
         <v>45803</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67064,7 +67064,7 @@
         <v>46248</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67142,7 +67142,7 @@
         <v>46248</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67215,7 +67215,7 @@
         <v>46239</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67288,7 +67288,7 @@
         <v>46266</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67361,7 +67361,7 @@
         <v>46253</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67434,7 +67434,7 @@
         <v>46251</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67507,7 +67507,7 @@
         <v>46253</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67585,7 +67585,7 @@
         <v>46251</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67663,7 +67663,7 @@
         <v>46253</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -67741,7 +67741,7 @@
         <v>46296</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -67819,7 +67819,7 @@
         <v>46296</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -67897,7 +67897,7 @@
         <v>46251</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -67970,7 +67970,7 @@
         <v>46253</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68043,7 +68043,7 @@
         <v>46253</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68116,7 +68116,7 @@
         <v>46266</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68189,7 +68189,7 @@
         <v>45734</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68262,7 +68262,7 @@
         <v>46254</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68335,7 +68335,7 @@
         <v>46254</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68408,7 +68408,7 @@
         <v>46300</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68481,7 +68481,7 @@
         <v>46300</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68554,7 +68554,7 @@
         <v>46254</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68632,7 +68632,7 @@
         <v>46254</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -68710,7 +68710,7 @@
         <v>46300</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -68783,7 +68783,7 @@
         <v>46256</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -68856,7 +68856,7 @@
         <v>46300</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -68934,7 +68934,7 @@
         <v>46274</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69007,7 +69007,7 @@
         <v>46256</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69080,7 +69080,7 @@
         <v>46297</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69153,7 +69153,7 @@
         <v>46298</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69226,7 +69226,7 @@
         <v>46268</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69299,7 +69299,7 @@
         <v>46258</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69377,7 +69377,7 @@
         <v>46300</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69450,7 +69450,7 @@
         <v>46301</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69523,7 +69523,7 @@
         <v>46301</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69596,7 +69596,7 @@
         <v>46304</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -69669,7 +69669,7 @@
         <v>46304</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -69742,7 +69742,7 @@
         <v>46266</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -69815,7 +69815,7 @@
         <v>46293</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -69888,7 +69888,7 @@
         <v>46262</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -69961,7 +69961,7 @@
         <v>46262</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70034,7 +70034,7 @@
         <v>46036</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70107,7 +70107,7 @@
         <v>46262</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70180,7 +70180,7 @@
         <v>45833</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70253,7 +70253,7 @@
         <v>46069</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70326,7 +70326,7 @@
         <v>44880</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70399,7 +70399,7 @@
         <v>44971</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70472,7 +70472,7 @@
         <v>45751</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70545,7 +70545,7 @@
         <v>45751</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -70623,7 +70623,7 @@
         <v>45790</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -70701,7 +70701,7 @@
         <v>46041</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -70774,7 +70774,7 @@
         <v>46078</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -70847,7 +70847,7 @@
         <v>46073</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -70920,7 +70920,7 @@
         <v>46142</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>

--- a/Översikt KRAMFORS.xlsx
+++ b/Översikt KRAMFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45544</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>46183</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>46029</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>46003</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>46094</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>46197</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>45763</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>44810</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>46196</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46287</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>45831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>45763</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>46197</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>46044</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>46241</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>46136</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>45056</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>46002</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>46203</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>45511</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>46181</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>45763</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>46196</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>46136</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45723</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>46265</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>44713</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>45399</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>45973</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>45985</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>45785</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>45484</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>45818</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>44524</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>45356</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>45660</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>45733</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>45996</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>44629</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>45957</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>45959</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>45516</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>45985</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>45282</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>46195</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>44813</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>46046</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>46258</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>45806</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>45818</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>45898</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>45898</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>46036</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>46178</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>45511</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         <v>45114</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>46273</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>45665</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>46241</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>46244</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>46254</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>45551</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>45786</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>45182</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>45468</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>45729</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>45840</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>45750</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>45156</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>45645</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>45344</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>45764</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>44965</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>45670</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>45924</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>44852</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>45943</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>45199</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>44803</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>45979</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>45998</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>46020</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>46021</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>46024</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>46030</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>46048</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>46071</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
         <v>46098</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>45764</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>46281</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>45243</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>45114</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>45636</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>45400</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>45071</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>44817</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>44804</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>44634</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>44859</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>44508</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>44508</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>44594</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>44608</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>44509</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>44496</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>44511</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>44587</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>44592</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>44592</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         <v>44722</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12352,7 +12352,7 @@
         <v>44688</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>44556</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12498,7 +12498,7 @@
         <v>44852</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         <v>44817</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>44817</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>44508</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>44762</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>44509</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>44859</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>44581</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>44516</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>44509</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>44539</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>44566</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>44687</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>44594</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>44719</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>44715</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>44803</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         <v>44629</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         <v>44594</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>44802</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>44509</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>44540</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>44550</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>44607</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>44876</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>44628</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>44616</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         <v>44749</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>44697</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>44581</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>44503</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44859</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
         <v>44601</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>44782</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14980,7 +14980,7 @@
         <v>44581</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>44804</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>45365</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>45534</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>44958</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>44978</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>45279</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>44610</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>45588</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15637,7 +15637,7 @@
         <v>45588</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15710,7 +15710,7 @@
         <v>45588</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>45440</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
         <v>45124</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>44608</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>44634</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         <v>45205</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>44629</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>44991</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>45664</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>45721</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>44958</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16523,7 +16523,7 @@
         <v>44573</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>45307</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>45148</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16742,7 +16742,7 @@
         <v>45190</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>44830</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>45000</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>45265</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>45712</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>45329</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>45526</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>45327</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>45099</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>45225</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>45518</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>45483</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>45724</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17696,7 +17696,7 @@
         <v>45232</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>45482</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>44958</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>44792</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45351</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>44909</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>45512</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         <v>45491</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>45202</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>45754</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>45225</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>45461</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>45469</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>45623</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>45623</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>44879</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>45345</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>45323</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>44606</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
         <v>45433</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
         <v>44956</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19259,7 +19259,7 @@
         <v>45294</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>44946</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>44546</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19478,7 +19478,7 @@
         <v>45273</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>44998</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19624,7 +19624,7 @@
         <v>45085</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19697,7 +19697,7 @@
         <v>45034</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>44574</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>45757</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>44826</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>45000</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>45153</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>45153</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>45273</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44908</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>45008</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         <v>44949</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>45714</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>44503</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>45685</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>45685</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20822,7 +20822,7 @@
         <v>45036</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
         <v>44894</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>45883</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>45883</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>45883</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>45883</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21260,7 +21260,7 @@
         <v>45733</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>45943</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>45425</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21479,7 +21479,7 @@
         <v>46029</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>46136</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>45797</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>46069</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21771,7 +21771,7 @@
         <v>44942</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>45959</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>44965</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         <v>44965</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22063,7 +22063,7 @@
         <v>45707</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>45616</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
         <v>45324</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22282,7 +22282,7 @@
         <v>45888</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22355,7 +22355,7 @@
         <v>45973</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>45890</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>45672</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>45960</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>45890</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>45821</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>45890</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>45674</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>45684</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23012,7 +23012,7 @@
         <v>45909</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>45754</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>45524</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>45898</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>45247</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>45901</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23455,7 +23455,7 @@
         <v>45589</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>45841</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>45898</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>45898</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23747,7 +23747,7 @@
         <v>45898</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23820,7 +23820,7 @@
         <v>45881</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23893,7 +23893,7 @@
         <v>45894</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>46107</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24039,7 +24039,7 @@
         <v>45901</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>45771</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>45898</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24258,7 +24258,7 @@
         <v>45901</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>45685</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>45989</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>45898</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>45898</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>45959</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>45898</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>45544</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>46084</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>45898</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>45898</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>45876</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>45842</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>46064</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         <v>44855</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>45875</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>45931</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>45173</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>45008</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>45726</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>45454</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>45818</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45896</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>45636</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>45909</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         <v>45813</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>45553</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>45909</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>45909</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>46140</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>44574</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26521,7 +26521,7 @@
         <v>46142</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>45043</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         <v>45912</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26745,7 +26745,7 @@
         <v>45918</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>46147</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>46146</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>45554</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>46146</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>45729</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>44727</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27261,7 +27261,7 @@
         <v>45475</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>45062</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>45513</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>46148</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         <v>45926</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>45926</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27704,7 +27704,7 @@
         <v>44840</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>44852</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27850,7 +27850,7 @@
         <v>44519</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27923,7 +27923,7 @@
         <v>45120</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27996,7 +27996,7 @@
         <v>45932</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>45282</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>46153</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>45935</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>45936</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28371,7 +28371,7 @@
         <v>45280</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>45937</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28517,7 +28517,7 @@
         <v>45698</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>45644</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>45936</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28736,7 +28736,7 @@
         <v>45937</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>44782</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>45943</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>44943</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>45278</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>45950</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>45946</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>45947</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>45744</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>45951</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>46155</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>45418</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>45959</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>45952</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>45952</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>45190</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>46155</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>46155</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>44883</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>45957</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>46157</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>45433</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>44774</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>46098</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>45541</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>45960</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45355</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45964</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>45964</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>45964</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>45964</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31019,7 +31019,7 @@
         <v>45964</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31097,7 +31097,7 @@
         <v>46160</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>45964</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>45964</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31321,7 +31321,7 @@
         <v>44747</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31394,7 +31394,7 @@
         <v>45964</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>45950</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31540,7 +31540,7 @@
         <v>46064</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31613,7 +31613,7 @@
         <v>45950</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>45947</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>45947</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31832,7 +31832,7 @@
         <v>45884</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>45679</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>45707</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>45959</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32124,7 +32124,7 @@
         <v>46160</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32202,7 +32202,7 @@
         <v>46160</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32275,7 +32275,7 @@
         <v>45916</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>45968</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>46161</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>45968</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>45971</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32640,7 +32640,7 @@
         <v>45638</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
         <v>45957</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32786,7 +32786,7 @@
         <v>45728</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32859,7 +32859,7 @@
         <v>45974</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32932,7 +32932,7 @@
         <v>45974</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33005,7 +33005,7 @@
         <v>45947</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>45974</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>46163</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>45974</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33297,7 +33297,7 @@
         <v>45974</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>45974</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>45974</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33516,7 +33516,7 @@
         <v>45979</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>45979</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33662,7 +33662,7 @@
         <v>46047</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33735,7 +33735,7 @@
         <v>45979</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33808,7 +33808,7 @@
         <v>45672</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33881,7 +33881,7 @@
         <v>45740</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>45680</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>45979</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34100,7 +34100,7 @@
         <v>45979</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34173,7 +34173,7 @@
         <v>46163</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>45979</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34319,7 +34319,7 @@
         <v>45981</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34392,7 +34392,7 @@
         <v>45674</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34465,7 +34465,7 @@
         <v>44956</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34538,7 +34538,7 @@
         <v>44956</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34611,7 +34611,7 @@
         <v>44897</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34684,7 +34684,7 @@
         <v>46164</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34757,7 +34757,7 @@
         <v>45981</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>45981</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34903,7 +34903,7 @@
         <v>46167</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34976,7 +34976,7 @@
         <v>45743</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35049,7 +35049,7 @@
         <v>45261</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35122,7 +35122,7 @@
         <v>45294</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>45982</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35268,7 +35268,7 @@
         <v>45982</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35341,7 +35341,7 @@
         <v>45561</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35414,7 +35414,7 @@
         <v>44834</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35487,7 +35487,7 @@
         <v>46164</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35560,7 +35560,7 @@
         <v>45986</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>45987</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35706,7 +35706,7 @@
         <v>46164</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35779,7 +35779,7 @@
         <v>45987</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35852,7 +35852,7 @@
         <v>45988</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35925,7 +35925,7 @@
         <v>45750</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35998,7 +35998,7 @@
         <v>45988</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>45320</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
         <v>44803</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36217,7 +36217,7 @@
         <v>45952</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36290,7 +36290,7 @@
         <v>45392</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>46146</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>46168</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36509,7 +36509,7 @@
         <v>46169</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>45044</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36655,7 +36655,7 @@
         <v>45173</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>46168</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>45994</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>45496</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36952,7 +36952,7 @@
         <v>45999</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37025,7 +37025,7 @@
         <v>45999</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37098,7 +37098,7 @@
         <v>45959</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37171,7 +37171,7 @@
         <v>45758</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37244,7 +37244,7 @@
         <v>45996</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37317,7 +37317,7 @@
         <v>46000</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>46000</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37463,7 +37463,7 @@
         <v>45981</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37536,7 +37536,7 @@
         <v>46000</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>46001</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>44813</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>46170</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37828,7 +37828,7 @@
         <v>45763</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37906,7 +37906,7 @@
         <v>46002</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37979,7 +37979,7 @@
         <v>45328</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38057,7 +38057,7 @@
         <v>45764</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38130,7 +38130,7 @@
         <v>46007</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>46007</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38276,7 +38276,7 @@
         <v>46009</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38349,7 +38349,7 @@
         <v>46008</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>45476</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>46009</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>44901</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>44804</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>46008</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>46009</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>45545</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>46008</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>46008</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>46008</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>46008</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>46174</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>46008</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39371,7 +39371,7 @@
         <v>46009</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>46009</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>45763</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>45763</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>45502</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>44529</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>46174</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>46014</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>46174</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>46174</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40111,7 +40111,7 @@
         <v>45336</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40184,7 +40184,7 @@
         <v>46022</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40257,7 +40257,7 @@
         <v>46024</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40330,7 +40330,7 @@
         <v>46024</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40403,7 +40403,7 @@
         <v>46174</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>46024</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40549,7 +40549,7 @@
         <v>46024</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40622,7 +40622,7 @@
         <v>46029</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40695,7 +40695,7 @@
         <v>46031</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40768,7 +40768,7 @@
         <v>44956</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40841,7 +40841,7 @@
         <v>46031</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40914,7 +40914,7 @@
         <v>44959</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>46034</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>44915</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>46176</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>46176</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>46041</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41357,7 +41357,7 @@
         <v>46041</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>46041</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41503,7 +41503,7 @@
         <v>46177</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41576,7 +41576,7 @@
         <v>46043</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>46043</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41722,7 +41722,7 @@
         <v>46043</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41795,7 +41795,7 @@
         <v>46043</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41868,7 +41868,7 @@
         <v>46042</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>46043</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42014,7 +42014,7 @@
         <v>45278</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>46044</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42165,7 +42165,7 @@
         <v>46044</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42238,7 +42238,7 @@
         <v>46181</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42311,7 +42311,7 @@
         <v>46049</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42384,7 +42384,7 @@
         <v>46181</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>46048</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42530,7 +42530,7 @@
         <v>46181</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42603,7 +42603,7 @@
         <v>46181</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42676,7 +42676,7 @@
         <v>46049</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42749,7 +42749,7 @@
         <v>46046</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42822,7 +42822,7 @@
         <v>46049</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42895,7 +42895,7 @@
         <v>46043</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>46046</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43041,7 +43041,7 @@
         <v>45552</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43114,7 +43114,7 @@
         <v>46046</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43187,7 +43187,7 @@
         <v>46047</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>45771</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43333,7 +43333,7 @@
         <v>45771</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>44739</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43479,7 +43479,7 @@
         <v>46181</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43557,7 +43557,7 @@
         <v>46054</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43630,7 +43630,7 @@
         <v>45034</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>46046</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>46054</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43849,7 +43849,7 @@
         <v>46054</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43922,7 +43922,7 @@
         <v>46046</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>46181</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44068,7 +44068,7 @@
         <v>44872</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44141,7 +44141,7 @@
         <v>45474</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44214,7 +44214,7 @@
         <v>45546</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44287,7 +44287,7 @@
         <v>44775</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44360,7 +44360,7 @@
         <v>46063</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44433,7 +44433,7 @@
         <v>46063</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44506,7 +44506,7 @@
         <v>46062</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>46069</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44652,7 +44652,7 @@
         <v>45300</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44725,7 +44725,7 @@
         <v>45608</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44798,7 +44798,7 @@
         <v>46188</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44871,7 +44871,7 @@
         <v>44529</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44944,7 +44944,7 @@
         <v>46043</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45017,7 +45017,7 @@
         <v>45712</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45090,7 +45090,7 @@
         <v>46188</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45163,7 +45163,7 @@
         <v>46071</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45236,7 +45236,7 @@
         <v>46072</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45309,7 +45309,7 @@
         <v>46188</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>45034</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>45040</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>46072</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45606,7 +45606,7 @@
         <v>44741</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45679,7 +45679,7 @@
         <v>46077</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45752,7 +45752,7 @@
         <v>44894</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45825,7 +45825,7 @@
         <v>45265</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>46190</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>46190</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46044,7 +46044,7 @@
         <v>46190</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46117,7 +46117,7 @@
         <v>46190</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>44571</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46263,7 +46263,7 @@
         <v>45034</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>46094</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>46093</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46482,7 +46482,7 @@
         <v>45664</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46555,7 +46555,7 @@
         <v>46052</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46628,7 +46628,7 @@
         <v>46098</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46701,7 +46701,7 @@
         <v>45572</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46774,7 +46774,7 @@
         <v>46098</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46847,7 +46847,7 @@
         <v>44556</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46920,7 +46920,7 @@
         <v>45182</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46993,7 +46993,7 @@
         <v>46099</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47071,7 +47071,7 @@
         <v>46195</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47144,7 +47144,7 @@
         <v>46100</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47217,7 +47217,7 @@
         <v>46195</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47290,7 +47290,7 @@
         <v>46104</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47363,7 +47363,7 @@
         <v>46104</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47436,7 +47436,7 @@
         <v>45161</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>46105</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47582,7 +47582,7 @@
         <v>45302</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47655,7 +47655,7 @@
         <v>44916</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47728,7 +47728,7 @@
         <v>46195</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47801,7 +47801,7 @@
         <v>45425</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47879,7 +47879,7 @@
         <v>45763</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47957,7 +47957,7 @@
         <v>45044</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48030,7 +48030,7 @@
         <v>46198</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48103,7 +48103,7 @@
         <v>46198</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>46198</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48249,7 +48249,7 @@
         <v>46198</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45674</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48395,7 +48395,7 @@
         <v>45356</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48468,7 +48468,7 @@
         <v>44971</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>45450</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48614,7 +48614,7 @@
         <v>46119</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48687,7 +48687,7 @@
         <v>45660</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48760,7 +48760,7 @@
         <v>45173</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45419</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48906,7 +48906,7 @@
         <v>45729</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48979,7 +48979,7 @@
         <v>46199</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49052,7 +49052,7 @@
         <v>46199</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49125,7 +49125,7 @@
         <v>46071</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49198,7 +49198,7 @@
         <v>46034</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49271,7 +49271,7 @@
         <v>45513</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49344,7 +49344,7 @@
         <v>46127</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>46128</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49490,7 +49490,7 @@
         <v>46112</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49563,7 +49563,7 @@
         <v>46127</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49636,7 +49636,7 @@
         <v>45764</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49714,7 +49714,7 @@
         <v>45420</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49787,7 +49787,7 @@
         <v>45632</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>46199</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49933,7 +49933,7 @@
         <v>45189</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50006,7 +50006,7 @@
         <v>46204</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50079,7 +50079,7 @@
         <v>44880</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50152,7 +50152,7 @@
         <v>45163</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50230,7 +50230,7 @@
         <v>46134</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>46134</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50376,7 +50376,7 @@
         <v>46205</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50449,7 +50449,7 @@
         <v>45239</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45645</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50595,7 +50595,7 @@
         <v>45579</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50673,7 +50673,7 @@
         <v>45538</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>45450</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50819,7 +50819,7 @@
         <v>44769</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>44965</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50965,7 +50965,7 @@
         <v>45724</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51038,7 +51038,7 @@
         <v>45365</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51111,7 +51111,7 @@
         <v>46209</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51184,7 +51184,7 @@
         <v>46209</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51257,7 +51257,7 @@
         <v>46209</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51330,7 +51330,7 @@
         <v>46210</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51403,7 +51403,7 @@
         <v>46210</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51476,7 +51476,7 @@
         <v>44888</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51549,7 +51549,7 @@
         <v>44908</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51622,7 +51622,7 @@
         <v>45365</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51695,7 +51695,7 @@
         <v>45034</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51768,7 +51768,7 @@
         <v>46164</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51841,7 +51841,7 @@
         <v>46140</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51914,7 +51914,7 @@
         <v>45770</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51992,7 +51992,7 @@
         <v>46224</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52070,7 +52070,7 @@
         <v>46225</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52143,7 +52143,7 @@
         <v>44536</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52221,7 +52221,7 @@
         <v>44613</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52299,7 +52299,7 @@
         <v>44608</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52372,7 +52372,7 @@
         <v>46273</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52445,7 +52445,7 @@
         <v>46273</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52518,7 +52518,7 @@
         <v>45764</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52596,7 +52596,7 @@
         <v>45726</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52669,7 +52669,7 @@
         <v>46274</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52747,7 +52747,7 @@
         <v>44880</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52820,7 +52820,7 @@
         <v>45589</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52893,7 +52893,7 @@
         <v>46232</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52966,7 +52966,7 @@
         <v>45034</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53039,7 +53039,7 @@
         <v>45365</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53112,7 +53112,7 @@
         <v>45089</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53185,7 +53185,7 @@
         <v>46281</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53258,7 +53258,7 @@
         <v>44853</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53331,7 +53331,7 @@
         <v>45366</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53404,7 +53404,7 @@
         <v>45684</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>44854</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53550,7 +53550,7 @@
         <v>44540</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53623,7 +53623,7 @@
         <v>45680</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53696,7 +53696,7 @@
         <v>46280</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53769,7 +53769,7 @@
         <v>44865</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53842,7 +53842,7 @@
         <v>45390</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53915,7 +53915,7 @@
         <v>46237</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53988,7 +53988,7 @@
         <v>46238</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54061,7 +54061,7 @@
         <v>46238</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54134,7 +54134,7 @@
         <v>46280</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54207,7 +54207,7 @@
         <v>46238</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54280,7 +54280,7 @@
         <v>46237</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54353,7 +54353,7 @@
         <v>45324</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54426,7 +54426,7 @@
         <v>45447</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54499,7 +54499,7 @@
         <v>46281</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54572,7 +54572,7 @@
         <v>45236</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>44537</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54718,7 +54718,7 @@
         <v>45723</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54791,7 +54791,7 @@
         <v>45713</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54864,7 +54864,7 @@
         <v>46239</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54937,7 +54937,7 @@
         <v>46240</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55010,7 +55010,7 @@
         <v>45236</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55083,7 +55083,7 @@
         <v>45162</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55156,7 +55156,7 @@
         <v>45062</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55229,7 +55229,7 @@
         <v>44750</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55302,7 +55302,7 @@
         <v>45240</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55375,7 +55375,7 @@
         <v>46239</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55448,7 +55448,7 @@
         <v>46283</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55521,7 +55521,7 @@
         <v>44958</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55594,7 +55594,7 @@
         <v>45678</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55667,7 +55667,7 @@
         <v>45189</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55740,7 +55740,7 @@
         <v>46266</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55813,7 +55813,7 @@
         <v>45392</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55886,7 +55886,7 @@
         <v>45237</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -55959,7 +55959,7 @@
         <v>44907</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56032,7 +56032,7 @@
         <v>46287</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56105,7 +56105,7 @@
         <v>45198</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56183,7 +56183,7 @@
         <v>46284</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56256,7 +56256,7 @@
         <v>46284</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56329,7 +56329,7 @@
         <v>45324</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56402,7 +56402,7 @@
         <v>46244</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56475,7 +56475,7 @@
         <v>45209</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56548,7 +56548,7 @@
         <v>45162</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56621,7 +56621,7 @@
         <v>45162</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56694,7 +56694,7 @@
         <v>46241</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56772,7 +56772,7 @@
         <v>46244</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56845,7 +56845,7 @@
         <v>46287</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -56918,7 +56918,7 @@
         <v>45520</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -56991,7 +56991,7 @@
         <v>46287</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57064,7 +57064,7 @@
         <v>46288</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57142,7 +57142,7 @@
         <v>45271</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57215,7 +57215,7 @@
         <v>46287</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57288,7 +57288,7 @@
         <v>44824</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57361,7 +57361,7 @@
         <v>45320</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57439,7 +57439,7 @@
         <v>44573</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57512,7 +57512,7 @@
         <v>46289</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57585,7 +57585,7 @@
         <v>45750</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57658,7 +57658,7 @@
         <v>44574</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57731,7 +57731,7 @@
         <v>46248</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57804,7 +57804,7 @@
         <v>45273</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -57877,7 +57877,7 @@
         <v>45519</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -57950,7 +57950,7 @@
         <v>44819</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58023,7 +58023,7 @@
         <v>46247</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58101,7 +58101,7 @@
         <v>44638</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58174,7 +58174,7 @@
         <v>45803</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58247,7 +58247,7 @@
         <v>46248</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58325,7 +58325,7 @@
         <v>45763</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58403,7 +58403,7 @@
         <v>45099</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58476,7 +58476,7 @@
         <v>46120</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58549,7 +58549,7 @@
         <v>45365</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58622,7 +58622,7 @@
         <v>45180</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58695,7 +58695,7 @@
         <v>46251</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58768,7 +58768,7 @@
         <v>46251</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -58841,7 +58841,7 @@
         <v>45400</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -58914,7 +58914,7 @@
         <v>44860</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -58987,7 +58987,7 @@
         <v>45099</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59060,7 +59060,7 @@
         <v>45232</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59138,7 +59138,7 @@
         <v>46251</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59216,7 +59216,7 @@
         <v>46254</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59294,7 +59294,7 @@
         <v>45271</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59367,7 +59367,7 @@
         <v>45328</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59440,7 +59440,7 @@
         <v>46254</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59513,7 +59513,7 @@
         <v>44788</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59586,7 +59586,7 @@
         <v>46296</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59664,7 +59664,7 @@
         <v>46253</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59737,7 +59737,7 @@
         <v>46296</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59815,7 +59815,7 @@
         <v>46239</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -59888,7 +59888,7 @@
         <v>46253</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -59966,7 +59966,7 @@
         <v>46254</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60044,7 +60044,7 @@
         <v>46297</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60117,7 +60117,7 @@
         <v>46253</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60190,7 +60190,7 @@
         <v>46274</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60263,7 +60263,7 @@
         <v>46254</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60336,7 +60336,7 @@
         <v>46253</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60409,7 +60409,7 @@
         <v>46253</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60487,7 +60487,7 @@
         <v>44564</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60560,7 +60560,7 @@
         <v>46300</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60633,7 +60633,7 @@
         <v>45034</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60706,7 +60706,7 @@
         <v>46300</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60779,7 +60779,7 @@
         <v>44998</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -60852,7 +60852,7 @@
         <v>46258</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -60930,7 +60930,7 @@
         <v>45645</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61003,7 +61003,7 @@
         <v>45645</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61076,7 +61076,7 @@
         <v>45776</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61154,7 +61154,7 @@
         <v>45734</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61227,7 +61227,7 @@
         <v>46256</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61300,7 +61300,7 @@
         <v>46300</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61373,7 +61373,7 @@
         <v>46300</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61446,7 +61446,7 @@
         <v>45782</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61519,7 +61519,7 @@
         <v>46300</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61597,7 +61597,7 @@
         <v>46301</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61670,7 +61670,7 @@
         <v>45496</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61748,7 +61748,7 @@
         <v>46256</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -61821,7 +61821,7 @@
         <v>46298</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -61894,7 +61894,7 @@
         <v>45408</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -61967,7 +61967,7 @@
         <v>45476</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62040,7 +62040,7 @@
         <v>44834</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62118,7 +62118,7 @@
         <v>45281</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62191,7 +62191,7 @@
         <v>45306</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62264,7 +62264,7 @@
         <v>46293</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62337,7 +62337,7 @@
         <v>45791</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62410,7 +62410,7 @@
         <v>45496</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62488,7 +62488,7 @@
         <v>45231</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62561,7 +62561,7 @@
         <v>45790</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62634,7 +62634,7 @@
         <v>45169</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62707,7 +62707,7 @@
         <v>45618</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62780,7 +62780,7 @@
         <v>45567</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -62853,7 +62853,7 @@
         <v>45792</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -62926,7 +62926,7 @@
         <v>45418</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -62999,7 +62999,7 @@
         <v>45415</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63072,7 +63072,7 @@
         <v>46262</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63145,7 +63145,7 @@
         <v>44503</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63218,7 +63218,7 @@
         <v>44804</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63291,7 +63291,7 @@
         <v>45435</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63369,7 +63369,7 @@
         <v>45797</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63442,7 +63442,7 @@
         <v>45552</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63515,7 +63515,7 @@
         <v>45797</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63588,7 +63588,7 @@
         <v>46304</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63661,7 +63661,7 @@
         <v>45798</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63739,7 +63739,7 @@
         <v>46301</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -63812,7 +63812,7 @@
         <v>45833</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -63885,7 +63885,7 @@
         <v>45799</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -63963,7 +63963,7 @@
         <v>46069</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64036,7 +64036,7 @@
         <v>46262</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64109,7 +64109,7 @@
         <v>46307</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64182,7 +64182,7 @@
         <v>45799</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64260,7 +64260,7 @@
         <v>44903</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64333,7 +64333,7 @@
         <v>45799</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64406,7 +64406,7 @@
         <v>46304</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64479,7 +64479,7 @@
         <v>46265</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64557,7 +64557,7 @@
         <v>46265</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64635,7 +64635,7 @@
         <v>46265</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64713,7 +64713,7 @@
         <v>46309</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -64786,7 +64786,7 @@
         <v>46266</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -64859,7 +64859,7 @@
         <v>46265</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -64932,7 +64932,7 @@
         <v>46262</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65005,7 +65005,7 @@
         <v>46266</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65078,7 +65078,7 @@
         <v>45475</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65151,7 +65151,7 @@
         <v>44834</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65229,7 +65229,7 @@
         <v>45036</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65302,7 +65302,7 @@
         <v>46266</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65375,7 +65375,7 @@
         <v>46266</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65448,7 +65448,7 @@
         <v>45805</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65521,7 +65521,7 @@
         <v>45805</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65594,7 +65594,7 @@
         <v>45643</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65667,7 +65667,7 @@
         <v>45807</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -65745,7 +65745,7 @@
         <v>46265</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -65823,7 +65823,7 @@
         <v>45726</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -65896,7 +65896,7 @@
         <v>45734</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -65969,7 +65969,7 @@
         <v>45654</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66042,7 +66042,7 @@
         <v>46265</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66120,7 +66120,7 @@
         <v>45712</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66193,7 +66193,7 @@
         <v>45678</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66266,7 +66266,7 @@
         <v>46265</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66339,7 +66339,7 @@
         <v>46036</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66412,7 +66412,7 @@
         <v>46307</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66485,7 +66485,7 @@
         <v>46267</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66558,7 +66558,7 @@
         <v>46268</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66631,7 +66631,7 @@
         <v>45593</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66704,7 +66704,7 @@
         <v>45813</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -66777,7 +66777,7 @@
         <v>45782</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -66850,7 +66850,7 @@
         <v>45813</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -66923,7 +66923,7 @@
         <v>45653</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -66996,7 +66996,7 @@
         <v>45753</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67069,7 +67069,7 @@
         <v>46268</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67142,7 +67142,7 @@
         <v>45768</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67215,7 +67215,7 @@
         <v>45818</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67293,7 +67293,7 @@
         <v>45819</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67366,7 +67366,7 @@
         <v>45825</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67439,7 +67439,7 @@
         <v>45825</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67512,7 +67512,7 @@
         <v>45825</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67585,7 +67585,7 @@
         <v>45825</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67658,7 +67658,7 @@
         <v>45825</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -67731,7 +67731,7 @@
         <v>45825</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -67804,7 +67804,7 @@
         <v>45825</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -67877,7 +67877,7 @@
         <v>45825</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -67950,7 +67950,7 @@
         <v>45825</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68023,7 +68023,7 @@
         <v>45825</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68096,7 +68096,7 @@
         <v>46309</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68169,7 +68169,7 @@
         <v>46310</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68242,7 +68242,7 @@
         <v>45833</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68320,7 +68320,7 @@
         <v>45832</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68393,7 +68393,7 @@
         <v>45834</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68471,7 +68471,7 @@
         <v>45838</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68544,7 +68544,7 @@
         <v>45838</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68622,7 +68622,7 @@
         <v>45841</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -68700,7 +68700,7 @@
         <v>45840</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -68778,7 +68778,7 @@
         <v>45841</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -68856,7 +68856,7 @@
         <v>45840</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -68929,7 +68929,7 @@
         <v>45840</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69007,7 +69007,7 @@
         <v>45841</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69080,7 +69080,7 @@
         <v>45841</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69153,7 +69153,7 @@
         <v>45842</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69226,7 +69226,7 @@
         <v>45852</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69299,7 +69299,7 @@
         <v>45855</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69372,7 +69372,7 @@
         <v>45799</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69445,7 +69445,7 @@
         <v>45859</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69518,7 +69518,7 @@
         <v>45860</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69591,7 +69591,7 @@
         <v>45799</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -69664,7 +69664,7 @@
         <v>45749</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -69737,7 +69737,7 @@
         <v>45825</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -69810,7 +69810,7 @@
         <v>45873</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -69883,7 +69883,7 @@
         <v>45875</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -69956,7 +69956,7 @@
         <v>45874</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70029,7 +70029,7 @@
         <v>45874</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70102,7 +70102,7 @@
         <v>45874</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70175,7 +70175,7 @@
         <v>45876</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70248,7 +70248,7 @@
         <v>45881</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70321,7 +70321,7 @@
         <v>45881</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70394,7 +70394,7 @@
         <v>44971</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70467,7 +70467,7 @@
         <v>45751</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70540,7 +70540,7 @@
         <v>45751</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -70618,7 +70618,7 @@
         <v>45790</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -70696,7 +70696,7 @@
         <v>46041</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -70769,7 +70769,7 @@
         <v>46078</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -70842,7 +70842,7 @@
         <v>46073</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -70915,7 +70915,7 @@
         <v>46142</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -70988,7 +70988,7 @@
         <v>44880</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>

--- a/Översikt KRAMFORS.xlsx
+++ b/Översikt KRAMFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45544</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>46183</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>46029</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>46003</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>46094</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>46197</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>45763</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>44810</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>46196</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46287</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>45831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>45763</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>46197</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>46044</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>46241</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>46136</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>45056</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>46002</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>46203</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>45511</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>46181</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>45763</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>46196</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>46136</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45723</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>46265</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>44713</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>45399</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>45973</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>45985</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>45785</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>45484</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>45818</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>44524</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>45356</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>45660</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>45733</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>45996</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>44629</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>45957</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>45959</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>45516</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>45985</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>45282</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>46195</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>44813</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>46046</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>46258</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>45806</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>45818</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>45898</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>45898</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>46036</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>46178</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>45511</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         <v>45114</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>46273</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>45665</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>46241</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>46244</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>46254</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>45551</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>45786</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>45182</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>45468</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>45729</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>45840</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>45750</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>45156</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>45645</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>45344</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>45764</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>44965</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>45670</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>45924</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>44852</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>45943</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>45199</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>44803</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>45979</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>45998</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>46020</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>46021</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>46024</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>46030</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>46048</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>46071</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
         <v>46098</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>45764</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>46281</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>45243</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>45114</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>45636</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>45400</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>45071</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>44817</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>44804</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>44634</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>44859</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>44508</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>44508</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>44594</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>44608</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>44509</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>44496</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>44511</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>44587</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>44592</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>44592</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         <v>44722</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12352,7 +12352,7 @@
         <v>44688</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>44556</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12498,7 +12498,7 @@
         <v>44852</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         <v>44817</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>44817</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>44508</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>44762</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>44509</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>44859</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>44581</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>44516</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>44509</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>44539</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>44566</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>44687</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>44594</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>44719</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>44715</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>44803</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         <v>44629</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         <v>44594</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>44802</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>44509</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>44540</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>44550</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>44607</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>44876</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>44628</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>44616</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         <v>44749</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>44697</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>44581</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>44503</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44859</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
         <v>44601</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>44782</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14980,7 +14980,7 @@
         <v>44581</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>44804</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>45365</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>45534</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>44958</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>44978</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>45279</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>44610</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>45588</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15637,7 +15637,7 @@
         <v>45588</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15710,7 +15710,7 @@
         <v>45588</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>45440</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
         <v>45124</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>44608</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>44634</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         <v>45205</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>44629</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>44991</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>45664</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>45721</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>44958</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16523,7 +16523,7 @@
         <v>44573</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>45307</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>45148</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16742,7 +16742,7 @@
         <v>45190</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>44830</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>45000</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>45265</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>45712</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>45329</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>45526</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>45327</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>45099</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>45225</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>45518</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>45483</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>45724</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17696,7 +17696,7 @@
         <v>45232</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>45482</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>44958</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>44792</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45351</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>44909</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>45512</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         <v>45491</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>45202</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>45754</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>45225</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>45461</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>45469</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>45623</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>45623</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>44879</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>45345</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>45323</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>44606</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
         <v>45433</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
         <v>44956</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19259,7 +19259,7 @@
         <v>45294</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>44946</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>44546</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19478,7 +19478,7 @@
         <v>45273</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>44998</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19624,7 +19624,7 @@
         <v>45085</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19697,7 +19697,7 @@
         <v>45034</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>44574</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>45757</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>44826</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>45000</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>45153</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>45153</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>45273</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44908</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>45008</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         <v>44949</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>45714</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>44503</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>45685</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>45685</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20822,7 +20822,7 @@
         <v>45036</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
         <v>44894</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>45883</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>45883</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>45883</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>45883</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21260,7 +21260,7 @@
         <v>45733</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>45943</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>45425</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21479,7 +21479,7 @@
         <v>46029</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>46136</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>45797</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>46069</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21771,7 +21771,7 @@
         <v>44942</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>45959</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>44965</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         <v>44965</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22063,7 +22063,7 @@
         <v>45707</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>45616</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
         <v>45324</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22282,7 +22282,7 @@
         <v>45888</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22355,7 +22355,7 @@
         <v>45973</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>45890</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>45672</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>45960</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>45890</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>45821</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>45890</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>45674</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>45684</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23012,7 +23012,7 @@
         <v>45909</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>45754</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>45524</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>45898</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>45247</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>45901</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23455,7 +23455,7 @@
         <v>45589</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>45841</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>45898</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>45898</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23747,7 +23747,7 @@
         <v>45898</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23820,7 +23820,7 @@
         <v>45881</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23893,7 +23893,7 @@
         <v>45894</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>46107</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24039,7 +24039,7 @@
         <v>45901</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>45771</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>45898</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24258,7 +24258,7 @@
         <v>45901</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>45685</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>45989</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>45898</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>45898</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>45959</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>45898</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>45544</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>46084</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>45898</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>45898</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>45876</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>45842</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>46064</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         <v>44855</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>45875</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>45931</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>45173</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>45008</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>45726</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>45454</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>45818</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45896</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>45636</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>45909</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         <v>45813</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>45553</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>45909</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>45909</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>46140</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>44574</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26521,7 +26521,7 @@
         <v>46142</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>45043</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         <v>45912</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26745,7 +26745,7 @@
         <v>45918</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>46147</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>46146</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>45554</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>46146</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>45729</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>44727</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27261,7 +27261,7 @@
         <v>45475</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>45062</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>45513</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>46148</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         <v>45926</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>45926</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27704,7 +27704,7 @@
         <v>44840</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>44852</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27850,7 +27850,7 @@
         <v>44519</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27923,7 +27923,7 @@
         <v>45120</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27996,7 +27996,7 @@
         <v>45932</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>45282</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>46153</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>45935</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>45936</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28371,7 +28371,7 @@
         <v>45280</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>45937</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28517,7 +28517,7 @@
         <v>45698</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>45644</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>45936</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28736,7 +28736,7 @@
         <v>45937</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>44782</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>45943</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>44943</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>45278</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>45950</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>45946</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>45947</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>45744</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>45951</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>46155</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>45418</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>45959</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>45952</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>45952</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>45190</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>46155</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>46155</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>44883</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>45957</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>46157</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>45433</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>44774</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>46098</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>45541</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>45960</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45355</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45964</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>45964</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>45964</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>45964</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31019,7 +31019,7 @@
         <v>45964</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31097,7 +31097,7 @@
         <v>46160</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>45964</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>45964</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31321,7 +31321,7 @@
         <v>44747</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31394,7 +31394,7 @@
         <v>45964</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>45950</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31540,7 +31540,7 @@
         <v>46064</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31613,7 +31613,7 @@
         <v>45950</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>45947</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>45947</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31832,7 +31832,7 @@
         <v>45884</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>45679</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>45707</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>45959</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32124,7 +32124,7 @@
         <v>46160</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32202,7 +32202,7 @@
         <v>46160</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32275,7 +32275,7 @@
         <v>45916</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>45968</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>46161</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>45968</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>45971</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32640,7 +32640,7 @@
         <v>45638</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
         <v>45957</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32786,7 +32786,7 @@
         <v>45728</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32859,7 +32859,7 @@
         <v>45974</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32932,7 +32932,7 @@
         <v>45974</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33005,7 +33005,7 @@
         <v>45947</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>45974</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>46163</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>45974</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33297,7 +33297,7 @@
         <v>45974</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>45974</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>45974</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33516,7 +33516,7 @@
         <v>45979</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>45979</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33662,7 +33662,7 @@
         <v>46047</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33735,7 +33735,7 @@
         <v>45979</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33808,7 +33808,7 @@
         <v>45672</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33881,7 +33881,7 @@
         <v>45740</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>45680</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>45979</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34100,7 +34100,7 @@
         <v>45979</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34173,7 +34173,7 @@
         <v>46163</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>45979</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34319,7 +34319,7 @@
         <v>45981</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34392,7 +34392,7 @@
         <v>45674</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34465,7 +34465,7 @@
         <v>44956</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34538,7 +34538,7 @@
         <v>44956</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34611,7 +34611,7 @@
         <v>44897</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34684,7 +34684,7 @@
         <v>46164</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34757,7 +34757,7 @@
         <v>45981</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>45981</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34903,7 +34903,7 @@
         <v>46167</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34976,7 +34976,7 @@
         <v>45743</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35049,7 +35049,7 @@
         <v>45261</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35122,7 +35122,7 @@
         <v>45294</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>45982</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35268,7 +35268,7 @@
         <v>45982</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35341,7 +35341,7 @@
         <v>45561</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35414,7 +35414,7 @@
         <v>44834</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35487,7 +35487,7 @@
         <v>46164</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35560,7 +35560,7 @@
         <v>45986</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>45987</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35706,7 +35706,7 @@
         <v>46164</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35779,7 +35779,7 @@
         <v>45987</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35852,7 +35852,7 @@
         <v>45988</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35925,7 +35925,7 @@
         <v>45750</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35998,7 +35998,7 @@
         <v>45988</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>45320</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
         <v>44803</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36217,7 +36217,7 @@
         <v>45952</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36290,7 +36290,7 @@
         <v>45392</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>46146</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>46168</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36509,7 +36509,7 @@
         <v>46169</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>45044</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36655,7 +36655,7 @@
         <v>45173</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>46168</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>45994</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>45496</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36952,7 +36952,7 @@
         <v>45999</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37025,7 +37025,7 @@
         <v>45999</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37098,7 +37098,7 @@
         <v>45959</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37171,7 +37171,7 @@
         <v>45758</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37244,7 +37244,7 @@
         <v>45996</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37317,7 +37317,7 @@
         <v>46000</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>46000</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37463,7 +37463,7 @@
         <v>45981</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37536,7 +37536,7 @@
         <v>46000</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>46001</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>44813</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>46170</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37828,7 +37828,7 @@
         <v>45763</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37906,7 +37906,7 @@
         <v>46002</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37979,7 +37979,7 @@
         <v>45328</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38057,7 +38057,7 @@
         <v>45764</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38130,7 +38130,7 @@
         <v>46007</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>46007</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38276,7 +38276,7 @@
         <v>46009</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38349,7 +38349,7 @@
         <v>46008</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>45476</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>46009</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>44901</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>44804</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>46008</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>46009</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>45545</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>46008</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>46008</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>46008</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>46008</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>46174</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>46008</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39371,7 +39371,7 @@
         <v>46009</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>46009</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>45763</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>45763</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>45502</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>44529</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>46174</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>46014</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>46174</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>46174</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40111,7 +40111,7 @@
         <v>45336</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40184,7 +40184,7 @@
         <v>46022</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40257,7 +40257,7 @@
         <v>46024</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40330,7 +40330,7 @@
         <v>46024</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40403,7 +40403,7 @@
         <v>46174</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>46024</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40549,7 +40549,7 @@
         <v>46024</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40622,7 +40622,7 @@
         <v>46029</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40695,7 +40695,7 @@
         <v>46031</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40768,7 +40768,7 @@
         <v>44956</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40841,7 +40841,7 @@
         <v>46031</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40914,7 +40914,7 @@
         <v>44959</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>46034</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>44915</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>46176</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>46176</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>46041</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41357,7 +41357,7 @@
         <v>46041</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>46041</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41503,7 +41503,7 @@
         <v>46177</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41576,7 +41576,7 @@
         <v>46043</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>46043</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41722,7 +41722,7 @@
         <v>46043</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41795,7 +41795,7 @@
         <v>46043</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41868,7 +41868,7 @@
         <v>46042</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>46043</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42014,7 +42014,7 @@
         <v>45278</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>46044</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42165,7 +42165,7 @@
         <v>46044</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42238,7 +42238,7 @@
         <v>46181</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42311,7 +42311,7 @@
         <v>46049</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42384,7 +42384,7 @@
         <v>46181</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>46048</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42530,7 +42530,7 @@
         <v>46181</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42603,7 +42603,7 @@
         <v>46181</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42676,7 +42676,7 @@
         <v>46049</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42749,7 +42749,7 @@
         <v>46046</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42822,7 +42822,7 @@
         <v>46049</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42895,7 +42895,7 @@
         <v>46043</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>46046</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43041,7 +43041,7 @@
         <v>45552</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43114,7 +43114,7 @@
         <v>46046</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43187,7 +43187,7 @@
         <v>46047</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>45771</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43333,7 +43333,7 @@
         <v>45771</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>44739</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43479,7 +43479,7 @@
         <v>46181</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43557,7 +43557,7 @@
         <v>46054</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43630,7 +43630,7 @@
         <v>45034</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>46046</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>46054</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43849,7 +43849,7 @@
         <v>46054</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43922,7 +43922,7 @@
         <v>46046</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>46181</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44068,7 +44068,7 @@
         <v>44872</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44141,7 +44141,7 @@
         <v>45474</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44214,7 +44214,7 @@
         <v>45546</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44287,7 +44287,7 @@
         <v>44775</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44360,7 +44360,7 @@
         <v>46063</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44433,7 +44433,7 @@
         <v>46063</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44506,7 +44506,7 @@
         <v>46062</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>46069</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44652,7 +44652,7 @@
         <v>45300</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44725,7 +44725,7 @@
         <v>45608</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44798,7 +44798,7 @@
         <v>46188</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44871,7 +44871,7 @@
         <v>44529</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44944,7 +44944,7 @@
         <v>46043</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45017,7 +45017,7 @@
         <v>45712</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45090,7 +45090,7 @@
         <v>46188</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45163,7 +45163,7 @@
         <v>46071</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45236,7 +45236,7 @@
         <v>46072</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45309,7 +45309,7 @@
         <v>46188</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>45034</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>45040</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>46072</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45606,7 +45606,7 @@
         <v>44741</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45679,7 +45679,7 @@
         <v>46077</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45752,7 +45752,7 @@
         <v>44894</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45825,7 +45825,7 @@
         <v>45265</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>46190</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>46190</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46044,7 +46044,7 @@
         <v>46190</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46117,7 +46117,7 @@
         <v>46190</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>44571</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46263,7 +46263,7 @@
         <v>45034</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>46094</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>46093</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46482,7 +46482,7 @@
         <v>45664</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46555,7 +46555,7 @@
         <v>46052</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46628,7 +46628,7 @@
         <v>46098</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46701,7 +46701,7 @@
         <v>45572</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46774,7 +46774,7 @@
         <v>46098</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46847,7 +46847,7 @@
         <v>44556</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46920,7 +46920,7 @@
         <v>45182</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46993,7 +46993,7 @@
         <v>46099</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47071,7 +47071,7 @@
         <v>46195</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47144,7 +47144,7 @@
         <v>46100</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47217,7 +47217,7 @@
         <v>46195</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47290,7 +47290,7 @@
         <v>46104</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47363,7 +47363,7 @@
         <v>46104</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47436,7 +47436,7 @@
         <v>45161</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>46105</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47582,7 +47582,7 @@
         <v>45302</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47655,7 +47655,7 @@
         <v>44916</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47728,7 +47728,7 @@
         <v>46195</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47801,7 +47801,7 @@
         <v>45425</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47879,7 +47879,7 @@
         <v>45763</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47957,7 +47957,7 @@
         <v>45044</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48030,7 +48030,7 @@
         <v>46198</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48103,7 +48103,7 @@
         <v>46198</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>46198</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48249,7 +48249,7 @@
         <v>46198</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45674</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48395,7 +48395,7 @@
         <v>45356</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48468,7 +48468,7 @@
         <v>44971</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>45450</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48614,7 +48614,7 @@
         <v>46119</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48687,7 +48687,7 @@
         <v>45660</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48760,7 +48760,7 @@
         <v>45173</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45419</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48906,7 +48906,7 @@
         <v>45729</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48979,7 +48979,7 @@
         <v>46199</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49052,7 +49052,7 @@
         <v>46199</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49125,7 +49125,7 @@
         <v>46071</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49198,7 +49198,7 @@
         <v>46034</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49271,7 +49271,7 @@
         <v>45513</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49344,7 +49344,7 @@
         <v>46127</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>46128</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49490,7 +49490,7 @@
         <v>46112</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49563,7 +49563,7 @@
         <v>46127</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49636,7 +49636,7 @@
         <v>45764</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49714,7 +49714,7 @@
         <v>45420</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49787,7 +49787,7 @@
         <v>45632</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>46199</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49933,7 +49933,7 @@
         <v>45189</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50006,7 +50006,7 @@
         <v>46204</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50079,7 +50079,7 @@
         <v>44880</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50152,7 +50152,7 @@
         <v>45163</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50230,7 +50230,7 @@
         <v>46134</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>46134</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50376,7 +50376,7 @@
         <v>46205</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50449,7 +50449,7 @@
         <v>45239</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45645</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50595,7 +50595,7 @@
         <v>45579</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50673,7 +50673,7 @@
         <v>45538</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>45450</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50819,7 +50819,7 @@
         <v>44769</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>44965</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50965,7 +50965,7 @@
         <v>45724</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51038,7 +51038,7 @@
         <v>45365</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51111,7 +51111,7 @@
         <v>46209</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51184,7 +51184,7 @@
         <v>46209</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51257,7 +51257,7 @@
         <v>46209</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51330,7 +51330,7 @@
         <v>46210</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51403,7 +51403,7 @@
         <v>46210</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51476,7 +51476,7 @@
         <v>44888</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51549,7 +51549,7 @@
         <v>44908</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51622,7 +51622,7 @@
         <v>45365</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51695,7 +51695,7 @@
         <v>45034</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51768,7 +51768,7 @@
         <v>46164</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51841,7 +51841,7 @@
         <v>46140</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51914,7 +51914,7 @@
         <v>45770</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51992,7 +51992,7 @@
         <v>46224</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52070,7 +52070,7 @@
         <v>46225</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52143,7 +52143,7 @@
         <v>44536</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52221,7 +52221,7 @@
         <v>44613</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52299,7 +52299,7 @@
         <v>44608</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52372,7 +52372,7 @@
         <v>46273</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52445,7 +52445,7 @@
         <v>46273</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52518,7 +52518,7 @@
         <v>45764</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52596,7 +52596,7 @@
         <v>45726</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52669,7 +52669,7 @@
         <v>46274</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52747,7 +52747,7 @@
         <v>44880</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52820,7 +52820,7 @@
         <v>45589</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52893,7 +52893,7 @@
         <v>46232</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52966,7 +52966,7 @@
         <v>45034</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53039,7 +53039,7 @@
         <v>45365</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53112,7 +53112,7 @@
         <v>45089</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53185,7 +53185,7 @@
         <v>46281</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53258,7 +53258,7 @@
         <v>44853</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53331,7 +53331,7 @@
         <v>45366</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53404,7 +53404,7 @@
         <v>45684</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>44854</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53550,7 +53550,7 @@
         <v>44540</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53623,7 +53623,7 @@
         <v>45680</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53696,7 +53696,7 @@
         <v>46280</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53769,7 +53769,7 @@
         <v>44865</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53842,7 +53842,7 @@
         <v>45390</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53915,7 +53915,7 @@
         <v>46237</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53988,7 +53988,7 @@
         <v>46238</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54061,7 +54061,7 @@
         <v>46238</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54134,7 +54134,7 @@
         <v>46280</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54207,7 +54207,7 @@
         <v>46238</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54280,7 +54280,7 @@
         <v>46237</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54353,7 +54353,7 @@
         <v>45324</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54426,7 +54426,7 @@
         <v>45447</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54499,7 +54499,7 @@
         <v>46281</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54572,7 +54572,7 @@
         <v>45236</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>44537</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54718,7 +54718,7 @@
         <v>45723</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54791,7 +54791,7 @@
         <v>45713</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54864,7 +54864,7 @@
         <v>46239</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54937,7 +54937,7 @@
         <v>46240</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55010,7 +55010,7 @@
         <v>45236</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55083,7 +55083,7 @@
         <v>45162</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55156,7 +55156,7 @@
         <v>45062</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55229,7 +55229,7 @@
         <v>44750</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55302,7 +55302,7 @@
         <v>45240</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55375,7 +55375,7 @@
         <v>46239</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55448,7 +55448,7 @@
         <v>46283</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55521,7 +55521,7 @@
         <v>44958</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55594,7 +55594,7 @@
         <v>45678</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55667,7 +55667,7 @@
         <v>45189</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55740,7 +55740,7 @@
         <v>46266</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55813,7 +55813,7 @@
         <v>45392</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55886,7 +55886,7 @@
         <v>45237</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -55959,7 +55959,7 @@
         <v>44907</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56032,7 +56032,7 @@
         <v>46287</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56105,7 +56105,7 @@
         <v>45198</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56183,7 +56183,7 @@
         <v>46284</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56256,7 +56256,7 @@
         <v>46284</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56329,7 +56329,7 @@
         <v>45324</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56402,7 +56402,7 @@
         <v>46244</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56475,7 +56475,7 @@
         <v>45209</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56548,7 +56548,7 @@
         <v>45162</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56621,7 +56621,7 @@
         <v>45162</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56694,7 +56694,7 @@
         <v>46241</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56772,7 +56772,7 @@
         <v>46244</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56845,7 +56845,7 @@
         <v>46287</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -56918,7 +56918,7 @@
         <v>45520</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -56991,7 +56991,7 @@
         <v>46287</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57064,7 +57064,7 @@
         <v>46288</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57142,7 +57142,7 @@
         <v>45271</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57215,7 +57215,7 @@
         <v>46287</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57288,7 +57288,7 @@
         <v>44824</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57361,7 +57361,7 @@
         <v>45320</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57439,7 +57439,7 @@
         <v>44573</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57512,7 +57512,7 @@
         <v>46289</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57585,7 +57585,7 @@
         <v>45750</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57658,7 +57658,7 @@
         <v>44574</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57731,7 +57731,7 @@
         <v>46248</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57804,7 +57804,7 @@
         <v>45273</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -57877,7 +57877,7 @@
         <v>45519</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -57950,7 +57950,7 @@
         <v>44819</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58023,7 +58023,7 @@
         <v>46247</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58101,7 +58101,7 @@
         <v>44638</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58174,7 +58174,7 @@
         <v>45803</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58247,7 +58247,7 @@
         <v>46248</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58325,7 +58325,7 @@
         <v>45763</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58403,7 +58403,7 @@
         <v>45099</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58476,7 +58476,7 @@
         <v>46120</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58549,7 +58549,7 @@
         <v>45365</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58622,7 +58622,7 @@
         <v>45180</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58695,7 +58695,7 @@
         <v>46251</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58768,7 +58768,7 @@
         <v>46251</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -58841,7 +58841,7 @@
         <v>45400</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -58914,7 +58914,7 @@
         <v>44860</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -58987,7 +58987,7 @@
         <v>45099</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59060,7 +59060,7 @@
         <v>45232</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59138,7 +59138,7 @@
         <v>46251</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59216,7 +59216,7 @@
         <v>46254</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59294,7 +59294,7 @@
         <v>45271</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59367,7 +59367,7 @@
         <v>45328</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59440,7 +59440,7 @@
         <v>46254</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59513,7 +59513,7 @@
         <v>44788</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59586,7 +59586,7 @@
         <v>46296</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59664,7 +59664,7 @@
         <v>46253</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59737,7 +59737,7 @@
         <v>46296</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59815,7 +59815,7 @@
         <v>46239</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -59888,7 +59888,7 @@
         <v>46253</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -59966,7 +59966,7 @@
         <v>46254</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60044,7 +60044,7 @@
         <v>46297</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60117,7 +60117,7 @@
         <v>46253</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60190,7 +60190,7 @@
         <v>46274</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60263,7 +60263,7 @@
         <v>46254</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60336,7 +60336,7 @@
         <v>46253</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60409,7 +60409,7 @@
         <v>46253</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60487,7 +60487,7 @@
         <v>44564</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60560,7 +60560,7 @@
         <v>46300</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60633,7 +60633,7 @@
         <v>45034</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60706,7 +60706,7 @@
         <v>46300</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60779,7 +60779,7 @@
         <v>44998</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -60852,7 +60852,7 @@
         <v>46258</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -60930,7 +60930,7 @@
         <v>45645</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61003,7 +61003,7 @@
         <v>45645</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61076,7 +61076,7 @@
         <v>45776</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61154,7 +61154,7 @@
         <v>45734</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61227,7 +61227,7 @@
         <v>46256</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61300,7 +61300,7 @@
         <v>46300</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61373,7 +61373,7 @@
         <v>46300</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61446,7 +61446,7 @@
         <v>45782</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61519,7 +61519,7 @@
         <v>46300</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61597,7 +61597,7 @@
         <v>46301</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61670,7 +61670,7 @@
         <v>45496</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61748,7 +61748,7 @@
         <v>46256</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -61821,7 +61821,7 @@
         <v>46298</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -61894,7 +61894,7 @@
         <v>45408</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -61967,7 +61967,7 @@
         <v>45476</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62040,7 +62040,7 @@
         <v>44834</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62118,7 +62118,7 @@
         <v>45281</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62191,7 +62191,7 @@
         <v>45306</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62264,7 +62264,7 @@
         <v>46293</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62337,7 +62337,7 @@
         <v>45791</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62410,7 +62410,7 @@
         <v>45496</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62488,7 +62488,7 @@
         <v>45231</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62561,7 +62561,7 @@
         <v>45790</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62634,7 +62634,7 @@
         <v>45169</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62707,7 +62707,7 @@
         <v>45618</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62780,7 +62780,7 @@
         <v>45567</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -62853,7 +62853,7 @@
         <v>45792</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -62926,7 +62926,7 @@
         <v>45418</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -62999,7 +62999,7 @@
         <v>45415</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63072,7 +63072,7 @@
         <v>46262</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63145,7 +63145,7 @@
         <v>44503</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63218,7 +63218,7 @@
         <v>44804</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63291,7 +63291,7 @@
         <v>45435</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63369,7 +63369,7 @@
         <v>45797</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63442,7 +63442,7 @@
         <v>45552</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63515,7 +63515,7 @@
         <v>45797</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63588,7 +63588,7 @@
         <v>46304</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63661,7 +63661,7 @@
         <v>45798</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63739,7 +63739,7 @@
         <v>46301</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -63812,7 +63812,7 @@
         <v>45833</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -63885,7 +63885,7 @@
         <v>45799</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -63963,7 +63963,7 @@
         <v>46069</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64036,7 +64036,7 @@
         <v>46262</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64109,7 +64109,7 @@
         <v>46307</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64182,7 +64182,7 @@
         <v>45799</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64260,7 +64260,7 @@
         <v>44903</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64333,7 +64333,7 @@
         <v>45799</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64406,7 +64406,7 @@
         <v>46304</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64479,7 +64479,7 @@
         <v>46265</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64557,7 +64557,7 @@
         <v>46265</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64635,7 +64635,7 @@
         <v>46265</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64713,7 +64713,7 @@
         <v>46309</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -64786,7 +64786,7 @@
         <v>46266</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -64859,7 +64859,7 @@
         <v>46265</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -64932,7 +64932,7 @@
         <v>46262</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65005,7 +65005,7 @@
         <v>46266</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65078,7 +65078,7 @@
         <v>45475</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65151,7 +65151,7 @@
         <v>44834</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65229,7 +65229,7 @@
         <v>45036</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65302,7 +65302,7 @@
         <v>46266</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65375,7 +65375,7 @@
         <v>46266</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65448,7 +65448,7 @@
         <v>45805</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65521,7 +65521,7 @@
         <v>45805</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65594,7 +65594,7 @@
         <v>45643</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65667,7 +65667,7 @@
         <v>45807</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -65745,7 +65745,7 @@
         <v>46265</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -65823,7 +65823,7 @@
         <v>45726</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -65896,7 +65896,7 @@
         <v>45734</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -65969,7 +65969,7 @@
         <v>45654</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66042,7 +66042,7 @@
         <v>46265</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66120,7 +66120,7 @@
         <v>45712</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66193,7 +66193,7 @@
         <v>45678</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66266,7 +66266,7 @@
         <v>46265</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66339,7 +66339,7 @@
         <v>46036</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66412,7 +66412,7 @@
         <v>46307</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66485,7 +66485,7 @@
         <v>46267</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66558,7 +66558,7 @@
         <v>46268</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66631,7 +66631,7 @@
         <v>45593</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66704,7 +66704,7 @@
         <v>45813</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -66777,7 +66777,7 @@
         <v>45782</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -66850,7 +66850,7 @@
         <v>45813</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -66923,7 +66923,7 @@
         <v>45653</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -66996,7 +66996,7 @@
         <v>45753</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67069,7 +67069,7 @@
         <v>46268</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67142,7 +67142,7 @@
         <v>45768</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67215,7 +67215,7 @@
         <v>45818</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67293,7 +67293,7 @@
         <v>45819</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67366,7 +67366,7 @@
         <v>45825</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67439,7 +67439,7 @@
         <v>45825</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67512,7 +67512,7 @@
         <v>45825</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67585,7 +67585,7 @@
         <v>45825</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67658,7 +67658,7 @@
         <v>45825</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -67731,7 +67731,7 @@
         <v>45825</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -67804,7 +67804,7 @@
         <v>45825</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -67877,7 +67877,7 @@
         <v>45825</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -67950,7 +67950,7 @@
         <v>45825</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68023,7 +68023,7 @@
         <v>45825</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68096,7 +68096,7 @@
         <v>46309</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68169,7 +68169,7 @@
         <v>46310</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68242,7 +68242,7 @@
         <v>45833</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68320,7 +68320,7 @@
         <v>45832</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68393,7 +68393,7 @@
         <v>45834</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68471,7 +68471,7 @@
         <v>45838</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68544,7 +68544,7 @@
         <v>45838</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68622,7 +68622,7 @@
         <v>45841</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -68700,7 +68700,7 @@
         <v>45840</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -68778,7 +68778,7 @@
         <v>45841</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -68856,7 +68856,7 @@
         <v>45840</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -68929,7 +68929,7 @@
         <v>45840</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69007,7 +69007,7 @@
         <v>45841</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69080,7 +69080,7 @@
         <v>45841</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69153,7 +69153,7 @@
         <v>45842</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69226,7 +69226,7 @@
         <v>45852</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69299,7 +69299,7 @@
         <v>45855</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69372,7 +69372,7 @@
         <v>45799</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69445,7 +69445,7 @@
         <v>45859</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69518,7 +69518,7 @@
         <v>45860</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69591,7 +69591,7 @@
         <v>45799</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -69664,7 +69664,7 @@
         <v>45749</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -69737,7 +69737,7 @@
         <v>45825</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -69810,7 +69810,7 @@
         <v>45873</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -69883,7 +69883,7 @@
         <v>45875</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -69956,7 +69956,7 @@
         <v>45874</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70029,7 +70029,7 @@
         <v>45874</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70102,7 +70102,7 @@
         <v>45874</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70175,7 +70175,7 @@
         <v>45876</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70248,7 +70248,7 @@
         <v>45881</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70321,7 +70321,7 @@
         <v>45881</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70394,7 +70394,7 @@
         <v>44971</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70467,7 +70467,7 @@
         <v>45751</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70540,7 +70540,7 @@
         <v>45751</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -70618,7 +70618,7 @@
         <v>45790</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -70696,7 +70696,7 @@
         <v>46041</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -70769,7 +70769,7 @@
         <v>46078</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -70842,7 +70842,7 @@
         <v>46073</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -70915,7 +70915,7 @@
         <v>46142</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -70988,7 +70988,7 @@
         <v>44880</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>

--- a/Översikt KRAMFORS.xlsx
+++ b/Översikt KRAMFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45544</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>46183</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>46029</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>46254</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>46003</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>46197</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>46094</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>45763</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45831</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>46287</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>46196</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>44810</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>45763</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>46316</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>46197</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>46044</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>46241</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>46203</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>46181</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>45763</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>46002</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>46136</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>45056</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>45511</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>45996</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>46196</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>46316</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>46136</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>45723</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>46265</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>44713</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>45973</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>45985</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         <v>45785</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>45484</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>45818</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>46317</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>45399</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>45356</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>45660</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44524</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>46314</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>45733</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>44629</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>45282</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>45957</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>45959</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>46195</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>45985</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>46046</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>45818</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>46258</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>45806</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>46317</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>45516</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>44813</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>45898</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>45898</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>46178</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>45114</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>45665</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>45551</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>45786</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>46036</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>46241</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         <v>46244</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>45468</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>45729</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>45840</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>45182</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>46273</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>45511</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>45750</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>44803</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>45924</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>45344</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>44852</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>45943</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>45243</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>45199</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9723,7 +9723,7 @@
         <v>45979</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>45400</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>45114</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         <v>45998</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>46020</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>46021</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>46281</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>46024</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10575,7 +10575,7 @@
         <v>46030</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>45636</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         <v>46048</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>46071</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>46098</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>45670</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11217,7 +11217,7 @@
         <v>44965</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         <v>45764</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>45645</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>45764</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>45156</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>45071</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         <v>44817</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>44804</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         <v>44634</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>44859</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>44508</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>44508</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
         <v>44608</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>44594</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         <v>44509</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>44496</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>44587</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>44511</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>44592</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
         <v>44592</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>44722</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>44688</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>44556</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13103,7 +13103,7 @@
         <v>44508</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>44852</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13249,7 +13249,7 @@
         <v>44817</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>44817</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13395,7 +13395,7 @@
         <v>44762</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>44509</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>44859</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>44581</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44516</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>44509</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>44539</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>44566</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>44687</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>44594</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>44719</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>44715</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>44803</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>44629</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>44594</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>44802</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>44509</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>44540</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>44550</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>44607</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>44876</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>44628</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15001,7 +15001,7 @@
         <v>44616</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>44749</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15147,7 +15147,7 @@
         <v>44697</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         <v>44581</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>44503</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>44859</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15439,7 +15439,7 @@
         <v>44601</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>44782</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>44581</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         <v>45883</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>45883</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>45888</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>44804</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>45721</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>45616</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>45890</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>45890</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>45205</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>45513</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>44840</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16466,7 +16466,7 @@
         <v>45672</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
         <v>45712</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16612,7 +16612,7 @@
         <v>44741</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>45890</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>45674</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>44788</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>44860</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>45883</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>45572</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>45883</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>45898</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>45898</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>45898</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>45898</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>45419</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>44853</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>45724</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>45898</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         <v>45043</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>45898</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17931,7 +17931,7 @@
         <v>45898</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>45044</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
         <v>45901</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>45365</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>45898</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18296,7 +18296,7 @@
         <v>45898</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>45901</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>45898</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>45901</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         <v>45239</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>45209</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>45225</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>45909</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>45909</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>45433</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>44897</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19099,7 +19099,7 @@
         <v>45909</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>45947</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>45947</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>46098</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>46047</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45232</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>46161</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>44883</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19688,7 +19688,7 @@
         <v>45947</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>45728</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>45912</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>45957</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>46064</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>45959</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>46164</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>45282</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>46164</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>46163</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>46163</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20496,7 +20496,7 @@
         <v>46164</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>45918</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>44750</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>45678</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>46146</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>45952</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>45981</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>46168</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>46167</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>44574</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>45173</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>45926</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>45926</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21445,7 +21445,7 @@
         <v>45757</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>46169</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>45034</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>46168</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>45496</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21820,7 +21820,7 @@
         <v>45000</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>45932</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>44774</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45085</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>46170</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>46174</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>44824</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>44852</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>45935</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>46174</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22565,7 +22565,7 @@
         <v>45936</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>44834</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>45937</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22784,7 +22784,7 @@
         <v>45936</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22857,7 +22857,7 @@
         <v>45937</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>46174</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>46174</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23076,7 +23076,7 @@
         <v>46174</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23149,7 +23149,7 @@
         <v>45943</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>45674</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>44901</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23368,7 +23368,7 @@
         <v>44747</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23441,7 +23441,7 @@
         <v>46177</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23514,7 +23514,7 @@
         <v>46176</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>45450</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23660,7 +23660,7 @@
         <v>45265</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23733,7 +23733,7 @@
         <v>45261</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23806,7 +23806,7 @@
         <v>45390</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>45664</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23952,7 +23952,7 @@
         <v>45946</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24025,7 +24025,7 @@
         <v>45674</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24098,7 +24098,7 @@
         <v>46176</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>45089</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>45947</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24317,7 +24317,7 @@
         <v>45034</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>46181</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>45520</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>45698</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24614,7 +24614,7 @@
         <v>45952</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24687,7 +24687,7 @@
         <v>46181</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>46181</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24833,7 +24833,7 @@
         <v>46181</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24906,7 +24906,7 @@
         <v>46181</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>46181</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25052,7 +25052,7 @@
         <v>45307</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25125,7 +25125,7 @@
         <v>45952</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>45951</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25271,7 +25271,7 @@
         <v>45957</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>44958</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>44880</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>45960</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25568,7 +25568,7 @@
         <v>45534</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25641,7 +25641,7 @@
         <v>45964</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25714,7 +25714,7 @@
         <v>45964</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>45964</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25860,7 +25860,7 @@
         <v>45964</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25933,7 +25933,7 @@
         <v>45124</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>45964</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26084,7 +26084,7 @@
         <v>46188</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26157,7 +26157,7 @@
         <v>45964</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>45964</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>45964</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>45524</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26459,7 +26459,7 @@
         <v>45099</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         <v>44907</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>46188</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26683,7 +26683,7 @@
         <v>45884</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26756,7 +26756,7 @@
         <v>46188</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26829,7 +26829,7 @@
         <v>46190</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>46190</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26975,7 +26975,7 @@
         <v>46190</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>46190</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>45950</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27194,7 +27194,7 @@
         <v>45950</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>45968</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27340,7 +27340,7 @@
         <v>45968</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27413,7 +27413,7 @@
         <v>46195</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27486,7 +27486,7 @@
         <v>46195</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         <v>46195</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27632,7 +27632,7 @@
         <v>45971</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27705,7 +27705,7 @@
         <v>45273</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27778,7 +27778,7 @@
         <v>45324</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27851,7 +27851,7 @@
         <v>45974</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>45974</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>45974</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28070,7 +28070,7 @@
         <v>45974</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28143,7 +28143,7 @@
         <v>45974</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>45974</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         <v>45579</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>45974</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>45680</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28513,7 +28513,7 @@
         <v>45236</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>46199</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>46198</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>46199</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>46198</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>46198</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28951,7 +28951,7 @@
         <v>45278</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44574</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29097,7 +29097,7 @@
         <v>46199</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>45979</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>46034</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29316,7 +29316,7 @@
         <v>46198</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29389,7 +29389,7 @@
         <v>45771</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29462,7 +29462,7 @@
         <v>45979</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29535,7 +29535,7 @@
         <v>45979</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>45000</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>45979</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>45979</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29832,7 +29832,7 @@
         <v>45979</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
         <v>45981</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29978,7 +29978,7 @@
         <v>45982</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>45982</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>45153</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30197,7 +30197,7 @@
         <v>45440</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30270,7 +30270,7 @@
         <v>45981</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
         <v>46204</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>45981</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>45986</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>45271</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         <v>46205</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>45355</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>45475</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>45987</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30927,7 +30927,7 @@
         <v>45987</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>45278</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31073,7 +31073,7 @@
         <v>45644</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>46209</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>46209</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>46209</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31365,7 +31365,7 @@
         <v>45988</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>45988</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>45265</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>46210</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>46210</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31730,7 +31730,7 @@
         <v>45994</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31803,7 +31803,7 @@
         <v>45099</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>45959</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>45996</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>45638</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>45754</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>45433</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>45450</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>45999</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32387,7 +32387,7 @@
         <v>45999</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>46000</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32533,7 +32533,7 @@
         <v>46001</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>46140</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32679,7 +32679,7 @@
         <v>46002</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32752,7 +32752,7 @@
         <v>45776</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32830,7 +32830,7 @@
         <v>46000</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32903,7 +32903,7 @@
         <v>46164</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32976,7 +32976,7 @@
         <v>46000</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>46224</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>45770</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>46225</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>45782</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33351,7 +33351,7 @@
         <v>46008</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>46008</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33497,7 +33497,7 @@
         <v>46007</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33570,7 +33570,7 @@
         <v>46008</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>46008</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>46232</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33789,7 +33789,7 @@
         <v>46007</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>46008</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>46008</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>46008</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34081,7 +34081,7 @@
         <v>44958</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34154,7 +34154,7 @@
         <v>46009</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34227,7 +34227,7 @@
         <v>46237</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34300,7 +34300,7 @@
         <v>46009</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34373,7 +34373,7 @@
         <v>46009</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         <v>46009</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>46280</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
         <v>46009</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>45281</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34738,7 +34738,7 @@
         <v>44834</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34816,7 +34816,7 @@
         <v>44854</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34889,7 +34889,7 @@
         <v>46237</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34962,7 +34962,7 @@
         <v>45306</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35035,7 +35035,7 @@
         <v>45408</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35108,7 +35108,7 @@
         <v>45476</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>44540</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35254,7 +35254,7 @@
         <v>45496</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35332,7 +35332,7 @@
         <v>46280</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>46014</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>45169</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>46238</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35624,7 +35624,7 @@
         <v>46238</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
         <v>46281</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35770,7 +35770,7 @@
         <v>46022</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>45790</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>46240</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>46024</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36062,7 +36062,7 @@
         <v>46239</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36135,7 +36135,7 @@
         <v>46239</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>46024</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36281,7 +36281,7 @@
         <v>46024</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>46024</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36427,7 +36427,7 @@
         <v>46281</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>46238</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36573,7 +36573,7 @@
         <v>45496</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>46029</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>45792</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36797,7 +36797,7 @@
         <v>46284</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36870,7 +36870,7 @@
         <v>46284</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36943,7 +36943,7 @@
         <v>45567</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>44894</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37089,7 +37089,7 @@
         <v>46031</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37162,7 +37162,7 @@
         <v>46034</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>46031</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37308,7 +37308,7 @@
         <v>45618</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37381,7 +37381,7 @@
         <v>45231</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>45791</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37527,7 +37527,7 @@
         <v>45415</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>46283</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>45418</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37746,7 +37746,7 @@
         <v>46241</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37824,7 +37824,7 @@
         <v>44804</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37897,7 +37897,7 @@
         <v>45552</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>44503</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38043,7 +38043,7 @@
         <v>46042</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38116,7 +38116,7 @@
         <v>46287</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>46288</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>46041</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38340,7 +38340,7 @@
         <v>46041</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38413,7 +38413,7 @@
         <v>46041</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38486,7 +38486,7 @@
         <v>45435</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>46043</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>46266</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38710,7 +38710,7 @@
         <v>46043</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38783,7 +38783,7 @@
         <v>46044</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>45797</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>45797</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>46043</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39075,7 +39075,7 @@
         <v>46043</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39148,7 +39148,7 @@
         <v>46043</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39221,7 +39221,7 @@
         <v>46244</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39294,7 +39294,7 @@
         <v>44903</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39367,7 +39367,7 @@
         <v>45798</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39445,7 +39445,7 @@
         <v>46044</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>46043</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39596,7 +39596,7 @@
         <v>46048</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39669,7 +39669,7 @@
         <v>46287</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39742,7 +39742,7 @@
         <v>46287</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39815,7 +39815,7 @@
         <v>46046</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>45799</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39966,7 +39966,7 @@
         <v>46046</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>46046</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40112,7 +40112,7 @@
         <v>46047</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40185,7 +40185,7 @@
         <v>46244</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40258,7 +40258,7 @@
         <v>46049</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40331,7 +40331,7 @@
         <v>46247</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40409,7 +40409,7 @@
         <v>45799</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40482,7 +40482,7 @@
         <v>45799</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>46049</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40633,7 +40633,7 @@
         <v>46049</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40706,7 +40706,7 @@
         <v>45036</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>44834</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40857,7 +40857,7 @@
         <v>46046</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>45805</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41003,7 +41003,7 @@
         <v>45805</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41076,7 +41076,7 @@
         <v>46289</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41149,7 +41149,7 @@
         <v>45475</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41222,7 +41222,7 @@
         <v>45643</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41295,7 +41295,7 @@
         <v>46054</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>46054</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>46046</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41514,7 +41514,7 @@
         <v>45712</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>46054</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41660,7 +41660,7 @@
         <v>45273</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41733,7 +41733,7 @@
         <v>45734</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41806,7 +41806,7 @@
         <v>45678</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41879,7 +41879,7 @@
         <v>45807</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41957,7 +41957,7 @@
         <v>45328</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42035,7 +42035,7 @@
         <v>46287</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42108,7 +42108,7 @@
         <v>45593</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42181,7 +42181,7 @@
         <v>45654</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42254,7 +42254,7 @@
         <v>45726</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>45753</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>46062</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42473,7 +42473,7 @@
         <v>45782</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42546,7 +42546,7 @@
         <v>45653</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42619,7 +42619,7 @@
         <v>45750</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42692,7 +42692,7 @@
         <v>46120</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42765,7 +42765,7 @@
         <v>45803</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42838,7 +42838,7 @@
         <v>44942</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
         <v>46063</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42984,7 +42984,7 @@
         <v>46063</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43057,7 +43057,7 @@
         <v>45813</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43130,7 +43130,7 @@
         <v>45813</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43203,7 +43203,7 @@
         <v>45768</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43276,7 +43276,7 @@
         <v>46248</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43354,7 +43354,7 @@
         <v>45818</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43432,7 +43432,7 @@
         <v>46069</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43505,7 +43505,7 @@
         <v>46248</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45819</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43651,7 +43651,7 @@
         <v>46071</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43724,7 +43724,7 @@
         <v>46043</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43797,7 +43797,7 @@
         <v>46072</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43870,7 +43870,7 @@
         <v>46239</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43943,7 +43943,7 @@
         <v>46253</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44016,7 +44016,7 @@
         <v>46072</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44089,7 +44089,7 @@
         <v>46077</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>46251</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44235,7 +44235,7 @@
         <v>46253</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>46251</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44391,7 +44391,7 @@
         <v>46253</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44469,7 +44469,7 @@
         <v>46296</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44547,7 +44547,7 @@
         <v>46296</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>45825</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45825</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>45825</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44844,7 +44844,7 @@
         <v>45825</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44917,7 +44917,7 @@
         <v>46251</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>45825</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45063,7 +45063,7 @@
         <v>45825</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45136,7 +45136,7 @@
         <v>46253</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>45825</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45282,7 +45282,7 @@
         <v>45825</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45355,7 +45355,7 @@
         <v>46253</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45428,7 +45428,7 @@
         <v>45825</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>45825</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>45832</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45647,7 +45647,7 @@
         <v>45734</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45720,7 +45720,7 @@
         <v>45833</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45798,7 +45798,7 @@
         <v>45834</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>46254</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45949,7 +45949,7 @@
         <v>46254</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46022,7 +46022,7 @@
         <v>46300</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46095,7 +46095,7 @@
         <v>46300</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46168,7 +46168,7 @@
         <v>46254</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46246,7 +46246,7 @@
         <v>46254</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46324,7 +46324,7 @@
         <v>45838</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46397,7 +46397,7 @@
         <v>46300</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>45838</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46548,7 +46548,7 @@
         <v>45840</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46626,7 +46626,7 @@
         <v>45482</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>45840</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46782,7 +46782,7 @@
         <v>46093</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46855,7 +46855,7 @@
         <v>45840</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>46256</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>46300</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>46094</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>45365</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>46052</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>46256</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47371,7 +47371,7 @@
         <v>45842</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47444,7 +47444,7 @@
         <v>46297</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47517,7 +47517,7 @@
         <v>45841</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47590,7 +47590,7 @@
         <v>45841</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47663,7 +47663,7 @@
         <v>46098</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47736,7 +47736,7 @@
         <v>46298</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47809,7 +47809,7 @@
         <v>45841</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47887,7 +47887,7 @@
         <v>45841</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>46098</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48038,7 +48038,7 @@
         <v>46099</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48116,7 +48116,7 @@
         <v>46100</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48189,7 +48189,7 @@
         <v>46104</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48262,7 +48262,7 @@
         <v>46104</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48335,7 +48335,7 @@
         <v>45469</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48408,7 +48408,7 @@
         <v>44519</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48481,7 +48481,7 @@
         <v>46105</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48554,7 +48554,7 @@
         <v>46258</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48632,7 +48632,7 @@
         <v>45852</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48705,7 +48705,7 @@
         <v>44529</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48778,7 +48778,7 @@
         <v>45645</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48851,7 +48851,7 @@
         <v>46300</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48924,7 +48924,7 @@
         <v>46301</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48997,7 +48997,7 @@
         <v>45855</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49070,7 +49070,7 @@
         <v>45799</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49143,7 +49143,7 @@
         <v>45860</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49216,7 +49216,7 @@
         <v>45859</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45799</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49362,7 +49362,7 @@
         <v>45825</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49435,7 +49435,7 @@
         <v>45749</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49508,7 +49508,7 @@
         <v>46304</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>46304</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49654,7 +49654,7 @@
         <v>46119</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49727,7 +49727,7 @@
         <v>46293</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49800,7 +49800,7 @@
         <v>44536</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49878,7 +49878,7 @@
         <v>45874</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49951,7 +49951,7 @@
         <v>45874</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50024,7 +50024,7 @@
         <v>45873</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50097,7 +50097,7 @@
         <v>44574</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50170,7 +50170,7 @@
         <v>46127</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50243,7 +50243,7 @@
         <v>45874</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50316,7 +50316,7 @@
         <v>46112</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50389,7 +50389,7 @@
         <v>46071</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50462,7 +50462,7 @@
         <v>45876</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50535,7 +50535,7 @@
         <v>44634</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50608,7 +50608,7 @@
         <v>46127</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50681,7 +50681,7 @@
         <v>45875</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50754,7 +50754,7 @@
         <v>45833</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50827,7 +50827,7 @@
         <v>46265</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50905,7 +50905,7 @@
         <v>46128</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>45632</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51051,7 +51051,7 @@
         <v>46265</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51124,7 +51124,7 @@
         <v>46262</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51197,7 +51197,7 @@
         <v>46262</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51270,7 +51270,7 @@
         <v>45881</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>45881</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51416,7 +51416,7 @@
         <v>45545</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51489,7 +51489,7 @@
         <v>46134</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51562,7 +51562,7 @@
         <v>46265</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51640,7 +51640,7 @@
         <v>44909</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51713,7 +51713,7 @@
         <v>45538</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51786,7 +51786,7 @@
         <v>46134</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51859,7 +51859,7 @@
         <v>46265</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51937,7 +51937,7 @@
         <v>46069</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52010,7 +52010,7 @@
         <v>45425</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52088,7 +52088,7 @@
         <v>44503</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>44908</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52234,7 +52234,7 @@
         <v>46307</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52307,7 +52307,7 @@
         <v>46301</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45797</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52453,7 +52453,7 @@
         <v>45664</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52526,7 +52526,7 @@
         <v>46265</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52604,7 +52604,7 @@
         <v>46265</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52682,7 +52682,7 @@
         <v>45491</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>44959</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52838,7 +52838,7 @@
         <v>44872</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52911,7 +52911,7 @@
         <v>46266</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52984,7 +52984,7 @@
         <v>45420</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53057,7 +53057,7 @@
         <v>46036</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53130,7 +53130,7 @@
         <v>45960</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53203,7 +53203,7 @@
         <v>46266</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53276,7 +53276,7 @@
         <v>46266</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53349,7 +53349,7 @@
         <v>46309</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53422,7 +53422,7 @@
         <v>46262</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53495,7 +53495,7 @@
         <v>46136</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53568,7 +53568,7 @@
         <v>46307</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53641,7 +53641,7 @@
         <v>46266</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53714,7 +53714,7 @@
         <v>46265</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53787,7 +53787,7 @@
         <v>44958</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53860,7 +53860,7 @@
         <v>44958</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53933,7 +53933,7 @@
         <v>46310</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54006,7 +54006,7 @@
         <v>46309</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54079,7 +54079,7 @@
         <v>45518</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54152,7 +54152,7 @@
         <v>45876</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54225,7 +54225,7 @@
         <v>45771</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54298,7 +54298,7 @@
         <v>45896</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54371,7 +54371,7 @@
         <v>46069</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54444,7 +54444,7 @@
         <v>45425</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54517,7 +54517,7 @@
         <v>46107</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54590,7 +54590,7 @@
         <v>46267</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54663,7 +54663,7 @@
         <v>45909</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54736,7 +54736,7 @@
         <v>44991</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54814,7 +54814,7 @@
         <v>46314</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54892,7 +54892,7 @@
         <v>44629</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54965,7 +54965,7 @@
         <v>44546</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55038,7 +55038,7 @@
         <v>44956</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55111,7 +55111,7 @@
         <v>46268</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55184,7 +55184,7 @@
         <v>45943</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55257,7 +55257,7 @@
         <v>45750</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55330,7 +55330,7 @@
         <v>46314</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55403,7 +55403,7 @@
         <v>46140</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55476,7 +55476,7 @@
         <v>46314</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55554,7 +55554,7 @@
         <v>45973</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55627,7 +55627,7 @@
         <v>45821</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55700,7 +55700,7 @@
         <v>46314</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55773,7 +55773,7 @@
         <v>45875</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55846,7 +55846,7 @@
         <v>46268</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55919,7 +55919,7 @@
         <v>45513</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55992,7 +55992,7 @@
         <v>44855</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56065,7 +56065,7 @@
         <v>45320</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56143,7 +56143,7 @@
         <v>46316</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56216,7 +56216,7 @@
         <v>45544</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56289,7 +56289,7 @@
         <v>45813</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56362,7 +56362,7 @@
         <v>45225</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56435,7 +56435,7 @@
         <v>46316</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56513,7 +56513,7 @@
         <v>46029</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56586,7 +56586,7 @@
         <v>45685</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56659,7 +56659,7 @@
         <v>46273</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56732,7 +56732,7 @@
         <v>46316</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56810,7 +56810,7 @@
         <v>45841</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56883,7 +56883,7 @@
         <v>46315</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56956,7 +56956,7 @@
         <v>44888</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57029,7 +57029,7 @@
         <v>45552</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57102,7 +57102,7 @@
         <v>46273</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57175,7 +57175,7 @@
         <v>46316</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57248,7 +57248,7 @@
         <v>46064</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57321,7 +57321,7 @@
         <v>45733</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57394,7 +57394,7 @@
         <v>46084</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57467,7 +57467,7 @@
         <v>45959</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57540,7 +57540,7 @@
         <v>46315</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57613,7 +57613,7 @@
         <v>45526</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57686,7 +57686,7 @@
         <v>46314</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57759,7 +57759,7 @@
         <v>44638</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57832,7 +57832,7 @@
         <v>46318</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57905,7 +57905,7 @@
         <v>45190</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57978,7 +57978,7 @@
         <v>45672</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58051,7 +58051,7 @@
         <v>45818</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58124,7 +58124,7 @@
         <v>45553</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58197,7 +58197,7 @@
         <v>46318</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58270,7 +58270,7 @@
         <v>46142</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58343,7 +58343,7 @@
         <v>46316</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58421,7 +58421,7 @@
         <v>45989</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58494,7 +58494,7 @@
         <v>45324</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58567,7 +58567,7 @@
         <v>45842</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58640,7 +58640,7 @@
         <v>45959</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58713,7 +58713,7 @@
         <v>45931</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58786,7 +58786,7 @@
         <v>44894</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58859,7 +58859,7 @@
         <v>45894</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58932,7 +58932,7 @@
         <v>45881</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59005,7 +59005,7 @@
         <v>45723</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59078,7 +59078,7 @@
         <v>45173</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59151,7 +59151,7 @@
         <v>46274</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59229,7 +59229,7 @@
         <v>46274</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59302,7 +59302,7 @@
         <v>46146</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59375,7 +59375,7 @@
         <v>44916</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59448,7 +59448,7 @@
         <v>44949</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59521,7 +59521,7 @@
         <v>46146</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59594,7 +59594,7 @@
         <v>46148</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59672,7 +59672,7 @@
         <v>46147</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59750,7 +59750,7 @@
         <v>45392</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59823,7 +59823,7 @@
         <v>45189</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59896,7 +59896,7 @@
         <v>45162</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59969,7 +59969,7 @@
         <v>45162</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60042,7 +60042,7 @@
         <v>45589</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60115,7 +60115,7 @@
         <v>45713</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60188,7 +60188,7 @@
         <v>45120</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60261,7 +60261,7 @@
         <v>45189</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60334,7 +60334,7 @@
         <v>46153</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60407,7 +60407,7 @@
         <v>45959</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60480,7 +60480,7 @@
         <v>45356</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60553,7 +60553,7 @@
         <v>45461</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60631,7 +60631,7 @@
         <v>46155</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60704,7 +60704,7 @@
         <v>45950</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60777,7 +60777,7 @@
         <v>46155</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60850,7 +60850,7 @@
         <v>46155</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60923,7 +60923,7 @@
         <v>45916</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60996,7 +60996,7 @@
         <v>46160</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61074,7 +61074,7 @@
         <v>46160</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61147,7 +61147,7 @@
         <v>45034</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61220,7 +61220,7 @@
         <v>44956</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61293,7 +61293,7 @@
         <v>45679</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61366,7 +61366,7 @@
         <v>46157</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61439,7 +61439,7 @@
         <v>45608</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61512,7 +61512,7 @@
         <v>45707</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61585,7 +61585,7 @@
         <v>46160</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61658,7 +61658,7 @@
         <v>44998</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61731,7 +61731,7 @@
         <v>44965</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61804,7 +61804,7 @@
         <v>44965</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61877,7 +61877,7 @@
         <v>45684</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61950,7 +61950,7 @@
         <v>45062</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62023,7 +62023,7 @@
         <v>44571</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62096,7 +62096,7 @@
         <v>45324</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62169,7 +62169,7 @@
         <v>45036</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62242,7 +62242,7 @@
         <v>45365</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62315,7 +62315,7 @@
         <v>45636</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62388,7 +62388,7 @@
         <v>44971</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62461,7 +62461,7 @@
         <v>45180</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62534,7 +62534,7 @@
         <v>44826</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62627,7 +62627,7 @@
         <v>45645</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62700,7 +62700,7 @@
         <v>45645</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62773,7 +62773,7 @@
         <v>44769</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62846,7 +62846,7 @@
         <v>45198</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62924,7 +62924,7 @@
         <v>45743</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62997,7 +62997,7 @@
         <v>45153</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63070,7 +63070,7 @@
         <v>44819</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63143,7 +63143,7 @@
         <v>44608</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63216,7 +63216,7 @@
         <v>45040</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63289,7 +63289,7 @@
         <v>45714</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63362,7 +63362,7 @@
         <v>45476</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63435,7 +63435,7 @@
         <v>45685</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63508,7 +63508,7 @@
         <v>45685</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63581,7 +63581,7 @@
         <v>45763</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63659,7 +63659,7 @@
         <v>45008</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63732,7 +63732,7 @@
         <v>45660</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63805,7 +63805,7 @@
         <v>45483</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63878,7 +63878,7 @@
         <v>44830</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63951,7 +63951,7 @@
         <v>45729</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64024,7 +64024,7 @@
         <v>44865</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64097,7 +64097,7 @@
         <v>45173</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64170,7 +64170,7 @@
         <v>45502</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64243,7 +64243,7 @@
         <v>45044</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64316,7 +64316,7 @@
         <v>45474</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64389,7 +64389,7 @@
         <v>45763</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64467,7 +64467,7 @@
         <v>45320</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64540,7 +64540,7 @@
         <v>45764</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64618,7 +64618,7 @@
         <v>44529</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64691,7 +64691,7 @@
         <v>44978</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64764,7 +64764,7 @@
         <v>44880</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64837,7 +64837,7 @@
         <v>44943</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64915,7 +64915,7 @@
         <v>45190</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64988,7 +64988,7 @@
         <v>44775</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65061,7 +65061,7 @@
         <v>44608</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65134,7 +65134,7 @@
         <v>45754</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65207,7 +65207,7 @@
         <v>45148</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65280,7 +65280,7 @@
         <v>45351</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65353,7 +65353,7 @@
         <v>45392</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65426,7 +65426,7 @@
         <v>45554</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65499,7 +65499,7 @@
         <v>45740</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65572,7 +65572,7 @@
         <v>44915</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65645,7 +65645,7 @@
         <v>45447</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65718,7 +65718,7 @@
         <v>45726</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65791,7 +65791,7 @@
         <v>45034</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65864,7 +65864,7 @@
         <v>44965</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65937,7 +65937,7 @@
         <v>45240</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66010,7 +66010,7 @@
         <v>45623</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66088,7 +66088,7 @@
         <v>44946</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66161,7 +66161,7 @@
         <v>44956</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66234,7 +66234,7 @@
         <v>44956</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66307,7 +66307,7 @@
         <v>45589</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66380,7 +66380,7 @@
         <v>45099</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66453,7 +66453,7 @@
         <v>44556</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66526,7 +66526,7 @@
         <v>45329</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66599,7 +66599,7 @@
         <v>45271</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66672,7 +66672,7 @@
         <v>44537</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66745,7 +66745,7 @@
         <v>44908</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66818,7 +66818,7 @@
         <v>45771</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66891,7 +66891,7 @@
         <v>45294</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66964,7 +66964,7 @@
         <v>45345</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67042,7 +67042,7 @@
         <v>45519</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67115,7 +67115,7 @@
         <v>44613</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67193,7 +67193,7 @@
         <v>45034</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67266,7 +67266,7 @@
         <v>45744</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67344,7 +67344,7 @@
         <v>45062</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67417,7 +67417,7 @@
         <v>45247</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67490,7 +67490,7 @@
         <v>45546</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67563,7 +67563,7 @@
         <v>45034</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67636,7 +67636,7 @@
         <v>45182</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67709,7 +67709,7 @@
         <v>45236</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67782,7 +67782,7 @@
         <v>45588</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67855,7 +67855,7 @@
         <v>45588</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67928,7 +67928,7 @@
         <v>45588</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68001,7 +68001,7 @@
         <v>45034</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68074,7 +68074,7 @@
         <v>45454</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68147,7 +68147,7 @@
         <v>44610</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68220,7 +68220,7 @@
         <v>45008</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68293,7 +68293,7 @@
         <v>45764</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68371,7 +68371,7 @@
         <v>44998</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68444,7 +68444,7 @@
         <v>45162</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68517,7 +68517,7 @@
         <v>44564</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68590,7 +68590,7 @@
         <v>45726</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68663,7 +68663,7 @@
         <v>45623</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68736,7 +68736,7 @@
         <v>44606</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68809,7 +68809,7 @@
         <v>45764</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68882,7 +68882,7 @@
         <v>44813</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -68955,7 +68955,7 @@
         <v>45202</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69028,7 +69028,7 @@
         <v>45729</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69101,7 +69101,7 @@
         <v>45232</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69174,7 +69174,7 @@
         <v>45366</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69247,7 +69247,7 @@
         <v>44573</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69320,7 +69320,7 @@
         <v>45758</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69393,7 +69393,7 @@
         <v>45237</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69466,7 +69466,7 @@
         <v>45707</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69539,7 +69539,7 @@
         <v>45161</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69612,7 +69612,7 @@
         <v>45724</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69685,7 +69685,7 @@
         <v>45763</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69763,7 +69763,7 @@
         <v>45302</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69836,7 +69836,7 @@
         <v>44739</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -69909,7 +69909,7 @@
         <v>45280</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -69982,7 +69982,7 @@
         <v>44792</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70055,7 +70055,7 @@
         <v>45279</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70128,7 +70128,7 @@
         <v>45327</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70201,7 +70201,7 @@
         <v>44804</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70274,7 +70274,7 @@
         <v>45336</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70347,7 +70347,7 @@
         <v>45684</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70420,7 +70420,7 @@
         <v>45680</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70493,7 +70493,7 @@
         <v>44803</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70566,7 +70566,7 @@
         <v>45512</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70644,7 +70644,7 @@
         <v>45294</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70717,7 +70717,7 @@
         <v>45323</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70790,7 +70790,7 @@
         <v>45763</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -70868,7 +70868,7 @@
         <v>45763</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -70946,7 +70946,7 @@
         <v>45365</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71019,7 +71019,7 @@
         <v>45365</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71092,7 +71092,7 @@
         <v>45712</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71165,7 +71165,7 @@
         <v>44782</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71238,7 +71238,7 @@
         <v>45541</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71311,7 +71311,7 @@
         <v>45163</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71389,7 +71389,7 @@
         <v>45328</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71462,7 +71462,7 @@
         <v>45273</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71535,7 +71535,7 @@
         <v>45418</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71608,7 +71608,7 @@
         <v>45300</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71681,7 +71681,7 @@
         <v>44573</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71754,7 +71754,7 @@
         <v>45400</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -71827,7 +71827,7 @@
         <v>44879</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -71900,7 +71900,7 @@
         <v>45561</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -71973,7 +71973,7 @@
         <v>44727</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72046,7 +72046,7 @@
         <v>44971</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72119,7 +72119,7 @@
         <v>45751</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72192,7 +72192,7 @@
         <v>45751</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72270,7 +72270,7 @@
         <v>45790</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72348,7 +72348,7 @@
         <v>46041</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72421,7 +72421,7 @@
         <v>46078</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72494,7 +72494,7 @@
         <v>46073</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72567,7 +72567,7 @@
         <v>46142</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72640,7 +72640,7 @@
         <v>44880</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>

--- a/Översikt KRAMFORS.xlsx
+++ b/Översikt KRAMFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45544</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>46183</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>46029</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>46254</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>46003</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>46197</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>46094</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>45763</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45831</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>46287</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>46196</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>44810</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>45763</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>46316</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>46197</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>46044</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>46241</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>46203</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>46181</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>45763</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>46002</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>46136</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>45056</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>45511</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>45996</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>46196</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>46316</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>46136</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>45723</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>46265</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>44713</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>45973</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>45985</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         <v>45785</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>45484</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>45818</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>46317</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>45399</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>45356</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>45660</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44524</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>46314</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>45733</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>44629</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>45282</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>45957</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>45959</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>46195</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>45985</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>46046</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>45818</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>46258</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>45806</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>46317</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>45516</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>44813</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>45898</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>45898</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>46178</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>45114</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>45665</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>45551</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>45786</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>46036</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>46241</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         <v>46244</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>45468</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>45729</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>45840</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>45182</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>46273</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>45511</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>45750</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>44803</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>45924</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>45344</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>44852</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>45943</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>45243</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>45199</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9723,7 +9723,7 @@
         <v>45979</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>45400</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>45114</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         <v>45998</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>46020</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>46021</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>46281</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>46024</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10575,7 +10575,7 @@
         <v>46030</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>45636</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         <v>46048</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>46071</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>46098</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>45670</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11217,7 +11217,7 @@
         <v>44965</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         <v>45764</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>45645</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>45764</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>45156</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>45071</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         <v>44817</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>44804</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         <v>44634</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>44859</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>44508</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>44508</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
         <v>44608</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>44594</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         <v>44509</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>44496</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>44587</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>44511</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>44592</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
         <v>44592</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>44722</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>44688</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>44556</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13103,7 +13103,7 @@
         <v>44508</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>44852</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13249,7 +13249,7 @@
         <v>44817</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>44817</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13395,7 +13395,7 @@
         <v>44762</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>44509</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>44859</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>44581</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44516</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>44509</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>44539</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>44566</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>44687</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>44594</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>44719</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>44715</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>44803</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>44629</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>44594</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>44802</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>44509</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>44540</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>44550</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>44607</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>44876</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>44628</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15001,7 +15001,7 @@
         <v>44616</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>44749</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15147,7 +15147,7 @@
         <v>44697</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         <v>44581</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>44503</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>44859</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15439,7 +15439,7 @@
         <v>44601</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>44782</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>44581</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         <v>45883</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>45883</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>45888</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>44804</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>45721</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>45616</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>45890</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>45890</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>45205</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>45513</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>44840</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16466,7 +16466,7 @@
         <v>45672</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
         <v>45712</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16612,7 +16612,7 @@
         <v>44741</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>45890</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>45674</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>44788</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>44860</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>45883</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>45572</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>45883</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>45898</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>45898</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>45898</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>45898</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>45419</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>44853</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>45724</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>45898</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         <v>45043</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>45898</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17931,7 +17931,7 @@
         <v>45898</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>45044</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
         <v>45901</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>45365</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>45898</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18296,7 +18296,7 @@
         <v>45898</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>45901</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>45898</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>45901</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         <v>45239</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>45209</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>45225</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>45909</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>45909</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>45433</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>44897</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19099,7 +19099,7 @@
         <v>45909</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>45947</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>45947</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>46098</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>46047</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45232</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>46161</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>44883</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19688,7 +19688,7 @@
         <v>45947</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>45728</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>45912</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>45957</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>46064</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>45959</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>46164</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>45282</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>46164</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>46163</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>46163</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20496,7 +20496,7 @@
         <v>46164</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>45918</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>44750</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>45678</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>46146</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>45952</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>45981</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>46168</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>46167</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>44574</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>45173</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>45926</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>45926</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21445,7 +21445,7 @@
         <v>45757</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>46169</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>45034</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>46168</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>45496</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21820,7 +21820,7 @@
         <v>45000</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>45932</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>44774</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45085</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>46170</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>46174</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>44824</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>44852</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>45935</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>46174</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22565,7 +22565,7 @@
         <v>45936</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>44834</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>45937</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22784,7 +22784,7 @@
         <v>45936</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22857,7 +22857,7 @@
         <v>45937</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>46174</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>46174</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23076,7 +23076,7 @@
         <v>46174</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23149,7 +23149,7 @@
         <v>45943</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>45674</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>44901</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23368,7 +23368,7 @@
         <v>44747</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23441,7 +23441,7 @@
         <v>46177</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23514,7 +23514,7 @@
         <v>46176</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>45450</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23660,7 +23660,7 @@
         <v>45265</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23733,7 +23733,7 @@
         <v>45261</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23806,7 +23806,7 @@
         <v>45390</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>45664</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23952,7 +23952,7 @@
         <v>45946</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24025,7 +24025,7 @@
         <v>45674</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24098,7 +24098,7 @@
         <v>46176</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>45089</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>45947</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24317,7 +24317,7 @@
         <v>45034</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>46181</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>45520</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>45698</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24614,7 +24614,7 @@
         <v>45952</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24687,7 +24687,7 @@
         <v>46181</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>46181</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24833,7 +24833,7 @@
         <v>46181</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24906,7 +24906,7 @@
         <v>46181</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>46181</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25052,7 +25052,7 @@
         <v>45307</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25125,7 +25125,7 @@
         <v>45952</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>45951</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25271,7 +25271,7 @@
         <v>45957</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>44958</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>44880</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>45960</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25568,7 +25568,7 @@
         <v>45534</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25641,7 +25641,7 @@
         <v>45964</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25714,7 +25714,7 @@
         <v>45964</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>45964</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25860,7 +25860,7 @@
         <v>45964</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25933,7 +25933,7 @@
         <v>45124</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>45964</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26084,7 +26084,7 @@
         <v>46188</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26157,7 +26157,7 @@
         <v>45964</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>45964</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>45964</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>45524</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26459,7 +26459,7 @@
         <v>45099</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         <v>44907</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>46188</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26683,7 +26683,7 @@
         <v>45884</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26756,7 +26756,7 @@
         <v>46188</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26829,7 +26829,7 @@
         <v>46190</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>46190</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26975,7 +26975,7 @@
         <v>46190</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>46190</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>45950</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27194,7 +27194,7 @@
         <v>45950</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>45968</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27340,7 +27340,7 @@
         <v>45968</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27413,7 +27413,7 @@
         <v>46195</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27486,7 +27486,7 @@
         <v>46195</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         <v>46195</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27632,7 +27632,7 @@
         <v>45971</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27705,7 +27705,7 @@
         <v>45273</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27778,7 +27778,7 @@
         <v>45324</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27851,7 +27851,7 @@
         <v>45974</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>45974</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>45974</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28070,7 +28070,7 @@
         <v>45974</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28143,7 +28143,7 @@
         <v>45974</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>45974</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         <v>45579</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>45974</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>45680</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28513,7 +28513,7 @@
         <v>45236</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>46199</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>46198</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>46199</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>46198</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>46198</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28951,7 +28951,7 @@
         <v>45278</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44574</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29097,7 +29097,7 @@
         <v>46199</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>45979</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>46034</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29316,7 +29316,7 @@
         <v>46198</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29389,7 +29389,7 @@
         <v>45771</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29462,7 +29462,7 @@
         <v>45979</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29535,7 +29535,7 @@
         <v>45979</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>45000</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>45979</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>45979</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29832,7 +29832,7 @@
         <v>45979</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
         <v>45981</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29978,7 +29978,7 @@
         <v>45982</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>45982</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>45153</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30197,7 +30197,7 @@
         <v>45440</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30270,7 +30270,7 @@
         <v>45981</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
         <v>46204</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>45981</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>45986</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>45271</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         <v>46205</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>45355</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>45475</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>45987</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30927,7 +30927,7 @@
         <v>45987</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>45278</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31073,7 +31073,7 @@
         <v>45644</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>46209</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>46209</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>46209</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31365,7 +31365,7 @@
         <v>45988</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>45988</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>45265</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>46210</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>46210</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31730,7 +31730,7 @@
         <v>45994</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31803,7 +31803,7 @@
         <v>45099</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>45959</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>45996</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>45638</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>45754</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>45433</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>45450</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>45999</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32387,7 +32387,7 @@
         <v>45999</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>46000</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32533,7 +32533,7 @@
         <v>46001</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>46140</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32679,7 +32679,7 @@
         <v>46002</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32752,7 +32752,7 @@
         <v>45776</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32830,7 +32830,7 @@
         <v>46000</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32903,7 +32903,7 @@
         <v>46164</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32976,7 +32976,7 @@
         <v>46000</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>46224</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>45770</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>46225</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>45782</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33351,7 +33351,7 @@
         <v>46008</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>46008</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33497,7 +33497,7 @@
         <v>46007</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33570,7 +33570,7 @@
         <v>46008</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>46008</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>46232</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33789,7 +33789,7 @@
         <v>46007</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>46008</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>46008</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>46008</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34081,7 +34081,7 @@
         <v>44958</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34154,7 +34154,7 @@
         <v>46009</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34227,7 +34227,7 @@
         <v>46237</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34300,7 +34300,7 @@
         <v>46009</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34373,7 +34373,7 @@
         <v>46009</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         <v>46009</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>46280</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
         <v>46009</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>45281</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34738,7 +34738,7 @@
         <v>44834</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34816,7 +34816,7 @@
         <v>44854</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34889,7 +34889,7 @@
         <v>46237</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34962,7 +34962,7 @@
         <v>45306</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35035,7 +35035,7 @@
         <v>45408</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35108,7 +35108,7 @@
         <v>45476</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>44540</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35254,7 +35254,7 @@
         <v>45496</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35332,7 +35332,7 @@
         <v>46280</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>46014</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>45169</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>46238</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35624,7 +35624,7 @@
         <v>46238</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
         <v>46281</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35770,7 +35770,7 @@
         <v>46022</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>45790</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>46240</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>46024</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36062,7 +36062,7 @@
         <v>46239</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36135,7 +36135,7 @@
         <v>46239</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>46024</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36281,7 +36281,7 @@
         <v>46024</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>46024</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36427,7 +36427,7 @@
         <v>46281</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>46238</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36573,7 +36573,7 @@
         <v>45496</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>46029</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>45792</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36797,7 +36797,7 @@
         <v>46284</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36870,7 +36870,7 @@
         <v>46284</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36943,7 +36943,7 @@
         <v>45567</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>44894</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37089,7 +37089,7 @@
         <v>46031</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37162,7 +37162,7 @@
         <v>46034</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>46031</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37308,7 +37308,7 @@
         <v>45618</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37381,7 +37381,7 @@
         <v>45231</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>45791</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37527,7 +37527,7 @@
         <v>45415</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>46283</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>45418</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37746,7 +37746,7 @@
         <v>46241</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37824,7 +37824,7 @@
         <v>44804</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37897,7 +37897,7 @@
         <v>45552</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>44503</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38043,7 +38043,7 @@
         <v>46042</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38116,7 +38116,7 @@
         <v>46287</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>46288</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>46041</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38340,7 +38340,7 @@
         <v>46041</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38413,7 +38413,7 @@
         <v>46041</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38486,7 +38486,7 @@
         <v>45435</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>46043</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>46266</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38710,7 +38710,7 @@
         <v>46043</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38783,7 +38783,7 @@
         <v>46044</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>45797</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>45797</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>46043</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39075,7 +39075,7 @@
         <v>46043</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39148,7 +39148,7 @@
         <v>46043</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39221,7 +39221,7 @@
         <v>46244</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39294,7 +39294,7 @@
         <v>44903</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39367,7 +39367,7 @@
         <v>45798</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39445,7 +39445,7 @@
         <v>46044</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>46043</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39596,7 +39596,7 @@
         <v>46048</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39669,7 +39669,7 @@
         <v>46287</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39742,7 +39742,7 @@
         <v>46287</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39815,7 +39815,7 @@
         <v>46046</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>45799</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39966,7 +39966,7 @@
         <v>46046</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>46046</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40112,7 +40112,7 @@
         <v>46047</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40185,7 +40185,7 @@
         <v>46244</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40258,7 +40258,7 @@
         <v>46049</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40331,7 +40331,7 @@
         <v>46247</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40409,7 +40409,7 @@
         <v>45799</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40482,7 +40482,7 @@
         <v>45799</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>46049</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40633,7 +40633,7 @@
         <v>46049</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40706,7 +40706,7 @@
         <v>45036</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>44834</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40857,7 +40857,7 @@
         <v>46046</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>45805</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41003,7 +41003,7 @@
         <v>45805</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41076,7 +41076,7 @@
         <v>46289</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41149,7 +41149,7 @@
         <v>45475</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41222,7 +41222,7 @@
         <v>45643</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41295,7 +41295,7 @@
         <v>46054</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>46054</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>46046</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41514,7 +41514,7 @@
         <v>45712</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>46054</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41660,7 +41660,7 @@
         <v>45273</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41733,7 +41733,7 @@
         <v>45734</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41806,7 +41806,7 @@
         <v>45678</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41879,7 +41879,7 @@
         <v>45807</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41957,7 +41957,7 @@
         <v>45328</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42035,7 +42035,7 @@
         <v>46287</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42108,7 +42108,7 @@
         <v>45593</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42181,7 +42181,7 @@
         <v>45654</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42254,7 +42254,7 @@
         <v>45726</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>45753</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>46062</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42473,7 +42473,7 @@
         <v>45782</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42546,7 +42546,7 @@
         <v>45653</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42619,7 +42619,7 @@
         <v>45750</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42692,7 +42692,7 @@
         <v>46120</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42765,7 +42765,7 @@
         <v>45803</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42838,7 +42838,7 @@
         <v>44942</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
         <v>46063</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42984,7 +42984,7 @@
         <v>46063</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43057,7 +43057,7 @@
         <v>45813</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43130,7 +43130,7 @@
         <v>45813</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43203,7 +43203,7 @@
         <v>45768</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43276,7 +43276,7 @@
         <v>46248</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43354,7 +43354,7 @@
         <v>45818</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43432,7 +43432,7 @@
         <v>46069</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43505,7 +43505,7 @@
         <v>46248</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45819</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43651,7 +43651,7 @@
         <v>46071</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43724,7 +43724,7 @@
         <v>46043</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43797,7 +43797,7 @@
         <v>46072</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43870,7 +43870,7 @@
         <v>46239</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43943,7 +43943,7 @@
         <v>46253</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44016,7 +44016,7 @@
         <v>46072</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44089,7 +44089,7 @@
         <v>46077</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>46251</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44235,7 +44235,7 @@
         <v>46253</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>46251</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44391,7 +44391,7 @@
         <v>46253</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44469,7 +44469,7 @@
         <v>46296</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44547,7 +44547,7 @@
         <v>46296</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>45825</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45825</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>45825</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44844,7 +44844,7 @@
         <v>45825</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44917,7 +44917,7 @@
         <v>46251</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>45825</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45063,7 +45063,7 @@
         <v>45825</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45136,7 +45136,7 @@
         <v>46253</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>45825</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45282,7 +45282,7 @@
         <v>45825</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45355,7 +45355,7 @@
         <v>46253</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45428,7 +45428,7 @@
         <v>45825</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>45825</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>45832</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45647,7 +45647,7 @@
         <v>45734</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45720,7 +45720,7 @@
         <v>45833</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45798,7 +45798,7 @@
         <v>45834</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>46254</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45949,7 +45949,7 @@
         <v>46254</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46022,7 +46022,7 @@
         <v>46300</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46095,7 +46095,7 @@
         <v>46300</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46168,7 +46168,7 @@
         <v>46254</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46246,7 +46246,7 @@
         <v>46254</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46324,7 +46324,7 @@
         <v>45838</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46397,7 +46397,7 @@
         <v>46300</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>45838</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46548,7 +46548,7 @@
         <v>45840</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46626,7 +46626,7 @@
         <v>45482</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>45840</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46782,7 +46782,7 @@
         <v>46093</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46855,7 +46855,7 @@
         <v>45840</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>46256</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>46300</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>46094</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>45365</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>46052</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>46256</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47371,7 +47371,7 @@
         <v>45842</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47444,7 +47444,7 @@
         <v>46297</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47517,7 +47517,7 @@
         <v>45841</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47590,7 +47590,7 @@
         <v>45841</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47663,7 +47663,7 @@
         <v>46098</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47736,7 +47736,7 @@
         <v>46298</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47809,7 +47809,7 @@
         <v>45841</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47887,7 +47887,7 @@
         <v>45841</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>46098</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48038,7 +48038,7 @@
         <v>46099</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48116,7 +48116,7 @@
         <v>46100</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48189,7 +48189,7 @@
         <v>46104</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48262,7 +48262,7 @@
         <v>46104</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48335,7 +48335,7 @@
         <v>45469</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48408,7 +48408,7 @@
         <v>44519</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48481,7 +48481,7 @@
         <v>46105</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48554,7 +48554,7 @@
         <v>46258</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48632,7 +48632,7 @@
         <v>45852</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48705,7 +48705,7 @@
         <v>44529</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48778,7 +48778,7 @@
         <v>45645</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48851,7 +48851,7 @@
         <v>46300</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48924,7 +48924,7 @@
         <v>46301</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48997,7 +48997,7 @@
         <v>45855</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49070,7 +49070,7 @@
         <v>45799</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49143,7 +49143,7 @@
         <v>45860</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49216,7 +49216,7 @@
         <v>45859</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45799</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49362,7 +49362,7 @@
         <v>45825</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49435,7 +49435,7 @@
         <v>45749</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49508,7 +49508,7 @@
         <v>46304</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>46304</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49654,7 +49654,7 @@
         <v>46119</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49727,7 +49727,7 @@
         <v>46293</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49800,7 +49800,7 @@
         <v>44536</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49878,7 +49878,7 @@
         <v>45874</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49951,7 +49951,7 @@
         <v>45874</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50024,7 +50024,7 @@
         <v>45873</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50097,7 +50097,7 @@
         <v>44574</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50170,7 +50170,7 @@
         <v>46127</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50243,7 +50243,7 @@
         <v>45874</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50316,7 +50316,7 @@
         <v>46112</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50389,7 +50389,7 @@
         <v>46071</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50462,7 +50462,7 @@
         <v>45876</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50535,7 +50535,7 @@
         <v>44634</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50608,7 +50608,7 @@
         <v>46127</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50681,7 +50681,7 @@
         <v>45875</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50754,7 +50754,7 @@
         <v>45833</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50827,7 +50827,7 @@
         <v>46265</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50905,7 +50905,7 @@
         <v>46128</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>45632</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51051,7 +51051,7 @@
         <v>46265</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51124,7 +51124,7 @@
         <v>46262</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51197,7 +51197,7 @@
         <v>46262</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51270,7 +51270,7 @@
         <v>45881</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>45881</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51416,7 +51416,7 @@
         <v>45545</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51489,7 +51489,7 @@
         <v>46134</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51562,7 +51562,7 @@
         <v>46265</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51640,7 +51640,7 @@
         <v>44909</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51713,7 +51713,7 @@
         <v>45538</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51786,7 +51786,7 @@
         <v>46134</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51859,7 +51859,7 @@
         <v>46265</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51937,7 +51937,7 @@
         <v>46069</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52010,7 +52010,7 @@
         <v>45425</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52088,7 +52088,7 @@
         <v>44503</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>44908</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52234,7 +52234,7 @@
         <v>46307</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52307,7 +52307,7 @@
         <v>46301</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45797</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52453,7 +52453,7 @@
         <v>45664</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52526,7 +52526,7 @@
         <v>46265</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52604,7 +52604,7 @@
         <v>46265</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52682,7 +52682,7 @@
         <v>45491</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>44959</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52838,7 +52838,7 @@
         <v>44872</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52911,7 +52911,7 @@
         <v>46266</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52984,7 +52984,7 @@
         <v>45420</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53057,7 +53057,7 @@
         <v>46036</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53130,7 +53130,7 @@
         <v>45960</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53203,7 +53203,7 @@
         <v>46266</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53276,7 +53276,7 @@
         <v>46266</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53349,7 +53349,7 @@
         <v>46309</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53422,7 +53422,7 @@
         <v>46262</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53495,7 +53495,7 @@
         <v>46136</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53568,7 +53568,7 @@
         <v>46307</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53641,7 +53641,7 @@
         <v>46266</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53714,7 +53714,7 @@
         <v>46265</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53787,7 +53787,7 @@
         <v>44958</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53860,7 +53860,7 @@
         <v>44958</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53933,7 +53933,7 @@
         <v>46310</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54006,7 +54006,7 @@
         <v>46309</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54079,7 +54079,7 @@
         <v>45518</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54152,7 +54152,7 @@
         <v>45876</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54225,7 +54225,7 @@
         <v>45771</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54298,7 +54298,7 @@
         <v>45896</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54371,7 +54371,7 @@
         <v>46069</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54444,7 +54444,7 @@
         <v>45425</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54517,7 +54517,7 @@
         <v>46107</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54590,7 +54590,7 @@
         <v>46267</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54663,7 +54663,7 @@
         <v>45909</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54736,7 +54736,7 @@
         <v>44991</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54814,7 +54814,7 @@
         <v>46314</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54892,7 +54892,7 @@
         <v>44629</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54965,7 +54965,7 @@
         <v>44546</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55038,7 +55038,7 @@
         <v>44956</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55111,7 +55111,7 @@
         <v>46268</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55184,7 +55184,7 @@
         <v>45943</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55257,7 +55257,7 @@
         <v>45750</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55330,7 +55330,7 @@
         <v>46314</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55403,7 +55403,7 @@
         <v>46140</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55476,7 +55476,7 @@
         <v>46314</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55554,7 +55554,7 @@
         <v>45973</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55627,7 +55627,7 @@
         <v>45821</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55700,7 +55700,7 @@
         <v>46314</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55773,7 +55773,7 @@
         <v>45875</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55846,7 +55846,7 @@
         <v>46268</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55919,7 +55919,7 @@
         <v>45513</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55992,7 +55992,7 @@
         <v>44855</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56065,7 +56065,7 @@
         <v>45320</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56143,7 +56143,7 @@
         <v>46316</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56216,7 +56216,7 @@
         <v>45544</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56289,7 +56289,7 @@
         <v>45813</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56362,7 +56362,7 @@
         <v>45225</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56435,7 +56435,7 @@
         <v>46316</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56513,7 +56513,7 @@
         <v>46029</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56586,7 +56586,7 @@
         <v>45685</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56659,7 +56659,7 @@
         <v>46273</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56732,7 +56732,7 @@
         <v>46316</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56810,7 +56810,7 @@
         <v>45841</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56883,7 +56883,7 @@
         <v>46315</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56956,7 +56956,7 @@
         <v>44888</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57029,7 +57029,7 @@
         <v>45552</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57102,7 +57102,7 @@
         <v>46273</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57175,7 +57175,7 @@
         <v>46316</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57248,7 +57248,7 @@
         <v>46064</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57321,7 +57321,7 @@
         <v>45733</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57394,7 +57394,7 @@
         <v>46084</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57467,7 +57467,7 @@
         <v>45959</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57540,7 +57540,7 @@
         <v>46315</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57613,7 +57613,7 @@
         <v>45526</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57686,7 +57686,7 @@
         <v>46314</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57759,7 +57759,7 @@
         <v>44638</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57832,7 +57832,7 @@
         <v>46318</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57905,7 +57905,7 @@
         <v>45190</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57978,7 +57978,7 @@
         <v>45672</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58051,7 +58051,7 @@
         <v>45818</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58124,7 +58124,7 @@
         <v>45553</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58197,7 +58197,7 @@
         <v>46318</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58270,7 +58270,7 @@
         <v>46142</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58343,7 +58343,7 @@
         <v>46316</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58421,7 +58421,7 @@
         <v>45989</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58494,7 +58494,7 @@
         <v>45324</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58567,7 +58567,7 @@
         <v>45842</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58640,7 +58640,7 @@
         <v>45959</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58713,7 +58713,7 @@
         <v>45931</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58786,7 +58786,7 @@
         <v>44894</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58859,7 +58859,7 @@
         <v>45894</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58932,7 +58932,7 @@
         <v>45881</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59005,7 +59005,7 @@
         <v>45723</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59078,7 +59078,7 @@
         <v>45173</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59151,7 +59151,7 @@
         <v>46274</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59229,7 +59229,7 @@
         <v>46274</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59302,7 +59302,7 @@
         <v>46146</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59375,7 +59375,7 @@
         <v>44916</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59448,7 +59448,7 @@
         <v>44949</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59521,7 +59521,7 @@
         <v>46146</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59594,7 +59594,7 @@
         <v>46148</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59672,7 +59672,7 @@
         <v>46147</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59750,7 +59750,7 @@
         <v>45392</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59823,7 +59823,7 @@
         <v>45189</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59896,7 +59896,7 @@
         <v>45162</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59969,7 +59969,7 @@
         <v>45162</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60042,7 +60042,7 @@
         <v>45589</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60115,7 +60115,7 @@
         <v>45713</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60188,7 +60188,7 @@
         <v>45120</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60261,7 +60261,7 @@
         <v>45189</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60334,7 +60334,7 @@
         <v>46153</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60407,7 +60407,7 @@
         <v>45959</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60480,7 +60480,7 @@
         <v>45356</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60553,7 +60553,7 @@
         <v>45461</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60631,7 +60631,7 @@
         <v>46155</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60704,7 +60704,7 @@
         <v>45950</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60777,7 +60777,7 @@
         <v>46155</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60850,7 +60850,7 @@
         <v>46155</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60923,7 +60923,7 @@
         <v>45916</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60996,7 +60996,7 @@
         <v>46160</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61074,7 +61074,7 @@
         <v>46160</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61147,7 +61147,7 @@
         <v>45034</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61220,7 +61220,7 @@
         <v>44956</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61293,7 +61293,7 @@
         <v>45679</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61366,7 +61366,7 @@
         <v>46157</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61439,7 +61439,7 @@
         <v>45608</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61512,7 +61512,7 @@
         <v>45707</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61585,7 +61585,7 @@
         <v>46160</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61658,7 +61658,7 @@
         <v>44998</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61731,7 +61731,7 @@
         <v>44965</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61804,7 +61804,7 @@
         <v>44965</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61877,7 +61877,7 @@
         <v>45684</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61950,7 +61950,7 @@
         <v>45062</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62023,7 +62023,7 @@
         <v>44571</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62096,7 +62096,7 @@
         <v>45324</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62169,7 +62169,7 @@
         <v>45036</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62242,7 +62242,7 @@
         <v>45365</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62315,7 +62315,7 @@
         <v>45636</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62388,7 +62388,7 @@
         <v>44971</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62461,7 +62461,7 @@
         <v>45180</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62534,7 +62534,7 @@
         <v>44826</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62627,7 +62627,7 @@
         <v>45645</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62700,7 +62700,7 @@
         <v>45645</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62773,7 +62773,7 @@
         <v>44769</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62846,7 +62846,7 @@
         <v>45198</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62924,7 +62924,7 @@
         <v>45743</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62997,7 +62997,7 @@
         <v>45153</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63070,7 +63070,7 @@
         <v>44819</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63143,7 +63143,7 @@
         <v>44608</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63216,7 +63216,7 @@
         <v>45040</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63289,7 +63289,7 @@
         <v>45714</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63362,7 +63362,7 @@
         <v>45476</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63435,7 +63435,7 @@
         <v>45685</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63508,7 +63508,7 @@
         <v>45685</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63581,7 +63581,7 @@
         <v>45763</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63659,7 +63659,7 @@
         <v>45008</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63732,7 +63732,7 @@
         <v>45660</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63805,7 +63805,7 @@
         <v>45483</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63878,7 +63878,7 @@
         <v>44830</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63951,7 +63951,7 @@
         <v>45729</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64024,7 +64024,7 @@
         <v>44865</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64097,7 +64097,7 @@
         <v>45173</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64170,7 +64170,7 @@
         <v>45502</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64243,7 +64243,7 @@
         <v>45044</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64316,7 +64316,7 @@
         <v>45474</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64389,7 +64389,7 @@
         <v>45763</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64467,7 +64467,7 @@
         <v>45320</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64540,7 +64540,7 @@
         <v>45764</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64618,7 +64618,7 @@
         <v>44529</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64691,7 +64691,7 @@
         <v>44978</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64764,7 +64764,7 @@
         <v>44880</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64837,7 +64837,7 @@
         <v>44943</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64915,7 +64915,7 @@
         <v>45190</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64988,7 +64988,7 @@
         <v>44775</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65061,7 +65061,7 @@
         <v>44608</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65134,7 +65134,7 @@
         <v>45754</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65207,7 +65207,7 @@
         <v>45148</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65280,7 +65280,7 @@
         <v>45351</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65353,7 +65353,7 @@
         <v>45392</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65426,7 +65426,7 @@
         <v>45554</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65499,7 +65499,7 @@
         <v>45740</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65572,7 +65572,7 @@
         <v>44915</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65645,7 +65645,7 @@
         <v>45447</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65718,7 +65718,7 @@
         <v>45726</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65791,7 +65791,7 @@
         <v>45034</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65864,7 +65864,7 @@
         <v>44965</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65937,7 +65937,7 @@
         <v>45240</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66010,7 +66010,7 @@
         <v>45623</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66088,7 +66088,7 @@
         <v>44946</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66161,7 +66161,7 @@
         <v>44956</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66234,7 +66234,7 @@
         <v>44956</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66307,7 +66307,7 @@
         <v>45589</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66380,7 +66380,7 @@
         <v>45099</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66453,7 +66453,7 @@
         <v>44556</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66526,7 +66526,7 @@
         <v>45329</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66599,7 +66599,7 @@
         <v>45271</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66672,7 +66672,7 @@
         <v>44537</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66745,7 +66745,7 @@
         <v>44908</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66818,7 +66818,7 @@
         <v>45771</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66891,7 +66891,7 @@
         <v>45294</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66964,7 +66964,7 @@
         <v>45345</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67042,7 +67042,7 @@
         <v>45519</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67115,7 +67115,7 @@
         <v>44613</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67193,7 +67193,7 @@
         <v>45034</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67266,7 +67266,7 @@
         <v>45744</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67344,7 +67344,7 @@
         <v>45062</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67417,7 +67417,7 @@
         <v>45247</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67490,7 +67490,7 @@
         <v>45546</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67563,7 +67563,7 @@
         <v>45034</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67636,7 +67636,7 @@
         <v>45182</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67709,7 +67709,7 @@
         <v>45236</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67782,7 +67782,7 @@
         <v>45588</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67855,7 +67855,7 @@
         <v>45588</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67928,7 +67928,7 @@
         <v>45588</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68001,7 +68001,7 @@
         <v>45034</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68074,7 +68074,7 @@
         <v>45454</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68147,7 +68147,7 @@
         <v>44610</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68220,7 +68220,7 @@
         <v>45008</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68293,7 +68293,7 @@
         <v>45764</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68371,7 +68371,7 @@
         <v>44998</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68444,7 +68444,7 @@
         <v>45162</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68517,7 +68517,7 @@
         <v>44564</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68590,7 +68590,7 @@
         <v>45726</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68663,7 +68663,7 @@
         <v>45623</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68736,7 +68736,7 @@
         <v>44606</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68809,7 +68809,7 @@
         <v>45764</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68882,7 +68882,7 @@
         <v>44813</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -68955,7 +68955,7 @@
         <v>45202</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69028,7 +69028,7 @@
         <v>45729</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69101,7 +69101,7 @@
         <v>45232</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69174,7 +69174,7 @@
         <v>45366</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69247,7 +69247,7 @@
         <v>44573</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69320,7 +69320,7 @@
         <v>45758</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69393,7 +69393,7 @@
         <v>45237</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69466,7 +69466,7 @@
         <v>45707</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69539,7 +69539,7 @@
         <v>45161</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69612,7 +69612,7 @@
         <v>45724</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69685,7 +69685,7 @@
         <v>45763</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69763,7 +69763,7 @@
         <v>45302</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69836,7 +69836,7 @@
         <v>44739</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -69909,7 +69909,7 @@
         <v>45280</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -69982,7 +69982,7 @@
         <v>44792</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70055,7 +70055,7 @@
         <v>45279</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70128,7 +70128,7 @@
         <v>45327</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70201,7 +70201,7 @@
         <v>44804</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70274,7 +70274,7 @@
         <v>45336</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70347,7 +70347,7 @@
         <v>45684</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70420,7 +70420,7 @@
         <v>45680</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70493,7 +70493,7 @@
         <v>44803</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70566,7 +70566,7 @@
         <v>45512</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70644,7 +70644,7 @@
         <v>45294</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70717,7 +70717,7 @@
         <v>45323</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70790,7 +70790,7 @@
         <v>45763</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -70868,7 +70868,7 @@
         <v>45763</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -70946,7 +70946,7 @@
         <v>45365</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71019,7 +71019,7 @@
         <v>45365</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71092,7 +71092,7 @@
         <v>45712</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71165,7 +71165,7 @@
         <v>44782</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71238,7 +71238,7 @@
         <v>45541</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71311,7 +71311,7 @@
         <v>45163</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71389,7 +71389,7 @@
         <v>45328</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71462,7 +71462,7 @@
         <v>45273</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71535,7 +71535,7 @@
         <v>45418</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71608,7 +71608,7 @@
         <v>45300</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71681,7 +71681,7 @@
         <v>44573</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71754,7 +71754,7 @@
         <v>45400</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -71827,7 +71827,7 @@
         <v>44879</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -71900,7 +71900,7 @@
         <v>45561</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -71973,7 +71973,7 @@
         <v>44727</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72046,7 +72046,7 @@
         <v>44971</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72119,7 +72119,7 @@
         <v>45751</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72192,7 +72192,7 @@
         <v>45751</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72270,7 +72270,7 @@
         <v>45790</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72348,7 +72348,7 @@
         <v>46041</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72421,7 +72421,7 @@
         <v>46078</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72494,7 +72494,7 @@
         <v>46073</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72567,7 +72567,7 @@
         <v>46142</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72640,7 +72640,7 @@
         <v>44880</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
